--- a/data/llm_costs.xlsx
+++ b/data/llm_costs.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_status" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vendor_summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="price_history" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="run_metadata" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -600,7 +601,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -667,7 +668,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -734,7 +735,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -801,7 +802,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -868,7 +869,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -935,7 +936,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1003,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1070,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1137,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1200,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1263,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1326,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1389,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1450,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1511,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1578,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1645,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1712,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1779,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1846,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1913,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1980,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2047,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2104,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2161,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2218,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2275,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2332,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2389,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2452,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2515,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2578,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2641,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2698,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2755,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2822,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2889,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2956,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3023,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3090,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3157,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3224,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3291,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3348,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3405,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3462,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3519,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3576,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3633,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3690,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3747,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3804,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3861,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3928,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3995,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4062,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4129,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4196,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4263,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4330,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4397,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4464,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4531,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4598,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4665,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4732,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4799,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4866,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -4932,7 +4933,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4996,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5059,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5122,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5185,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5250,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5315,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5380,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5445,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5502,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5559,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5618,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5677,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5736,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5795,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5860,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5923,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5986,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6049,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6114,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6183,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6252,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6321,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6390,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6457,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6524,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6593,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6662,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6728,7 +6729,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6795,7 +6796,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6861,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6923,7 +6924,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6989,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -7053,7 +7054,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7119,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7182,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7245,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7310,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7375,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -7437,7 +7438,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7507,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7576,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7645,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7714,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7783,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -7875,7 +7876,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7909,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -7941,7 +7942,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7975,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8008,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -8040,7 +8041,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-24T14:02:54+00:00</t>
+          <t>2026-05-24T16:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q153"/>
+  <dimension ref="A1:Q266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -18146,6 +18147,7313 @@
         </is>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Claude Haiku 4.5</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>haiku</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="n">
+        <v>5</v>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Claude Opus 4</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="n">
+        <v>15</v>
+      </c>
+      <c r="H155" t="n">
+        <v>75</v>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="K155" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.1</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="n">
+        <v>15</v>
+      </c>
+      <c r="H156" t="n">
+        <v>75</v>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="K156" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.5</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="n">
+        <v>5</v>
+      </c>
+      <c r="H157" t="n">
+        <v>25</v>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.6</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="n">
+        <v>5</v>
+      </c>
+      <c r="H158" t="n">
+        <v>25</v>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.7</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="n">
+        <v>5</v>
+      </c>
+      <c r="H159" t="n">
+        <v>25</v>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="n">
+        <v>3</v>
+      </c>
+      <c r="H160" t="n">
+        <v>15</v>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.5</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="n">
+        <v>3</v>
+      </c>
+      <c r="H161" t="n">
+        <v>15</v>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="n">
+        <v>3</v>
+      </c>
+      <c r="H162" t="n">
+        <v>15</v>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H169" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H170" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H171" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H172" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H173" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>$0.054 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H174" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>$0.054 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H176" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Preview TTS</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Preview TTS</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="n">
+        <v>5</v>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="n">
+        <v>5</v>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="n">
+        <v>18</v>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>$0.225, prompts &lt;= 200k tokens $0.45, prompts &gt; 200k $8.10 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="n">
+        <v>10</v>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro Preview TTS</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro Preview TTS</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H189" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="n">
+        <v>1</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H190" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="n">
+        <v>1</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H191" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H192" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="n">
+        <v>1</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H193" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>$0.09 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H194" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>$0.09 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" t="n">
+        <v>3</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="n">
+        <v>1</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>$0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H196" t="n">
+        <v>3</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="n">
+        <v>1</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>$0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="n">
+        <v>2</v>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>text, image</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash TTS Preview</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash TTS Preview</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="n">
+        <v>1</v>
+      </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H211" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H212" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H213" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="n">
+        <v>1</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H214" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H219" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H220" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H221" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="n">
+        <v>1</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H222" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="n">
+        <v>1</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="n">
+        <v>6</v>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="n">
+        <v>6</v>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>$0.36, prompts &lt;= 200k tokens $0.72, prompts &gt; 200k $8.10 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="n">
+        <v>12</v>
+      </c>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H227" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="n">
+        <v>1</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>$0.075 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H228" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="n">
+        <v>1</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>$0.08 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H229" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="n">
+        <v>1</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>$0.27 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H230" t="n">
+        <v>9</v>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="n">
+        <v>1</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>$0.15 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Gemini Embedding</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>embedding</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Gemini Embedding</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>embedding</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="n">
+        <v>1</v>
+      </c>
+      <c r="H233" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H234" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="n">
+        <v>2</v>
+      </c>
+      <c r="H235" t="n">
+        <v>5</v>
+      </c>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="n">
+        <v>1</v>
+      </c>
+      <c r="H236" t="n">
+        <v>5</v>
+      </c>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>chat-latest</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>chat</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="n">
+        <v>5</v>
+      </c>
+      <c r="H237" t="n">
+        <v>30</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>computer-use-preview</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>computer</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H238" t="n">
+        <v>6</v>
+      </c>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini-transcribe</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H239" t="n">
+        <v>5</v>
+      </c>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Image generation models | Video generation models | Transcription models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>gpt-4o-transcribe</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H240" t="n">
+        <v>10</v>
+      </c>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Image generation models | Video generation models | Transcription models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>gpt-5.3-codex</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H241" t="n">
+        <v>14</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>5</v>
+      </c>
+      <c r="H242" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I242" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H243" t="n">
+        <v>15</v>
+      </c>
+      <c r="I243" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>gpt-5.4-mini</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H244" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I244" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>gpt-5.4-nano</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H245" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I245" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>gpt-5.4-pro</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>60</v>
+      </c>
+      <c r="H246" t="n">
+        <v>270</v>
+      </c>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>gpt-5.4-pro</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G247" t="n">
+        <v>30</v>
+      </c>
+      <c r="H247" t="n">
+        <v>180</v>
+      </c>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G248" t="n">
+        <v>10</v>
+      </c>
+      <c r="H248" t="n">
+        <v>45</v>
+      </c>
+      <c r="I248" t="n">
+        <v>1</v>
+      </c>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G249" t="n">
+        <v>5</v>
+      </c>
+      <c r="H249" t="n">
+        <v>30</v>
+      </c>
+      <c r="I249" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>gpt-5.5-pro</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>60</v>
+      </c>
+      <c r="H250" t="n">
+        <v>270</v>
+      </c>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>gpt-5.5-pro</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>30</v>
+      </c>
+      <c r="H251" t="n">
+        <v>180</v>
+      </c>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H252" t="n">
+        <v>8</v>
+      </c>
+      <c r="I252" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="n">
+        <v>2</v>
+      </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="n">
+        <v>8</v>
+      </c>
+      <c r="H254" t="n">
+        <v>32</v>
+      </c>
+      <c r="I254" t="n">
+        <v>2</v>
+      </c>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="n">
+        <v>5</v>
+      </c>
+      <c r="H255" t="n">
+        <v>10</v>
+      </c>
+      <c r="I255" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="n">
+        <v>8</v>
+      </c>
+      <c r="H256" t="n">
+        <v>30</v>
+      </c>
+      <c r="I256" t="n">
+        <v>2</v>
+      </c>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="n">
+        <v>5</v>
+      </c>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>o3-deep-research</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="n">
+        <v>5</v>
+      </c>
+      <c r="H258" t="n">
+        <v>20</v>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>all-fine-tuned-models-will-remain-available-for-inference-until-their-base-models-are-deprecated-the-full-timeline-is-here</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="n">
+        <v>4</v>
+      </c>
+      <c r="H259" t="n">
+        <v>16</v>
+      </c>
+      <c r="I259" t="n">
+        <v>1</v>
+      </c>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>Specialized models | Finetuning | OpenAI is winding down the fine-tuning platform. The platform is no longer accessible to new users, but existing users of the fine-tuning platform will be able to create training jobs for the coming months. | All fine-tuned models will remain available for inference until their base models are deprecated. The full timeline is here .</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16 with data sharing</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>all-fine-tuned-models-will-remain-available-for-inference-until-their-base-models-are-deprecated-the-full-timeline-is-here</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="n">
+        <v>2</v>
+      </c>
+      <c r="H260" t="n">
+        <v>8</v>
+      </c>
+      <c r="I260" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Specialized models | Finetuning | OpenAI is winding down the fine-tuning platform. The platform is no longer accessible to new users, but existing users of the fine-tuning platform will be able to create training jobs for the coming months. | All fine-tuned models will remain available for inference until their base models are deprecated. The full timeline is here .</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>o4-mini-deep-research</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="n">
+        <v>1</v>
+      </c>
+      <c r="H261" t="n">
+        <v>4</v>
+      </c>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>grok-4.20-0309-non-reasoning</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H262" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I262" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>grok-4.20-0309-reasoning</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H263" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I263" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>grok-4.20-multi-agent-0309</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H264" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I264" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J264" t="inlineStr"/>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>grok-4.3</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H265" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I265" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>grok-build-0.1</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>256k</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>1</v>
+      </c>
+      <c r="H266" t="n">
+        <v>2</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>generated_at</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>records_count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>status_rows</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>partial_run</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:09:54+00:00</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>113</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/llm_costs.xlsx
+++ b/data/llm_costs.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="prices_current" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_status" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vendor_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="price_history" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="run_metadata" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="prices_current" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="source_status" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="vendor_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="price_history" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="run_metadata" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,14 +429,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q114"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
@@ -446,8 +446,8 @@
     <col width="38" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="38" customWidth="1" min="15" max="15"/>
+    <col width="39" customWidth="1" min="16" max="16"/>
     <col width="27" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
@@ -601,7 +601,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-24T16:09:54+00:00</t>
+          <t>2026-05-24T16:22:02+00:00</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-24T16:09:54+00:00</t>
+          <t>2026-05-24T16:22:02+00:00</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-24T16:09:54+00:00</t>
+          <t>2026-05-24T16:22:02+00:00</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-24T16:09:54+00:00</t>
+          <t>2026-05-24T16:22:02+00:00</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-24T16:09:54+00:00</t>
+          <t>2026-05-24T16:22:02+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-24T16:09:54+00:00</t>
+          <t>2026-05-24T16:22:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-24T16:09:54+00:00</t>
+          <t>2026-05-24T16:22:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-24T16:09:54+00:00</t>
+          <t>2026-05-24T16:22:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1137,6653 +1137,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Gemini 2.0 Flash</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Gemini 2.0 Flash</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Gemini 2.0 Flash</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Gemini 2.0 Flash</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Gemini 2.0 Flash-Lite</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Gemini 2.0 Flash-Lite</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>flex</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>flex</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>$0.054 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>$0.054 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash Image 🍌</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>text / image</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash Image 🍌</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>flex</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>text / image</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash Image 🍌</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>text / image</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash Image 🍌</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>text / image</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash Preview TTS</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash Preview TTS</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Pro</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="n">
-        <v>5</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Pro</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>flex</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="n">
-        <v>5</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Pro</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="n">
-        <v>18</v>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>$0.225, prompts &lt;= 200k tokens $0.45, prompts &gt; 200k $8.10 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Pro</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="n">
-        <v>10</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Pro Preview TTS</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Pro Preview TTS</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Gemini 3 Flash Preview</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Gemini 3 Flash Preview</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Gemini 3 Flash Preview</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>flex</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Gemini 3 Flash Preview</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>flex</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
-        <v>1</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Gemini 3 Flash Preview</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H41" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>$0.09 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Gemini 3 Flash Preview</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H42" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>$0.09 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Gemini 3 Flash Preview</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="n">
-        <v>1</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>$0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Gemini 3 Flash Preview</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H44" t="n">
-        <v>3</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="n">
-        <v>1</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>$0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Gemini 3 Pro Image Preview 🍌</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Gemini 3 Pro Image Preview 🍌</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Gemini 3 Pro Image Preview 🍌</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>flex</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Gemini 3 Pro Image Preview 🍌</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>flex</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Gemini 3 Pro Image Preview 🍌</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>text/image</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Gemini 3 Pro Image Preview 🍌</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>text/image</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="n">
-        <v>2</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash Image Preview 🍌</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>text, image</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash Image Preview 🍌</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>text/image</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash TTS Preview</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash TTS Preview</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>flex</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>flex</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H59" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H60" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H61" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H62" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="n">
-        <v>1</v>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite Preview</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite Preview</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite Preview</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>flex</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite Preview</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>flex</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite Preview</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H67" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite Preview</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H68" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite Preview</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H69" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="n">
-        <v>1</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite Preview</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H70" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="n">
-        <v>1</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Pro Preview</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="n">
-        <v>6</v>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Pro Preview</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>flex</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="n">
-        <v>6</v>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Pro Preview</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>$0.36, prompts &lt;= 200k tokens $0.72, prompts &gt; 200k $8.10 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Pro Preview</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="n">
-        <v>12</v>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Gemini 3.5 Flash</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H75" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="n">
-        <v>1</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>$0.075 $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Gemini 3.5 Flash</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>flex</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H76" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="n">
-        <v>1</v>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>$0.08 $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Gemini 3.5 Flash</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H77" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="n">
-        <v>1</v>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>$0.27 $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Gemini 3.5 Flash</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H78" t="n">
-        <v>9</v>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="n">
-        <v>1</v>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>$0.15 $1.00 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Gemini Embedding</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>embedding</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Gemini Embedding</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>embedding</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Gemini Robotics-ER 1.6 Preview</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>robotics-er</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Gemini Robotics-ER 1.6 Preview</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>robotics-er</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H82" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Gemini Robotics-ER 1.6 Preview</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>robotics-er</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>audio</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="n">
-        <v>2</v>
-      </c>
-      <c r="H83" t="n">
-        <v>5</v>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Gemini Robotics-ER 1.6 Preview</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>robotics-er</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>text / image / video</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" t="n">
-        <v>5</v>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>chat-latest</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>chat</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>specialized-models</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="n">
-        <v>5</v>
-      </c>
-      <c r="H85" t="n">
-        <v>30</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>computer-use-preview</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>computer</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>specialized-models</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H86" t="n">
-        <v>6</v>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>gpt-4o-mini-transcribe</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>prices-per-1m-tokens-unless-noted</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H87" t="n">
-        <v>5</v>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>Image generation models | Video generation models | Transcription models | Prices per 1M tokens unless noted.</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>gpt-4o-transcribe</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>prices-per-1m-tokens-unless-noted</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H88" t="n">
-        <v>10</v>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>Image generation models | Video generation models | Transcription models | Prices per 1M tokens unless noted.</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>gpt-5.3-codex</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>specialized-models</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="H89" t="n">
-        <v>14</v>
-      </c>
-      <c r="I89" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>gpt-5.4</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>flagship-models-long-context</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="G90" t="n">
-        <v>5</v>
-      </c>
-      <c r="H90" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>Going live | Legacy APIs | Resources | Flagship models</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>gpt-5.4</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>flagship-models-short-context</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="G91" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H91" t="n">
-        <v>15</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>Going live | Legacy APIs | Resources | Flagship models</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>gpt-5.4-mini</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>flagship-models-short-context</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="G92" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H92" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>Going live | Legacy APIs | Resources | Flagship models</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>gpt-5.4-nano</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>flagship-models-short-context</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H93" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>Going live | Legacy APIs | Resources | Flagship models</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>gpt-5.4-pro</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>flagship-models-long-context</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
-        <v>60</v>
-      </c>
-      <c r="H94" t="n">
-        <v>270</v>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>Going live | Legacy APIs | Resources | Flagship models</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>gpt-5.4-pro</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>flagship-models-short-context</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="G95" t="n">
-        <v>30</v>
-      </c>
-      <c r="H95" t="n">
-        <v>180</v>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>Going live | Legacy APIs | Resources | Flagship models</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>gpt-5.5</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>flagship-models-long-context</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="G96" t="n">
-        <v>10</v>
-      </c>
-      <c r="H96" t="n">
-        <v>45</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>Going live | Legacy APIs | Resources | Flagship models</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>gpt-5.5</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>flagship-models-short-context</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="G97" t="n">
-        <v>5</v>
-      </c>
-      <c r="H97" t="n">
-        <v>30</v>
-      </c>
-      <c r="I97" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>Going live | Legacy APIs | Resources | Flagship models</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>gpt-5.5-pro</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>flagship-models-long-context</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="G98" t="n">
-        <v>60</v>
-      </c>
-      <c r="H98" t="n">
-        <v>270</v>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>Going live | Legacy APIs | Resources | Flagship models</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>gpt-5.5-pro</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>flagship-models-short-context</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="G99" t="n">
-        <v>30</v>
-      </c>
-      <c r="H99" t="n">
-        <v>180</v>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>Going live | Legacy APIs | Resources | Flagship models</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>gpt-image-1-mini</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>image-generation-models</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H100" t="n">
-        <v>8</v>
-      </c>
-      <c r="I100" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>gpt-image-1-mini</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>image-generation-models</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="n">
-        <v>2</v>
-      </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>gpt-image-1.5</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>image-generation-models</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="n">
-        <v>8</v>
-      </c>
-      <c r="H102" t="n">
-        <v>32</v>
-      </c>
-      <c r="I102" t="n">
-        <v>2</v>
-      </c>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>gpt-image-1.5</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>image-generation-models</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="n">
-        <v>5</v>
-      </c>
-      <c r="H103" t="n">
-        <v>10</v>
-      </c>
-      <c r="I103" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>gpt-image-2</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>image-generation-models</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="n">
-        <v>8</v>
-      </c>
-      <c r="H104" t="n">
-        <v>30</v>
-      </c>
-      <c r="I104" t="n">
-        <v>2</v>
-      </c>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>gpt-image-2</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>gpt</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>image-generation-models</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="n">
-        <v>5</v>
-      </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>o3-deep-research</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>o3</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>specialized-models</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="n">
-        <v>5</v>
-      </c>
-      <c r="H106" t="n">
-        <v>20</v>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>o4-mini-2025-04-16</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>o4</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>all-fine-tuned-models-will-remain-available-for-inference-until-their-base-models-are-deprecated-the-full-timeline-is-here</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="n">
-        <v>4</v>
-      </c>
-      <c r="H107" t="n">
-        <v>16</v>
-      </c>
-      <c r="I107" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>Specialized models | Finetuning | OpenAI is winding down the fine-tuning platform. The platform is no longer accessible to new users, but existing users of the fine-tuning platform will be able to create training jobs for the coming months. | All fine-tuned models will remain available for inference until their base models are deprecated. The full timeline is here .</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>o4-mini-2025-04-16 with data sharing</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>o4</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>all-fine-tuned-models-will-remain-available-for-inference-until-their-base-models-are-deprecated-the-full-timeline-is-here</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="n">
-        <v>2</v>
-      </c>
-      <c r="H108" t="n">
-        <v>8</v>
-      </c>
-      <c r="I108" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>Specialized models | Finetuning | OpenAI is winding down the fine-tuning platform. The platform is no longer accessible to new users, but existing users of the fine-tuning platform will be able to create training jobs for the coming months. | All fine-tuned models will remain available for inference until their base models are deprecated. The full timeline is here .</t>
-        </is>
-      </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>o4-mini-deep-research</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>o4</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>specialized-models</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="n">
-        <v>1</v>
-      </c>
-      <c r="H109" t="n">
-        <v>4</v>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
-        </is>
-      </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>xAI</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>grok-4.20-0309-non-reasoning</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>grok</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
-      <c r="G110" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H110" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I110" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>Official xAI Chat API pricing.</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>https://docs.x.ai/docs/pricing</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>xAI</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>grok-4.20-0309-reasoning</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>grok</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
-      <c r="G111" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H111" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I111" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>Official xAI Chat API pricing.</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>https://docs.x.ai/docs/pricing</t>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>xAI</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>grok-4.20-multi-agent-0309</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>grok</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
-      <c r="G112" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H112" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I112" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>Official xAI Chat API pricing.</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>https://docs.x.ai/docs/pricing</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>xAI</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>grok-4.3</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>grok</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
-      <c r="G113" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H113" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I113" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>Official xAI Chat API pricing.</t>
-        </is>
-      </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>https://docs.x.ai/docs/pricing</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>xAI</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>grok-build-0.1</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>grok</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>256k</t>
-        </is>
-      </c>
-      <c r="G114" t="n">
-        <v>1</v>
-      </c>
-      <c r="H114" t="n">
-        <v>2</v>
-      </c>
-      <c r="I114" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>USD per 1M tokens</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>Official xAI Chat API pricing.</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>https://docs.x.ai/docs/pricing</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>2026-05-24T16:09:54+00:00</t>
+          <t>2026-05-24T16:22:02+00:00</t>
         </is>
       </c>
     </row>
@@ -7876,7 +1230,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-24T16:09:54+00:00</t>
+          <t>2026-05-24T16:22:02+00:00</t>
         </is>
       </c>
     </row>
@@ -7909,7 +1263,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-24T16:09:54+00:00</t>
+          <t>2026-05-24T16:22:02+00:00</t>
         </is>
       </c>
     </row>
@@ -7921,7 +1275,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C4" t="b">
@@ -7934,15 +1288,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Parsed Gemini API pricing tables from ai.google.dev.</t>
+          <t>ERROR: lxml not found, please install it</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-24T16:09:54+00:00</t>
+          <t>2026-05-24T16:22:02+00:00</t>
         </is>
       </c>
     </row>
@@ -7975,7 +1329,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-24T16:09:54+00:00</t>
+          <t>2026-05-24T16:22:02+00:00</t>
         </is>
       </c>
     </row>
@@ -7987,7 +1341,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C6" t="b">
@@ -8000,15 +1354,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Parsed official OpenAI pricing tables from developers.openai.com.</t>
+          <t>ERROR: lxml not found, please install it</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-24T16:09:54+00:00</t>
+          <t>2026-05-24T16:22:02+00:00</t>
         </is>
       </c>
     </row>
@@ -8020,7 +1374,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C7" t="b">
@@ -8033,15 +1387,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Parsed xAI Chat API token pricing from docs.x.ai.</t>
+          <t>ERROR: lxml not found, please install it</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-24T16:09:54+00:00</t>
+          <t>2026-05-24T16:22:02+00:00</t>
         </is>
       </c>
     </row>
@@ -8056,7 +1410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8121,72 +1475,6 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F3" t="n">
-        <v>21.6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>18</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>60</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F4" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>xAI</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8198,7 +1486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q266"/>
+  <dimension ref="A1:Q275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -25396,6 +18684,609 @@
         </is>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Claude Haiku 4.5</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>haiku</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="n">
+        <v>1</v>
+      </c>
+      <c r="H267" t="n">
+        <v>5</v>
+      </c>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K267" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:22:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Claude Opus 4</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="n">
+        <v>15</v>
+      </c>
+      <c r="H268" t="n">
+        <v>75</v>
+      </c>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="K268" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:22:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.1</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="n">
+        <v>15</v>
+      </c>
+      <c r="H269" t="n">
+        <v>75</v>
+      </c>
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="K269" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:22:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.5</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="n">
+        <v>5</v>
+      </c>
+      <c r="H270" t="n">
+        <v>25</v>
+      </c>
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K270" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:22:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.6</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="n">
+        <v>5</v>
+      </c>
+      <c r="H271" t="n">
+        <v>25</v>
+      </c>
+      <c r="I271" t="inlineStr"/>
+      <c r="J271" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K271" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:22:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.7</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="n">
+        <v>5</v>
+      </c>
+      <c r="H272" t="n">
+        <v>25</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K272" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:22:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="n">
+        <v>3</v>
+      </c>
+      <c r="H273" t="n">
+        <v>15</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K273" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:22:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.5</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="n">
+        <v>3</v>
+      </c>
+      <c r="H274" t="n">
+        <v>15</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K274" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:22:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="n">
+        <v>3</v>
+      </c>
+      <c r="H275" t="n">
+        <v>15</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K275" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>2026-05-24T16:22:02+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25441,17 +19332,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-24T16:09:54+00:00</t>
+          <t>2026-05-24T16:22:02+00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/llm_costs.xlsx
+++ b/data/llm_costs.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7633,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -7891,7 +7891,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q397"/>
+  <dimension ref="A1:Q519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -34410,6 +34410,7836 @@
         </is>
       </c>
     </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Claude Haiku 4.5</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>haiku</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="n">
+        <v>1</v>
+      </c>
+      <c r="H398" t="n">
+        <v>5</v>
+      </c>
+      <c r="I398" t="inlineStr"/>
+      <c r="J398" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K398" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L398" t="inlineStr"/>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Claude Opus 4</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="n">
+        <v>15</v>
+      </c>
+      <c r="H399" t="n">
+        <v>75</v>
+      </c>
+      <c r="I399" t="inlineStr"/>
+      <c r="J399" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="K399" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L399" t="inlineStr"/>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.1</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="n">
+        <v>15</v>
+      </c>
+      <c r="H400" t="n">
+        <v>75</v>
+      </c>
+      <c r="I400" t="inlineStr"/>
+      <c r="J400" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="K400" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L400" t="inlineStr"/>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.5</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="n">
+        <v>5</v>
+      </c>
+      <c r="H401" t="n">
+        <v>25</v>
+      </c>
+      <c r="I401" t="inlineStr"/>
+      <c r="J401" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K401" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.6</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="n">
+        <v>5</v>
+      </c>
+      <c r="H402" t="n">
+        <v>25</v>
+      </c>
+      <c r="I402" t="inlineStr"/>
+      <c r="J402" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K402" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.7</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="n">
+        <v>5</v>
+      </c>
+      <c r="H403" t="n">
+        <v>25</v>
+      </c>
+      <c r="I403" t="inlineStr"/>
+      <c r="J403" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K403" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="n">
+        <v>3</v>
+      </c>
+      <c r="H404" t="n">
+        <v>15</v>
+      </c>
+      <c r="I404" t="inlineStr"/>
+      <c r="J404" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K404" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.5</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="n">
+        <v>3</v>
+      </c>
+      <c r="H405" t="n">
+        <v>15</v>
+      </c>
+      <c r="I405" t="inlineStr"/>
+      <c r="J405" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K405" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="n">
+        <v>3</v>
+      </c>
+      <c r="H406" t="n">
+        <v>15</v>
+      </c>
+      <c r="I406" t="inlineStr"/>
+      <c r="J406" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K406" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L406" t="inlineStr"/>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H407" t="inlineStr"/>
+      <c r="I407" t="inlineStr"/>
+      <c r="J407" t="inlineStr"/>
+      <c r="K407" t="inlineStr"/>
+      <c r="L407" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H408" t="inlineStr"/>
+      <c r="I408" t="inlineStr"/>
+      <c r="J408" t="inlineStr"/>
+      <c r="K408" t="inlineStr"/>
+      <c r="L408" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H409" t="inlineStr"/>
+      <c r="I409" t="inlineStr"/>
+      <c r="J409" t="inlineStr"/>
+      <c r="K409" t="inlineStr"/>
+      <c r="L409" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H410" t="inlineStr"/>
+      <c r="I410" t="inlineStr"/>
+      <c r="J410" t="inlineStr"/>
+      <c r="K410" t="inlineStr"/>
+      <c r="L410" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="H411" t="inlineStr"/>
+      <c r="I411" t="inlineStr"/>
+      <c r="J411" t="inlineStr"/>
+      <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H412" t="inlineStr"/>
+      <c r="I412" t="inlineStr"/>
+      <c r="J412" t="inlineStr"/>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H413" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I413" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="n">
+        <v>1</v>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H414" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I414" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="n">
+        <v>1</v>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H415" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I415" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="n">
+        <v>1</v>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H416" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I416" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J416" t="inlineStr"/>
+      <c r="K416" t="inlineStr"/>
+      <c r="L416" t="n">
+        <v>1</v>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H417" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I417" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J417" t="inlineStr"/>
+      <c r="K417" t="inlineStr"/>
+      <c r="L417" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>$0.054 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H418" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I418" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J418" t="inlineStr"/>
+      <c r="K418" t="inlineStr"/>
+      <c r="L418" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>$0.054 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="n">
+        <v>1</v>
+      </c>
+      <c r="H419" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I419" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J419" t="inlineStr"/>
+      <c r="K419" t="inlineStr"/>
+      <c r="L419" t="n">
+        <v>1</v>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H420" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I420" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J420" t="inlineStr"/>
+      <c r="K420" t="inlineStr"/>
+      <c r="L420" t="n">
+        <v>1</v>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H421" t="inlineStr"/>
+      <c r="I421" t="inlineStr"/>
+      <c r="J421" t="inlineStr"/>
+      <c r="K421" t="inlineStr"/>
+      <c r="L421" t="inlineStr"/>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr"/>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H422" t="inlineStr"/>
+      <c r="I422" t="inlineStr"/>
+      <c r="J422" t="inlineStr"/>
+      <c r="K422" t="inlineStr"/>
+      <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr"/>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H423" t="inlineStr"/>
+      <c r="I423" t="inlineStr"/>
+      <c r="J423" t="inlineStr"/>
+      <c r="K423" t="inlineStr"/>
+      <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr"/>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H424" t="inlineStr"/>
+      <c r="I424" t="inlineStr"/>
+      <c r="J424" t="inlineStr"/>
+      <c r="K424" t="inlineStr"/>
+      <c r="L424" t="inlineStr"/>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr"/>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Preview TTS</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H425" t="inlineStr"/>
+      <c r="I425" t="inlineStr"/>
+      <c r="J425" t="inlineStr"/>
+      <c r="K425" t="inlineStr"/>
+      <c r="L425" t="inlineStr"/>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr"/>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Preview TTS</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H426" t="inlineStr"/>
+      <c r="I426" t="inlineStr"/>
+      <c r="J426" t="inlineStr"/>
+      <c r="K426" t="inlineStr"/>
+      <c r="L426" t="inlineStr"/>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr"/>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="n">
+        <v>5</v>
+      </c>
+      <c r="I427" t="inlineStr"/>
+      <c r="J427" t="inlineStr"/>
+      <c r="K427" t="inlineStr"/>
+      <c r="L427" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="n">
+        <v>5</v>
+      </c>
+      <c r="I428" t="inlineStr"/>
+      <c r="J428" t="inlineStr"/>
+      <c r="K428" t="inlineStr"/>
+      <c r="L428" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="n">
+        <v>18</v>
+      </c>
+      <c r="I429" t="inlineStr"/>
+      <c r="J429" t="inlineStr"/>
+      <c r="K429" t="inlineStr"/>
+      <c r="L429" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>$0.225, prompts &lt;= 200k tokens $0.45, prompts &gt; 200k $8.10 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr"/>
+      <c r="H430" t="n">
+        <v>10</v>
+      </c>
+      <c r="I430" t="inlineStr"/>
+      <c r="J430" t="inlineStr"/>
+      <c r="K430" t="inlineStr"/>
+      <c r="L430" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro Preview TTS</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H431" t="inlineStr"/>
+      <c r="I431" t="inlineStr"/>
+      <c r="J431" t="inlineStr"/>
+      <c r="K431" t="inlineStr"/>
+      <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr"/>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro Preview TTS</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="n">
+        <v>1</v>
+      </c>
+      <c r="H432" t="inlineStr"/>
+      <c r="I432" t="inlineStr"/>
+      <c r="J432" t="inlineStr"/>
+      <c r="K432" t="inlineStr"/>
+      <c r="L432" t="inlineStr"/>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr"/>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H433" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I433" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J433" t="inlineStr"/>
+      <c r="K433" t="inlineStr"/>
+      <c r="L433" t="n">
+        <v>1</v>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H434" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I434" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="inlineStr"/>
+      <c r="L434" t="n">
+        <v>1</v>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H435" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I435" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J435" t="inlineStr"/>
+      <c r="K435" t="inlineStr"/>
+      <c r="L435" t="n">
+        <v>1</v>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H436" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I436" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J436" t="inlineStr"/>
+      <c r="K436" t="inlineStr"/>
+      <c r="L436" t="n">
+        <v>1</v>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H437" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I437" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J437" t="inlineStr"/>
+      <c r="K437" t="inlineStr"/>
+      <c r="L437" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>$0.09 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H438" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I438" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J438" t="inlineStr"/>
+      <c r="K438" t="inlineStr"/>
+      <c r="L438" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>$0.09 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="n">
+        <v>1</v>
+      </c>
+      <c r="H439" t="n">
+        <v>3</v>
+      </c>
+      <c r="I439" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J439" t="inlineStr"/>
+      <c r="K439" t="inlineStr"/>
+      <c r="L439" t="n">
+        <v>1</v>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>$0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H440" t="n">
+        <v>3</v>
+      </c>
+      <c r="I440" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J440" t="inlineStr"/>
+      <c r="K440" t="inlineStr"/>
+      <c r="L440" t="n">
+        <v>1</v>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>$0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H441" t="inlineStr"/>
+      <c r="I441" t="inlineStr"/>
+      <c r="J441" t="inlineStr"/>
+      <c r="K441" t="inlineStr"/>
+      <c r="L441" t="inlineStr"/>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr"/>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="n">
+        <v>1</v>
+      </c>
+      <c r="H442" t="inlineStr"/>
+      <c r="I442" t="inlineStr"/>
+      <c r="J442" t="inlineStr"/>
+      <c r="K442" t="inlineStr"/>
+      <c r="L442" t="inlineStr"/>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr"/>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H443" t="inlineStr"/>
+      <c r="I443" t="inlineStr"/>
+      <c r="J443" t="inlineStr"/>
+      <c r="K443" t="inlineStr"/>
+      <c r="L443" t="inlineStr"/>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr"/>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="n">
+        <v>1</v>
+      </c>
+      <c r="H444" t="inlineStr"/>
+      <c r="I444" t="inlineStr"/>
+      <c r="J444" t="inlineStr"/>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr"/>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H445" t="inlineStr"/>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
+      <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr"/>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr"/>
+      <c r="G446" t="n">
+        <v>2</v>
+      </c>
+      <c r="H446" t="inlineStr"/>
+      <c r="I446" t="inlineStr"/>
+      <c r="J446" t="inlineStr"/>
+      <c r="K446" t="inlineStr"/>
+      <c r="L446" t="inlineStr"/>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr"/>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>text, image</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr"/>
+      <c r="G447" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H447" t="inlineStr"/>
+      <c r="I447" t="inlineStr"/>
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="inlineStr"/>
+      <c r="L447" t="inlineStr"/>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr"/>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H448" t="inlineStr"/>
+      <c r="I448" t="inlineStr"/>
+      <c r="J448" t="inlineStr"/>
+      <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr"/>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash TTS Preview</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H449" t="inlineStr"/>
+      <c r="I449" t="inlineStr"/>
+      <c r="J449" t="inlineStr"/>
+      <c r="K449" t="inlineStr"/>
+      <c r="L449" t="inlineStr"/>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr"/>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash TTS Preview</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="n">
+        <v>1</v>
+      </c>
+      <c r="H450" t="inlineStr"/>
+      <c r="I450" t="inlineStr"/>
+      <c r="J450" t="inlineStr"/>
+      <c r="K450" t="inlineStr"/>
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr"/>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr"/>
+      <c r="G451" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H451" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I451" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J451" t="inlineStr"/>
+      <c r="K451" t="inlineStr"/>
+      <c r="L451" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr"/>
+      <c r="G452" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H452" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I452" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J452" t="inlineStr"/>
+      <c r="K452" t="inlineStr"/>
+      <c r="L452" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr"/>
+      <c r="G453" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H453" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I453" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J453" t="inlineStr"/>
+      <c r="K453" t="inlineStr"/>
+      <c r="L453" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr"/>
+      <c r="G454" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H454" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I454" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J454" t="inlineStr"/>
+      <c r="K454" t="inlineStr"/>
+      <c r="L454" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr"/>
+      <c r="G455" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H455" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I455" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J455" t="inlineStr"/>
+      <c r="K455" t="inlineStr"/>
+      <c r="L455" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr"/>
+      <c r="G456" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H456" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I456" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J456" t="inlineStr"/>
+      <c r="K456" t="inlineStr"/>
+      <c r="L456" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr"/>
+      <c r="G457" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H457" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I457" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J457" t="inlineStr"/>
+      <c r="K457" t="inlineStr"/>
+      <c r="L457" t="n">
+        <v>1</v>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr"/>
+      <c r="G458" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H458" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I458" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J458" t="inlineStr"/>
+      <c r="K458" t="inlineStr"/>
+      <c r="L458" t="n">
+        <v>1</v>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr"/>
+      <c r="G459" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H459" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I459" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J459" t="inlineStr"/>
+      <c r="K459" t="inlineStr"/>
+      <c r="L459" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr"/>
+      <c r="G460" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H460" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I460" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J460" t="inlineStr"/>
+      <c r="K460" t="inlineStr"/>
+      <c r="L460" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr"/>
+      <c r="G461" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H461" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I461" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J461" t="inlineStr"/>
+      <c r="K461" t="inlineStr"/>
+      <c r="L461" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr"/>
+      <c r="G462" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H462" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I462" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J462" t="inlineStr"/>
+      <c r="K462" t="inlineStr"/>
+      <c r="L462" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr"/>
+      <c r="G463" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H463" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I463" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J463" t="inlineStr"/>
+      <c r="K463" t="inlineStr"/>
+      <c r="L463" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr"/>
+      <c r="G464" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H464" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I464" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J464" t="inlineStr"/>
+      <c r="K464" t="inlineStr"/>
+      <c r="L464" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr"/>
+      <c r="G465" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H465" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I465" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J465" t="inlineStr"/>
+      <c r="K465" t="inlineStr"/>
+      <c r="L465" t="n">
+        <v>1</v>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr"/>
+      <c r="G466" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H466" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I466" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J466" t="inlineStr"/>
+      <c r="K466" t="inlineStr"/>
+      <c r="L466" t="n">
+        <v>1</v>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr"/>
+      <c r="G467" t="inlineStr"/>
+      <c r="H467" t="n">
+        <v>6</v>
+      </c>
+      <c r="I467" t="inlineStr"/>
+      <c r="J467" t="inlineStr"/>
+      <c r="K467" t="inlineStr"/>
+      <c r="L467" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr"/>
+      <c r="G468" t="inlineStr"/>
+      <c r="H468" t="n">
+        <v>6</v>
+      </c>
+      <c r="I468" t="inlineStr"/>
+      <c r="J468" t="inlineStr"/>
+      <c r="K468" t="inlineStr"/>
+      <c r="L468" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr"/>
+      <c r="G469" t="inlineStr"/>
+      <c r="H469" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I469" t="inlineStr"/>
+      <c r="J469" t="inlineStr"/>
+      <c r="K469" t="inlineStr"/>
+      <c r="L469" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>$0.36, prompts &lt;= 200k tokens $0.72, prompts &gt; 200k $8.10 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr"/>
+      <c r="G470" t="inlineStr"/>
+      <c r="H470" t="n">
+        <v>12</v>
+      </c>
+      <c r="I470" t="inlineStr"/>
+      <c r="J470" t="inlineStr"/>
+      <c r="K470" t="inlineStr"/>
+      <c r="L470" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr"/>
+      <c r="G471" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H471" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I471" t="inlineStr"/>
+      <c r="J471" t="inlineStr"/>
+      <c r="K471" t="inlineStr"/>
+      <c r="L471" t="n">
+        <v>1</v>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>$0.075 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr"/>
+      <c r="G472" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H472" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I472" t="inlineStr"/>
+      <c r="J472" t="inlineStr"/>
+      <c r="K472" t="inlineStr"/>
+      <c r="L472" t="n">
+        <v>1</v>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>$0.08 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr"/>
+      <c r="G473" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H473" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I473" t="inlineStr"/>
+      <c r="J473" t="inlineStr"/>
+      <c r="K473" t="inlineStr"/>
+      <c r="L473" t="n">
+        <v>1</v>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>$0.27 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr"/>
+      <c r="G474" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H474" t="n">
+        <v>9</v>
+      </c>
+      <c r="I474" t="inlineStr"/>
+      <c r="J474" t="inlineStr"/>
+      <c r="K474" t="inlineStr"/>
+      <c r="L474" t="n">
+        <v>1</v>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>$0.15 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Gemini Embedding</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>embedding</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr"/>
+      <c r="G475" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H475" t="inlineStr"/>
+      <c r="I475" t="inlineStr"/>
+      <c r="J475" t="inlineStr"/>
+      <c r="K475" t="inlineStr"/>
+      <c r="L475" t="inlineStr"/>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr"/>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Gemini Embedding</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>embedding</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr"/>
+      <c r="G476" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H476" t="inlineStr"/>
+      <c r="I476" t="inlineStr"/>
+      <c r="J476" t="inlineStr"/>
+      <c r="K476" t="inlineStr"/>
+      <c r="L476" t="inlineStr"/>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr"/>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr"/>
+      <c r="G477" t="n">
+        <v>1</v>
+      </c>
+      <c r="H477" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I477" t="inlineStr"/>
+      <c r="J477" t="inlineStr"/>
+      <c r="K477" t="inlineStr"/>
+      <c r="L477" t="inlineStr"/>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr"/>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr"/>
+      <c r="G478" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H478" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I478" t="inlineStr"/>
+      <c r="J478" t="inlineStr"/>
+      <c r="K478" t="inlineStr"/>
+      <c r="L478" t="inlineStr"/>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr"/>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="n">
+        <v>2</v>
+      </c>
+      <c r="H479" t="n">
+        <v>5</v>
+      </c>
+      <c r="I479" t="inlineStr"/>
+      <c r="J479" t="inlineStr"/>
+      <c r="K479" t="inlineStr"/>
+      <c r="L479" t="inlineStr"/>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr"/>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="n">
+        <v>1</v>
+      </c>
+      <c r="H480" t="n">
+        <v>5</v>
+      </c>
+      <c r="I480" t="inlineStr"/>
+      <c r="J480" t="inlineStr"/>
+      <c r="K480" t="inlineStr"/>
+      <c r="L480" t="inlineStr"/>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr"/>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>chat-latest</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>chat</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>tools</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="n">
+        <v>5</v>
+      </c>
+      <c r="H481" t="n">
+        <v>30</v>
+      </c>
+      <c r="I481" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J481" t="inlineStr"/>
+      <c r="K481" t="inlineStr"/>
+      <c r="L481" t="inlineStr"/>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>Video generation models | Transcription models | Prices per 1M tokens unless noted. | Tools</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>computer-use-preview</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>computer</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H482" t="n">
+        <v>6</v>
+      </c>
+      <c r="I482" t="inlineStr"/>
+      <c r="J482" t="inlineStr"/>
+      <c r="K482" t="inlineStr"/>
+      <c r="L482" t="inlineStr"/>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini-transcribe</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>video-generation-models</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H483" t="n">
+        <v>5</v>
+      </c>
+      <c r="I483" t="inlineStr"/>
+      <c r="J483" t="inlineStr"/>
+      <c r="K483" t="inlineStr"/>
+      <c r="L483" t="inlineStr"/>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models | Video generation models</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>gpt-4o-transcribe</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>video-generation-models</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H484" t="n">
+        <v>10</v>
+      </c>
+      <c r="I484" t="inlineStr"/>
+      <c r="J484" t="inlineStr"/>
+      <c r="K484" t="inlineStr"/>
+      <c r="L484" t="inlineStr"/>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models | Video generation models</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>gpt-5.3-codex</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr"/>
+      <c r="G485" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H485" t="n">
+        <v>28</v>
+      </c>
+      <c r="I485" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J485" t="inlineStr"/>
+      <c r="K485" t="inlineStr"/>
+      <c r="L485" t="inlineStr"/>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>gpt-5.3-codex</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>tools</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H486" t="n">
+        <v>14</v>
+      </c>
+      <c r="I486" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="J486" t="inlineStr"/>
+      <c r="K486" t="inlineStr"/>
+      <c r="L486" t="inlineStr"/>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>Video generation models | Transcription models | Prices per 1M tokens unless noted. | Tools</t>
+        </is>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G487" t="n">
+        <v>5</v>
+      </c>
+      <c r="H487" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I487" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J487" t="inlineStr"/>
+      <c r="K487" t="inlineStr"/>
+      <c r="L487" t="inlineStr"/>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G488" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H488" t="n">
+        <v>15</v>
+      </c>
+      <c r="I488" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J488" t="inlineStr"/>
+      <c r="K488" t="inlineStr"/>
+      <c r="L488" t="inlineStr"/>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>gpt-5.4-mini</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G489" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H489" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I489" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J489" t="inlineStr"/>
+      <c r="K489" t="inlineStr"/>
+      <c r="L489" t="inlineStr"/>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>gpt-5.4-nano</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G490" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H490" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I490" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J490" t="inlineStr"/>
+      <c r="K490" t="inlineStr"/>
+      <c r="L490" t="inlineStr"/>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>gpt-5.4-pro</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G491" t="n">
+        <v>60</v>
+      </c>
+      <c r="H491" t="n">
+        <v>270</v>
+      </c>
+      <c r="I491" t="inlineStr"/>
+      <c r="J491" t="inlineStr"/>
+      <c r="K491" t="inlineStr"/>
+      <c r="L491" t="inlineStr"/>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>gpt-5.4-pro</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G492" t="n">
+        <v>30</v>
+      </c>
+      <c r="H492" t="n">
+        <v>180</v>
+      </c>
+      <c r="I492" t="inlineStr"/>
+      <c r="J492" t="inlineStr"/>
+      <c r="K492" t="inlineStr"/>
+      <c r="L492" t="inlineStr"/>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G493" t="n">
+        <v>10</v>
+      </c>
+      <c r="H493" t="n">
+        <v>45</v>
+      </c>
+      <c r="I493" t="n">
+        <v>1</v>
+      </c>
+      <c r="J493" t="inlineStr"/>
+      <c r="K493" t="inlineStr"/>
+      <c r="L493" t="inlineStr"/>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G494" t="n">
+        <v>5</v>
+      </c>
+      <c r="H494" t="n">
+        <v>30</v>
+      </c>
+      <c r="I494" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J494" t="inlineStr"/>
+      <c r="K494" t="inlineStr"/>
+      <c r="L494" t="inlineStr"/>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>gpt-5.5-pro</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G495" t="n">
+        <v>60</v>
+      </c>
+      <c r="H495" t="n">
+        <v>270</v>
+      </c>
+      <c r="I495" t="inlineStr"/>
+      <c r="J495" t="inlineStr"/>
+      <c r="K495" t="inlineStr"/>
+      <c r="L495" t="inlineStr"/>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>gpt-5.5-pro</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G496" t="n">
+        <v>30</v>
+      </c>
+      <c r="H496" t="n">
+        <v>180</v>
+      </c>
+      <c r="I496" t="inlineStr"/>
+      <c r="J496" t="inlineStr"/>
+      <c r="K496" t="inlineStr"/>
+      <c r="L496" t="inlineStr"/>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr"/>
+      <c r="G497" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H497" t="n">
+        <v>4</v>
+      </c>
+      <c r="I497" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J497" t="inlineStr"/>
+      <c r="K497" t="inlineStr"/>
+      <c r="L497" t="inlineStr"/>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr"/>
+      <c r="G498" t="n">
+        <v>1</v>
+      </c>
+      <c r="H498" t="inlineStr"/>
+      <c r="I498" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J498" t="inlineStr"/>
+      <c r="K498" t="inlineStr"/>
+      <c r="L498" t="inlineStr"/>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr"/>
+      <c r="G499" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H499" t="n">
+        <v>8</v>
+      </c>
+      <c r="I499" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J499" t="inlineStr"/>
+      <c r="K499" t="inlineStr"/>
+      <c r="L499" t="inlineStr"/>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr"/>
+      <c r="G500" t="n">
+        <v>2</v>
+      </c>
+      <c r="H500" t="inlineStr"/>
+      <c r="I500" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J500" t="inlineStr"/>
+      <c r="K500" t="inlineStr"/>
+      <c r="L500" t="inlineStr"/>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr"/>
+      <c r="G501" t="n">
+        <v>4</v>
+      </c>
+      <c r="H501" t="n">
+        <v>16</v>
+      </c>
+      <c r="I501" t="n">
+        <v>1</v>
+      </c>
+      <c r="J501" t="inlineStr"/>
+      <c r="K501" t="inlineStr"/>
+      <c r="L501" t="inlineStr"/>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H502" t="n">
+        <v>5</v>
+      </c>
+      <c r="I502" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J502" t="inlineStr"/>
+      <c r="K502" t="inlineStr"/>
+      <c r="L502" t="inlineStr"/>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="n">
+        <v>8</v>
+      </c>
+      <c r="H503" t="n">
+        <v>32</v>
+      </c>
+      <c r="I503" t="n">
+        <v>2</v>
+      </c>
+      <c r="J503" t="inlineStr"/>
+      <c r="K503" t="inlineStr"/>
+      <c r="L503" t="inlineStr"/>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr"/>
+      <c r="G504" t="n">
+        <v>5</v>
+      </c>
+      <c r="H504" t="n">
+        <v>10</v>
+      </c>
+      <c r="I504" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J504" t="inlineStr"/>
+      <c r="K504" t="inlineStr"/>
+      <c r="L504" t="inlineStr"/>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr"/>
+      <c r="G505" t="n">
+        <v>4</v>
+      </c>
+      <c r="H505" t="n">
+        <v>15</v>
+      </c>
+      <c r="I505" t="n">
+        <v>1</v>
+      </c>
+      <c r="J505" t="inlineStr"/>
+      <c r="K505" t="inlineStr"/>
+      <c r="L505" t="inlineStr"/>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr"/>
+      <c r="G506" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H506" t="inlineStr"/>
+      <c r="I506" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="J506" t="inlineStr"/>
+      <c r="K506" t="inlineStr"/>
+      <c r="L506" t="inlineStr"/>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr"/>
+      <c r="G507" t="n">
+        <v>8</v>
+      </c>
+      <c r="H507" t="n">
+        <v>30</v>
+      </c>
+      <c r="I507" t="n">
+        <v>2</v>
+      </c>
+      <c r="J507" t="inlineStr"/>
+      <c r="K507" t="inlineStr"/>
+      <c r="L507" t="inlineStr"/>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr"/>
+      <c r="G508" t="n">
+        <v>5</v>
+      </c>
+      <c r="H508" t="inlineStr"/>
+      <c r="I508" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J508" t="inlineStr"/>
+      <c r="K508" t="inlineStr"/>
+      <c r="L508" t="inlineStr"/>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>o3-deep-research</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr"/>
+      <c r="G509" t="n">
+        <v>5</v>
+      </c>
+      <c r="H509" t="n">
+        <v>20</v>
+      </c>
+      <c r="I509" t="inlineStr"/>
+      <c r="J509" t="inlineStr"/>
+      <c r="K509" t="inlineStr"/>
+      <c r="L509" t="inlineStr"/>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>all-fine-tuned-models-will-remain-available-for-inference-until-their-base-models-are-deprecated-the-full-timeline-is-here</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr"/>
+      <c r="G510" t="n">
+        <v>2</v>
+      </c>
+      <c r="H510" t="n">
+        <v>8</v>
+      </c>
+      <c r="I510" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J510" t="inlineStr"/>
+      <c r="K510" t="inlineStr"/>
+      <c r="L510" t="inlineStr"/>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>Specialized models | Finetuning | OpenAI is winding down the fine-tuning platform. The platform is no longer accessible to new users, but existing users of the fine-tuning platform will be able to create training jobs for the coming months. | All fine-tuned models will remain available for inference until their base models are deprecated. The full timeline is here .</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr"/>
+      <c r="G511" t="n">
+        <v>4</v>
+      </c>
+      <c r="H511" t="n">
+        <v>16</v>
+      </c>
+      <c r="I511" t="n">
+        <v>1</v>
+      </c>
+      <c r="J511" t="inlineStr"/>
+      <c r="K511" t="inlineStr"/>
+      <c r="L511" t="inlineStr"/>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16 with data sharing</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>all-fine-tuned-models-will-remain-available-for-inference-until-their-base-models-are-deprecated-the-full-timeline-is-here</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr"/>
+      <c r="G512" t="n">
+        <v>1</v>
+      </c>
+      <c r="H512" t="n">
+        <v>4</v>
+      </c>
+      <c r="I512" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J512" t="inlineStr"/>
+      <c r="K512" t="inlineStr"/>
+      <c r="L512" t="inlineStr"/>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>Specialized models | Finetuning | OpenAI is winding down the fine-tuning platform. The platform is no longer accessible to new users, but existing users of the fine-tuning platform will be able to create training jobs for the coming months. | All fine-tuned models will remain available for inference until their base models are deprecated. The full timeline is here .</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16 with data sharing</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr"/>
+      <c r="G513" t="n">
+        <v>2</v>
+      </c>
+      <c r="H513" t="n">
+        <v>8</v>
+      </c>
+      <c r="I513" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J513" t="inlineStr"/>
+      <c r="K513" t="inlineStr"/>
+      <c r="L513" t="inlineStr"/>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>o4-mini-deep-research</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr"/>
+      <c r="G514" t="n">
+        <v>1</v>
+      </c>
+      <c r="H514" t="n">
+        <v>4</v>
+      </c>
+      <c r="I514" t="inlineStr"/>
+      <c r="J514" t="inlineStr"/>
+      <c r="K514" t="inlineStr"/>
+      <c r="L514" t="inlineStr"/>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>grok-4.20-0309-non-reasoning</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G515" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H515" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I515" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J515" t="inlineStr"/>
+      <c r="K515" t="inlineStr"/>
+      <c r="L515" t="inlineStr"/>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>grok-4.20-0309-reasoning</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G516" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H516" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I516" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J516" t="inlineStr"/>
+      <c r="K516" t="inlineStr"/>
+      <c r="L516" t="inlineStr"/>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>grok-4.20-multi-agent-0309</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G517" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H517" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I517" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J517" t="inlineStr"/>
+      <c r="K517" t="inlineStr"/>
+      <c r="L517" t="inlineStr"/>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>grok-4.3</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G518" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H518" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I518" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J518" t="inlineStr"/>
+      <c r="K518" t="inlineStr"/>
+      <c r="L518" t="inlineStr"/>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>grok-build-0.1</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>256k</t>
+        </is>
+      </c>
+      <c r="G519" t="n">
+        <v>1</v>
+      </c>
+      <c r="H519" t="n">
+        <v>2</v>
+      </c>
+      <c r="I519" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J519" t="inlineStr"/>
+      <c r="K519" t="inlineStr"/>
+      <c r="L519" t="inlineStr"/>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:07:09+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34455,7 +42285,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-25T11:30:19+00:00</t>
+          <t>2026-05-26T07:07:09+00:00</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/llm_costs.xlsx
+++ b/data/llm_costs.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7633,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -7891,7 +7891,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q519"/>
+  <dimension ref="A1:Q641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -42240,6 +42240,7836 @@
         </is>
       </c>
     </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Claude Haiku 4.5</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>haiku</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="n">
+        <v>1</v>
+      </c>
+      <c r="H520" t="n">
+        <v>5</v>
+      </c>
+      <c r="I520" t="inlineStr"/>
+      <c r="J520" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K520" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L520" t="inlineStr"/>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q520" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Claude Opus 4</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr"/>
+      <c r="G521" t="n">
+        <v>15</v>
+      </c>
+      <c r="H521" t="n">
+        <v>75</v>
+      </c>
+      <c r="I521" t="inlineStr"/>
+      <c r="J521" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="K521" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L521" t="inlineStr"/>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q521" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.1</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr"/>
+      <c r="G522" t="n">
+        <v>15</v>
+      </c>
+      <c r="H522" t="n">
+        <v>75</v>
+      </c>
+      <c r="I522" t="inlineStr"/>
+      <c r="J522" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="K522" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L522" t="inlineStr"/>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q522" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.5</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr"/>
+      <c r="G523" t="n">
+        <v>5</v>
+      </c>
+      <c r="H523" t="n">
+        <v>25</v>
+      </c>
+      <c r="I523" t="inlineStr"/>
+      <c r="J523" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K523" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L523" t="inlineStr"/>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q523" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.6</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr"/>
+      <c r="G524" t="n">
+        <v>5</v>
+      </c>
+      <c r="H524" t="n">
+        <v>25</v>
+      </c>
+      <c r="I524" t="inlineStr"/>
+      <c r="J524" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K524" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q524" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.7</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr"/>
+      <c r="G525" t="n">
+        <v>5</v>
+      </c>
+      <c r="H525" t="n">
+        <v>25</v>
+      </c>
+      <c r="I525" t="inlineStr"/>
+      <c r="J525" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K525" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L525" t="inlineStr"/>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q525" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr"/>
+      <c r="G526" t="n">
+        <v>3</v>
+      </c>
+      <c r="H526" t="n">
+        <v>15</v>
+      </c>
+      <c r="I526" t="inlineStr"/>
+      <c r="J526" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K526" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L526" t="inlineStr"/>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q526" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.5</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr"/>
+      <c r="G527" t="n">
+        <v>3</v>
+      </c>
+      <c r="H527" t="n">
+        <v>15</v>
+      </c>
+      <c r="I527" t="inlineStr"/>
+      <c r="J527" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K527" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L527" t="inlineStr"/>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q527" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr"/>
+      <c r="G528" t="n">
+        <v>3</v>
+      </c>
+      <c r="H528" t="n">
+        <v>15</v>
+      </c>
+      <c r="I528" t="inlineStr"/>
+      <c r="J528" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K528" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L528" t="inlineStr"/>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q528" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr"/>
+      <c r="G529" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H529" t="inlineStr"/>
+      <c r="I529" t="inlineStr"/>
+      <c r="J529" t="inlineStr"/>
+      <c r="K529" t="inlineStr"/>
+      <c r="L529" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q529" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr"/>
+      <c r="G530" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H530" t="inlineStr"/>
+      <c r="I530" t="inlineStr"/>
+      <c r="J530" t="inlineStr"/>
+      <c r="K530" t="inlineStr"/>
+      <c r="L530" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q530" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr"/>
+      <c r="G531" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H531" t="inlineStr"/>
+      <c r="I531" t="inlineStr"/>
+      <c r="J531" t="inlineStr"/>
+      <c r="K531" t="inlineStr"/>
+      <c r="L531" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q531" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr"/>
+      <c r="G532" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H532" t="inlineStr"/>
+      <c r="I532" t="inlineStr"/>
+      <c r="J532" t="inlineStr"/>
+      <c r="K532" t="inlineStr"/>
+      <c r="L532" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q532" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr"/>
+      <c r="G533" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="H533" t="inlineStr"/>
+      <c r="I533" t="inlineStr"/>
+      <c r="J533" t="inlineStr"/>
+      <c r="K533" t="inlineStr"/>
+      <c r="L533" t="inlineStr"/>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q533" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr"/>
+      <c r="G534" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H534" t="inlineStr"/>
+      <c r="I534" t="inlineStr"/>
+      <c r="J534" t="inlineStr"/>
+      <c r="K534" t="inlineStr"/>
+      <c r="L534" t="inlineStr"/>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q534" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr"/>
+      <c r="G535" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H535" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I535" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J535" t="inlineStr"/>
+      <c r="K535" t="inlineStr"/>
+      <c r="L535" t="n">
+        <v>1</v>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q535" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr"/>
+      <c r="G536" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H536" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I536" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J536" t="inlineStr"/>
+      <c r="K536" t="inlineStr"/>
+      <c r="L536" t="n">
+        <v>1</v>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q536" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr"/>
+      <c r="G537" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H537" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I537" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J537" t="inlineStr"/>
+      <c r="K537" t="inlineStr"/>
+      <c r="L537" t="n">
+        <v>1</v>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q537" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr"/>
+      <c r="G538" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H538" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I538" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J538" t="inlineStr"/>
+      <c r="K538" t="inlineStr"/>
+      <c r="L538" t="n">
+        <v>1</v>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q538" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr"/>
+      <c r="G539" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H539" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I539" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J539" t="inlineStr"/>
+      <c r="K539" t="inlineStr"/>
+      <c r="L539" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>$0.054 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q539" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr"/>
+      <c r="G540" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H540" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I540" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J540" t="inlineStr"/>
+      <c r="K540" t="inlineStr"/>
+      <c r="L540" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>$0.054 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q540" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr"/>
+      <c r="G541" t="n">
+        <v>1</v>
+      </c>
+      <c r="H541" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I541" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J541" t="inlineStr"/>
+      <c r="K541" t="inlineStr"/>
+      <c r="L541" t="n">
+        <v>1</v>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q541" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr"/>
+      <c r="G542" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H542" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I542" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J542" t="inlineStr"/>
+      <c r="K542" t="inlineStr"/>
+      <c r="L542" t="n">
+        <v>1</v>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q542" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr"/>
+      <c r="G543" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H543" t="inlineStr"/>
+      <c r="I543" t="inlineStr"/>
+      <c r="J543" t="inlineStr"/>
+      <c r="K543" t="inlineStr"/>
+      <c r="L543" t="inlineStr"/>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr"/>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q543" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr"/>
+      <c r="G544" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H544" t="inlineStr"/>
+      <c r="I544" t="inlineStr"/>
+      <c r="J544" t="inlineStr"/>
+      <c r="K544" t="inlineStr"/>
+      <c r="L544" t="inlineStr"/>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr"/>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q544" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr"/>
+      <c r="G545" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H545" t="inlineStr"/>
+      <c r="I545" t="inlineStr"/>
+      <c r="J545" t="inlineStr"/>
+      <c r="K545" t="inlineStr"/>
+      <c r="L545" t="inlineStr"/>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr"/>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q545" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr"/>
+      <c r="G546" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H546" t="inlineStr"/>
+      <c r="I546" t="inlineStr"/>
+      <c r="J546" t="inlineStr"/>
+      <c r="K546" t="inlineStr"/>
+      <c r="L546" t="inlineStr"/>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr"/>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q546" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Preview TTS</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr"/>
+      <c r="G547" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H547" t="inlineStr"/>
+      <c r="I547" t="inlineStr"/>
+      <c r="J547" t="inlineStr"/>
+      <c r="K547" t="inlineStr"/>
+      <c r="L547" t="inlineStr"/>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr"/>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q547" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Preview TTS</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr"/>
+      <c r="G548" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H548" t="inlineStr"/>
+      <c r="I548" t="inlineStr"/>
+      <c r="J548" t="inlineStr"/>
+      <c r="K548" t="inlineStr"/>
+      <c r="L548" t="inlineStr"/>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr"/>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q548" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr"/>
+      <c r="G549" t="inlineStr"/>
+      <c r="H549" t="n">
+        <v>5</v>
+      </c>
+      <c r="I549" t="inlineStr"/>
+      <c r="J549" t="inlineStr"/>
+      <c r="K549" t="inlineStr"/>
+      <c r="L549" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q549" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr"/>
+      <c r="G550" t="inlineStr"/>
+      <c r="H550" t="n">
+        <v>5</v>
+      </c>
+      <c r="I550" t="inlineStr"/>
+      <c r="J550" t="inlineStr"/>
+      <c r="K550" t="inlineStr"/>
+      <c r="L550" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q550" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr"/>
+      <c r="G551" t="inlineStr"/>
+      <c r="H551" t="n">
+        <v>18</v>
+      </c>
+      <c r="I551" t="inlineStr"/>
+      <c r="J551" t="inlineStr"/>
+      <c r="K551" t="inlineStr"/>
+      <c r="L551" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>$0.225, prompts &lt;= 200k tokens $0.45, prompts &gt; 200k $8.10 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q551" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr"/>
+      <c r="G552" t="inlineStr"/>
+      <c r="H552" t="n">
+        <v>10</v>
+      </c>
+      <c r="I552" t="inlineStr"/>
+      <c r="J552" t="inlineStr"/>
+      <c r="K552" t="inlineStr"/>
+      <c r="L552" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q552" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro Preview TTS</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr"/>
+      <c r="G553" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H553" t="inlineStr"/>
+      <c r="I553" t="inlineStr"/>
+      <c r="J553" t="inlineStr"/>
+      <c r="K553" t="inlineStr"/>
+      <c r="L553" t="inlineStr"/>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr"/>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q553" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro Preview TTS</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr"/>
+      <c r="G554" t="n">
+        <v>1</v>
+      </c>
+      <c r="H554" t="inlineStr"/>
+      <c r="I554" t="inlineStr"/>
+      <c r="J554" t="inlineStr"/>
+      <c r="K554" t="inlineStr"/>
+      <c r="L554" t="inlineStr"/>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr"/>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q554" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr"/>
+      <c r="G555" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H555" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I555" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J555" t="inlineStr"/>
+      <c r="K555" t="inlineStr"/>
+      <c r="L555" t="n">
+        <v>1</v>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q555" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr"/>
+      <c r="G556" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H556" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I556" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J556" t="inlineStr"/>
+      <c r="K556" t="inlineStr"/>
+      <c r="L556" t="n">
+        <v>1</v>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q556" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr"/>
+      <c r="G557" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H557" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I557" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J557" t="inlineStr"/>
+      <c r="K557" t="inlineStr"/>
+      <c r="L557" t="n">
+        <v>1</v>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q557" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr"/>
+      <c r="G558" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H558" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I558" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J558" t="inlineStr"/>
+      <c r="K558" t="inlineStr"/>
+      <c r="L558" t="n">
+        <v>1</v>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q558" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr"/>
+      <c r="G559" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H559" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I559" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J559" t="inlineStr"/>
+      <c r="K559" t="inlineStr"/>
+      <c r="L559" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>$0.09 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q559" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr"/>
+      <c r="G560" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H560" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I560" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J560" t="inlineStr"/>
+      <c r="K560" t="inlineStr"/>
+      <c r="L560" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>$0.09 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q560" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr"/>
+      <c r="G561" t="n">
+        <v>1</v>
+      </c>
+      <c r="H561" t="n">
+        <v>3</v>
+      </c>
+      <c r="I561" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J561" t="inlineStr"/>
+      <c r="K561" t="inlineStr"/>
+      <c r="L561" t="n">
+        <v>1</v>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>$0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q561" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr"/>
+      <c r="G562" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H562" t="n">
+        <v>3</v>
+      </c>
+      <c r="I562" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J562" t="inlineStr"/>
+      <c r="K562" t="inlineStr"/>
+      <c r="L562" t="n">
+        <v>1</v>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>$0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q562" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr"/>
+      <c r="G563" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H563" t="inlineStr"/>
+      <c r="I563" t="inlineStr"/>
+      <c r="J563" t="inlineStr"/>
+      <c r="K563" t="inlineStr"/>
+      <c r="L563" t="inlineStr"/>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr"/>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q563" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr"/>
+      <c r="G564" t="n">
+        <v>1</v>
+      </c>
+      <c r="H564" t="inlineStr"/>
+      <c r="I564" t="inlineStr"/>
+      <c r="J564" t="inlineStr"/>
+      <c r="K564" t="inlineStr"/>
+      <c r="L564" t="inlineStr"/>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr"/>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q564" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr"/>
+      <c r="G565" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H565" t="inlineStr"/>
+      <c r="I565" t="inlineStr"/>
+      <c r="J565" t="inlineStr"/>
+      <c r="K565" t="inlineStr"/>
+      <c r="L565" t="inlineStr"/>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr"/>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q565" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr"/>
+      <c r="G566" t="n">
+        <v>1</v>
+      </c>
+      <c r="H566" t="inlineStr"/>
+      <c r="I566" t="inlineStr"/>
+      <c r="J566" t="inlineStr"/>
+      <c r="K566" t="inlineStr"/>
+      <c r="L566" t="inlineStr"/>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr"/>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q566" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr"/>
+      <c r="G567" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H567" t="inlineStr"/>
+      <c r="I567" t="inlineStr"/>
+      <c r="J567" t="inlineStr"/>
+      <c r="K567" t="inlineStr"/>
+      <c r="L567" t="inlineStr"/>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr"/>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q567" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr"/>
+      <c r="G568" t="n">
+        <v>2</v>
+      </c>
+      <c r="H568" t="inlineStr"/>
+      <c r="I568" t="inlineStr"/>
+      <c r="J568" t="inlineStr"/>
+      <c r="K568" t="inlineStr"/>
+      <c r="L568" t="inlineStr"/>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr"/>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q568" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>text, image</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr"/>
+      <c r="G569" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H569" t="inlineStr"/>
+      <c r="I569" t="inlineStr"/>
+      <c r="J569" t="inlineStr"/>
+      <c r="K569" t="inlineStr"/>
+      <c r="L569" t="inlineStr"/>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr"/>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q569" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash Image Preview 🍌</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr"/>
+      <c r="G570" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H570" t="inlineStr"/>
+      <c r="I570" t="inlineStr"/>
+      <c r="J570" t="inlineStr"/>
+      <c r="K570" t="inlineStr"/>
+      <c r="L570" t="inlineStr"/>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr"/>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q570" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash TTS Preview</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr"/>
+      <c r="G571" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H571" t="inlineStr"/>
+      <c r="I571" t="inlineStr"/>
+      <c r="J571" t="inlineStr"/>
+      <c r="K571" t="inlineStr"/>
+      <c r="L571" t="inlineStr"/>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr"/>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q571" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash TTS Preview</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr"/>
+      <c r="G572" t="n">
+        <v>1</v>
+      </c>
+      <c r="H572" t="inlineStr"/>
+      <c r="I572" t="inlineStr"/>
+      <c r="J572" t="inlineStr"/>
+      <c r="K572" t="inlineStr"/>
+      <c r="L572" t="inlineStr"/>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr"/>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q572" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr"/>
+      <c r="G573" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H573" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I573" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J573" t="inlineStr"/>
+      <c r="K573" t="inlineStr"/>
+      <c r="L573" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q573" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr"/>
+      <c r="G574" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H574" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I574" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J574" t="inlineStr"/>
+      <c r="K574" t="inlineStr"/>
+      <c r="L574" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr"/>
+      <c r="G575" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H575" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I575" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J575" t="inlineStr"/>
+      <c r="K575" t="inlineStr"/>
+      <c r="L575" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr"/>
+      <c r="G576" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H576" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I576" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J576" t="inlineStr"/>
+      <c r="K576" t="inlineStr"/>
+      <c r="L576" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr"/>
+      <c r="G577" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H577" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I577" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J577" t="inlineStr"/>
+      <c r="K577" t="inlineStr"/>
+      <c r="L577" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr"/>
+      <c r="G578" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H578" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I578" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J578" t="inlineStr"/>
+      <c r="K578" t="inlineStr"/>
+      <c r="L578" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q578" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr"/>
+      <c r="G579" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H579" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I579" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J579" t="inlineStr"/>
+      <c r="K579" t="inlineStr"/>
+      <c r="L579" t="n">
+        <v>1</v>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q579" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr"/>
+      <c r="G580" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H580" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I580" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J580" t="inlineStr"/>
+      <c r="K580" t="inlineStr"/>
+      <c r="L580" t="n">
+        <v>1</v>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q580" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr"/>
+      <c r="G581" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H581" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I581" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J581" t="inlineStr"/>
+      <c r="K581" t="inlineStr"/>
+      <c r="L581" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q581" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr"/>
+      <c r="G582" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H582" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I582" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J582" t="inlineStr"/>
+      <c r="K582" t="inlineStr"/>
+      <c r="L582" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q582" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr"/>
+      <c r="G583" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H583" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I583" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J583" t="inlineStr"/>
+      <c r="K583" t="inlineStr"/>
+      <c r="L583" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q583" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr"/>
+      <c r="G584" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H584" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I584" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J584" t="inlineStr"/>
+      <c r="K584" t="inlineStr"/>
+      <c r="L584" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q584" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr"/>
+      <c r="G585" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H585" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I585" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J585" t="inlineStr"/>
+      <c r="K585" t="inlineStr"/>
+      <c r="L585" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q585" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr"/>
+      <c r="G586" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H586" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I586" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J586" t="inlineStr"/>
+      <c r="K586" t="inlineStr"/>
+      <c r="L586" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q586" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr"/>
+      <c r="G587" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H587" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I587" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J587" t="inlineStr"/>
+      <c r="K587" t="inlineStr"/>
+      <c r="L587" t="n">
+        <v>1</v>
+      </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q587" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite Preview</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr"/>
+      <c r="G588" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H588" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I588" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J588" t="inlineStr"/>
+      <c r="K588" t="inlineStr"/>
+      <c r="L588" t="n">
+        <v>1</v>
+      </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q588" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr"/>
+      <c r="G589" t="inlineStr"/>
+      <c r="H589" t="n">
+        <v>6</v>
+      </c>
+      <c r="I589" t="inlineStr"/>
+      <c r="J589" t="inlineStr"/>
+      <c r="K589" t="inlineStr"/>
+      <c r="L589" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q589" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr"/>
+      <c r="G590" t="inlineStr"/>
+      <c r="H590" t="n">
+        <v>6</v>
+      </c>
+      <c r="I590" t="inlineStr"/>
+      <c r="J590" t="inlineStr"/>
+      <c r="K590" t="inlineStr"/>
+      <c r="L590" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q590" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr"/>
+      <c r="G591" t="inlineStr"/>
+      <c r="H591" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I591" t="inlineStr"/>
+      <c r="J591" t="inlineStr"/>
+      <c r="K591" t="inlineStr"/>
+      <c r="L591" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>$0.36, prompts &lt;= 200k tokens $0.72, prompts &gt; 200k $8.10 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q591" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr"/>
+      <c r="G592" t="inlineStr"/>
+      <c r="H592" t="n">
+        <v>12</v>
+      </c>
+      <c r="I592" t="inlineStr"/>
+      <c r="J592" t="inlineStr"/>
+      <c r="K592" t="inlineStr"/>
+      <c r="L592" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P592" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q592" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr"/>
+      <c r="G593" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H593" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I593" t="inlineStr"/>
+      <c r="J593" t="inlineStr"/>
+      <c r="K593" t="inlineStr"/>
+      <c r="L593" t="n">
+        <v>1</v>
+      </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>$0.075 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P593" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q593" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr"/>
+      <c r="G594" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H594" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I594" t="inlineStr"/>
+      <c r="J594" t="inlineStr"/>
+      <c r="K594" t="inlineStr"/>
+      <c r="L594" t="n">
+        <v>1</v>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>$0.08 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P594" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q594" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr"/>
+      <c r="G595" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H595" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I595" t="inlineStr"/>
+      <c r="J595" t="inlineStr"/>
+      <c r="K595" t="inlineStr"/>
+      <c r="L595" t="n">
+        <v>1</v>
+      </c>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>$0.27 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P595" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q595" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr"/>
+      <c r="G596" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H596" t="n">
+        <v>9</v>
+      </c>
+      <c r="I596" t="inlineStr"/>
+      <c r="J596" t="inlineStr"/>
+      <c r="K596" t="inlineStr"/>
+      <c r="L596" t="n">
+        <v>1</v>
+      </c>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>$0.15 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P596" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q596" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Gemini Embedding</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>embedding</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr"/>
+      <c r="G597" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H597" t="inlineStr"/>
+      <c r="I597" t="inlineStr"/>
+      <c r="J597" t="inlineStr"/>
+      <c r="K597" t="inlineStr"/>
+      <c r="L597" t="inlineStr"/>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O597" t="inlineStr"/>
+      <c r="P597" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q597" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Gemini Embedding</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>embedding</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr"/>
+      <c r="G598" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H598" t="inlineStr"/>
+      <c r="I598" t="inlineStr"/>
+      <c r="J598" t="inlineStr"/>
+      <c r="K598" t="inlineStr"/>
+      <c r="L598" t="inlineStr"/>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O598" t="inlineStr"/>
+      <c r="P598" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q598" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr"/>
+      <c r="G599" t="n">
+        <v>1</v>
+      </c>
+      <c r="H599" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I599" t="inlineStr"/>
+      <c r="J599" t="inlineStr"/>
+      <c r="K599" t="inlineStr"/>
+      <c r="L599" t="inlineStr"/>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O599" t="inlineStr"/>
+      <c r="P599" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q599" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr"/>
+      <c r="G600" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H600" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I600" t="inlineStr"/>
+      <c r="J600" t="inlineStr"/>
+      <c r="K600" t="inlineStr"/>
+      <c r="L600" t="inlineStr"/>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O600" t="inlineStr"/>
+      <c r="P600" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q600" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr"/>
+      <c r="G601" t="n">
+        <v>2</v>
+      </c>
+      <c r="H601" t="n">
+        <v>5</v>
+      </c>
+      <c r="I601" t="inlineStr"/>
+      <c r="J601" t="inlineStr"/>
+      <c r="K601" t="inlineStr"/>
+      <c r="L601" t="inlineStr"/>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O601" t="inlineStr"/>
+      <c r="P601" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q601" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr"/>
+      <c r="G602" t="n">
+        <v>1</v>
+      </c>
+      <c r="H602" t="n">
+        <v>5</v>
+      </c>
+      <c r="I602" t="inlineStr"/>
+      <c r="J602" t="inlineStr"/>
+      <c r="K602" t="inlineStr"/>
+      <c r="L602" t="inlineStr"/>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O602" t="inlineStr"/>
+      <c r="P602" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q602" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>chat-latest</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>chat</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>tools</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr"/>
+      <c r="G603" t="n">
+        <v>5</v>
+      </c>
+      <c r="H603" t="n">
+        <v>30</v>
+      </c>
+      <c r="I603" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J603" t="inlineStr"/>
+      <c r="K603" t="inlineStr"/>
+      <c r="L603" t="inlineStr"/>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>Video generation models | Transcription models | Prices per 1M tokens unless noted. | Tools</t>
+        </is>
+      </c>
+      <c r="P603" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q603" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>computer-use-preview</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>computer</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr"/>
+      <c r="G604" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H604" t="n">
+        <v>6</v>
+      </c>
+      <c r="I604" t="inlineStr"/>
+      <c r="J604" t="inlineStr"/>
+      <c r="K604" t="inlineStr"/>
+      <c r="L604" t="inlineStr"/>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q604" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini-transcribe</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>video-generation-models</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr"/>
+      <c r="G605" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H605" t="n">
+        <v>5</v>
+      </c>
+      <c r="I605" t="inlineStr"/>
+      <c r="J605" t="inlineStr"/>
+      <c r="K605" t="inlineStr"/>
+      <c r="L605" t="inlineStr"/>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models | Video generation models</t>
+        </is>
+      </c>
+      <c r="P605" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q605" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>gpt-4o-transcribe</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>video-generation-models</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr"/>
+      <c r="G606" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H606" t="n">
+        <v>10</v>
+      </c>
+      <c r="I606" t="inlineStr"/>
+      <c r="J606" t="inlineStr"/>
+      <c r="K606" t="inlineStr"/>
+      <c r="L606" t="inlineStr"/>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models | Video generation models</t>
+        </is>
+      </c>
+      <c r="P606" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q606" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>gpt-5.3-codex</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr"/>
+      <c r="G607" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H607" t="n">
+        <v>28</v>
+      </c>
+      <c r="I607" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J607" t="inlineStr"/>
+      <c r="K607" t="inlineStr"/>
+      <c r="L607" t="inlineStr"/>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P607" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q607" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>gpt-5.3-codex</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>tools</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr"/>
+      <c r="G608" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H608" t="n">
+        <v>14</v>
+      </c>
+      <c r="I608" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="J608" t="inlineStr"/>
+      <c r="K608" t="inlineStr"/>
+      <c r="L608" t="inlineStr"/>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>Video generation models | Transcription models | Prices per 1M tokens unless noted. | Tools</t>
+        </is>
+      </c>
+      <c r="P608" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q608" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G609" t="n">
+        <v>5</v>
+      </c>
+      <c r="H609" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I609" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J609" t="inlineStr"/>
+      <c r="K609" t="inlineStr"/>
+      <c r="L609" t="inlineStr"/>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P609" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q609" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G610" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H610" t="n">
+        <v>15</v>
+      </c>
+      <c r="I610" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J610" t="inlineStr"/>
+      <c r="K610" t="inlineStr"/>
+      <c r="L610" t="inlineStr"/>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N610" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P610" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q610" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>gpt-5.4-mini</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G611" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H611" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I611" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J611" t="inlineStr"/>
+      <c r="K611" t="inlineStr"/>
+      <c r="L611" t="inlineStr"/>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P611" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q611" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>gpt-5.4-nano</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G612" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H612" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I612" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J612" t="inlineStr"/>
+      <c r="K612" t="inlineStr"/>
+      <c r="L612" t="inlineStr"/>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P612" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q612" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>gpt-5.4-pro</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G613" t="n">
+        <v>60</v>
+      </c>
+      <c r="H613" t="n">
+        <v>270</v>
+      </c>
+      <c r="I613" t="inlineStr"/>
+      <c r="J613" t="inlineStr"/>
+      <c r="K613" t="inlineStr"/>
+      <c r="L613" t="inlineStr"/>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P613" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q613" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>gpt-5.4-pro</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G614" t="n">
+        <v>30</v>
+      </c>
+      <c r="H614" t="n">
+        <v>180</v>
+      </c>
+      <c r="I614" t="inlineStr"/>
+      <c r="J614" t="inlineStr"/>
+      <c r="K614" t="inlineStr"/>
+      <c r="L614" t="inlineStr"/>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P614" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q614" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G615" t="n">
+        <v>10</v>
+      </c>
+      <c r="H615" t="n">
+        <v>45</v>
+      </c>
+      <c r="I615" t="n">
+        <v>1</v>
+      </c>
+      <c r="J615" t="inlineStr"/>
+      <c r="K615" t="inlineStr"/>
+      <c r="L615" t="inlineStr"/>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q615" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G616" t="n">
+        <v>5</v>
+      </c>
+      <c r="H616" t="n">
+        <v>30</v>
+      </c>
+      <c r="I616" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J616" t="inlineStr"/>
+      <c r="K616" t="inlineStr"/>
+      <c r="L616" t="inlineStr"/>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q616" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>gpt-5.5-pro</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G617" t="n">
+        <v>60</v>
+      </c>
+      <c r="H617" t="n">
+        <v>270</v>
+      </c>
+      <c r="I617" t="inlineStr"/>
+      <c r="J617" t="inlineStr"/>
+      <c r="K617" t="inlineStr"/>
+      <c r="L617" t="inlineStr"/>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q617" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>gpt-5.5-pro</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G618" t="n">
+        <v>30</v>
+      </c>
+      <c r="H618" t="n">
+        <v>180</v>
+      </c>
+      <c r="I618" t="inlineStr"/>
+      <c r="J618" t="inlineStr"/>
+      <c r="K618" t="inlineStr"/>
+      <c r="L618" t="inlineStr"/>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q618" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr"/>
+      <c r="G619" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H619" t="n">
+        <v>4</v>
+      </c>
+      <c r="I619" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J619" t="inlineStr"/>
+      <c r="K619" t="inlineStr"/>
+      <c r="L619" t="inlineStr"/>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q619" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr"/>
+      <c r="G620" t="n">
+        <v>1</v>
+      </c>
+      <c r="H620" t="inlineStr"/>
+      <c r="I620" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J620" t="inlineStr"/>
+      <c r="K620" t="inlineStr"/>
+      <c r="L620" t="inlineStr"/>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q620" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr"/>
+      <c r="G621" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H621" t="n">
+        <v>8</v>
+      </c>
+      <c r="I621" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J621" t="inlineStr"/>
+      <c r="K621" t="inlineStr"/>
+      <c r="L621" t="inlineStr"/>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q621" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr"/>
+      <c r="G622" t="n">
+        <v>2</v>
+      </c>
+      <c r="H622" t="inlineStr"/>
+      <c r="I622" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J622" t="inlineStr"/>
+      <c r="K622" t="inlineStr"/>
+      <c r="L622" t="inlineStr"/>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q622" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr"/>
+      <c r="G623" t="n">
+        <v>4</v>
+      </c>
+      <c r="H623" t="n">
+        <v>16</v>
+      </c>
+      <c r="I623" t="n">
+        <v>1</v>
+      </c>
+      <c r="J623" t="inlineStr"/>
+      <c r="K623" t="inlineStr"/>
+      <c r="L623" t="inlineStr"/>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q623" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr"/>
+      <c r="G624" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H624" t="n">
+        <v>5</v>
+      </c>
+      <c r="I624" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J624" t="inlineStr"/>
+      <c r="K624" t="inlineStr"/>
+      <c r="L624" t="inlineStr"/>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q624" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr"/>
+      <c r="G625" t="n">
+        <v>8</v>
+      </c>
+      <c r="H625" t="n">
+        <v>32</v>
+      </c>
+      <c r="I625" t="n">
+        <v>2</v>
+      </c>
+      <c r="J625" t="inlineStr"/>
+      <c r="K625" t="inlineStr"/>
+      <c r="L625" t="inlineStr"/>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q625" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr"/>
+      <c r="G626" t="n">
+        <v>5</v>
+      </c>
+      <c r="H626" t="n">
+        <v>10</v>
+      </c>
+      <c r="I626" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J626" t="inlineStr"/>
+      <c r="K626" t="inlineStr"/>
+      <c r="L626" t="inlineStr"/>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P626" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q626" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr"/>
+      <c r="G627" t="n">
+        <v>4</v>
+      </c>
+      <c r="H627" t="n">
+        <v>15</v>
+      </c>
+      <c r="I627" t="n">
+        <v>1</v>
+      </c>
+      <c r="J627" t="inlineStr"/>
+      <c r="K627" t="inlineStr"/>
+      <c r="L627" t="inlineStr"/>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P627" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q627" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr"/>
+      <c r="G628" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H628" t="inlineStr"/>
+      <c r="I628" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="J628" t="inlineStr"/>
+      <c r="K628" t="inlineStr"/>
+      <c r="L628" t="inlineStr"/>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P628" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q628" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr"/>
+      <c r="G629" t="n">
+        <v>8</v>
+      </c>
+      <c r="H629" t="n">
+        <v>30</v>
+      </c>
+      <c r="I629" t="n">
+        <v>2</v>
+      </c>
+      <c r="J629" t="inlineStr"/>
+      <c r="K629" t="inlineStr"/>
+      <c r="L629" t="inlineStr"/>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P629" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q629" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr"/>
+      <c r="G630" t="n">
+        <v>5</v>
+      </c>
+      <c r="H630" t="inlineStr"/>
+      <c r="I630" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J630" t="inlineStr"/>
+      <c r="K630" t="inlineStr"/>
+      <c r="L630" t="inlineStr"/>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P630" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q630" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>o3-deep-research</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr"/>
+      <c r="G631" t="n">
+        <v>5</v>
+      </c>
+      <c r="H631" t="n">
+        <v>20</v>
+      </c>
+      <c r="I631" t="inlineStr"/>
+      <c r="J631" t="inlineStr"/>
+      <c r="K631" t="inlineStr"/>
+      <c r="L631" t="inlineStr"/>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P631" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q631" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>all-fine-tuned-models-will-remain-available-for-inference-until-their-base-models-are-deprecated-the-full-timeline-is-here</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr"/>
+      <c r="G632" t="n">
+        <v>2</v>
+      </c>
+      <c r="H632" t="n">
+        <v>8</v>
+      </c>
+      <c r="I632" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J632" t="inlineStr"/>
+      <c r="K632" t="inlineStr"/>
+      <c r="L632" t="inlineStr"/>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N632" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O632" t="inlineStr">
+        <is>
+          <t>Specialized models | Finetuning | OpenAI is winding down the fine-tuning platform. The platform is no longer accessible to new users, but existing users of the fine-tuning platform will be able to create training jobs for the coming months. | All fine-tuned models will remain available for inference until their base models are deprecated. The full timeline is here .</t>
+        </is>
+      </c>
+      <c r="P632" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q632" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr"/>
+      <c r="G633" t="n">
+        <v>4</v>
+      </c>
+      <c r="H633" t="n">
+        <v>16</v>
+      </c>
+      <c r="I633" t="n">
+        <v>1</v>
+      </c>
+      <c r="J633" t="inlineStr"/>
+      <c r="K633" t="inlineStr"/>
+      <c r="L633" t="inlineStr"/>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N633" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P633" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q633" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16 with data sharing</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>all-fine-tuned-models-will-remain-available-for-inference-until-their-base-models-are-deprecated-the-full-timeline-is-here</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr"/>
+      <c r="G634" t="n">
+        <v>1</v>
+      </c>
+      <c r="H634" t="n">
+        <v>4</v>
+      </c>
+      <c r="I634" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J634" t="inlineStr"/>
+      <c r="K634" t="inlineStr"/>
+      <c r="L634" t="inlineStr"/>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N634" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O634" t="inlineStr">
+        <is>
+          <t>Specialized models | Finetuning | OpenAI is winding down the fine-tuning platform. The platform is no longer accessible to new users, but existing users of the fine-tuning platform will be able to create training jobs for the coming months. | All fine-tuned models will remain available for inference until their base models are deprecated. The full timeline is here .</t>
+        </is>
+      </c>
+      <c r="P634" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q634" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16 with data sharing</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr"/>
+      <c r="G635" t="n">
+        <v>2</v>
+      </c>
+      <c r="H635" t="n">
+        <v>8</v>
+      </c>
+      <c r="I635" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J635" t="inlineStr"/>
+      <c r="K635" t="inlineStr"/>
+      <c r="L635" t="inlineStr"/>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N635" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P635" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q635" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>o4-mini-deep-research</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr"/>
+      <c r="G636" t="n">
+        <v>1</v>
+      </c>
+      <c r="H636" t="n">
+        <v>4</v>
+      </c>
+      <c r="I636" t="inlineStr"/>
+      <c r="J636" t="inlineStr"/>
+      <c r="K636" t="inlineStr"/>
+      <c r="L636" t="inlineStr"/>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N636" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P636" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q636" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>grok-4.20-0309-non-reasoning</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G637" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H637" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I637" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J637" t="inlineStr"/>
+      <c r="K637" t="inlineStr"/>
+      <c r="L637" t="inlineStr"/>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N637" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P637" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q637" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>grok-4.20-0309-reasoning</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G638" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H638" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I638" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J638" t="inlineStr"/>
+      <c r="K638" t="inlineStr"/>
+      <c r="L638" t="inlineStr"/>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P638" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q638" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>grok-4.20-multi-agent-0309</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G639" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H639" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I639" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J639" t="inlineStr"/>
+      <c r="K639" t="inlineStr"/>
+      <c r="L639" t="inlineStr"/>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N639" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O639" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P639" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q639" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>grok-4.3</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G640" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H640" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I640" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J640" t="inlineStr"/>
+      <c r="K640" t="inlineStr"/>
+      <c r="L640" t="inlineStr"/>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N640" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P640" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q640" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>grok-build-0.1</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>256k</t>
+        </is>
+      </c>
+      <c r="G641" t="n">
+        <v>1</v>
+      </c>
+      <c r="H641" t="n">
+        <v>2</v>
+      </c>
+      <c r="I641" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J641" t="inlineStr"/>
+      <c r="K641" t="inlineStr"/>
+      <c r="L641" t="inlineStr"/>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N641" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P641" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q641" t="inlineStr">
+        <is>
+          <t>2026-05-27T07:20:59+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -42285,7 +50115,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-26T07:07:09+00:00</t>
+          <t>2026-05-27T07:20:59+00:00</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/llm_costs.xlsx
+++ b/data/llm_costs.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Flash Image 🍌</t>
+          <t>Gemini 3 Pro Image 🍌</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3385,12 +3385,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>text, image</t>
+          <t>image</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>0.25</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3427,27 +3427,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Flash Image 🍌</t>
+          <t>Gemini 3 Pro Image 🍌</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>batch</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>text/image</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3484,27 +3484,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Flash TTS Preview</t>
+          <t>Gemini 3 Pro Image 🍌</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>batch</t>
+          <t>flex</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>image</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>0.5</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3541,17 +3541,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Flash TTS Preview</t>
+          <t>Gemini 3 Pro Image 🍌</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>flex</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3598,39 +3598,33 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Flash-Lite</t>
+          <t>Gemini 3 Pro Image 🍌</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>batch</t>
+          <t>priority</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>audio</t>
+          <t>text/image</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.025</v>
-      </c>
+        <v>3.6</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>USD per 1M tokens</t>
@@ -3641,11 +3635,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
@@ -3653,7 +3643,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3665,39 +3655,33 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Flash-Lite</t>
+          <t>Gemini 3 Pro Image 🍌</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>batch</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>text / image / video</t>
+          <t>text/image</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.0125</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>USD per 1M tokens</t>
@@ -3708,11 +3692,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
@@ -3720,7 +3700,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3712,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Flash-Lite</t>
+          <t>Gemini 3.1 Flash Image 🍌</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3742,29 +3722,23 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>flex</t>
+          <t>batch</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>audio</t>
+          <t>text, image</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
         <v>0.25</v>
       </c>
-      <c r="H52" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.025</v>
-      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>USD per 1M tokens</t>
@@ -3775,11 +3749,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
@@ -3787,7 +3757,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3769,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Flash-Lite</t>
+          <t>Gemini 3.1 Flash Image 🍌</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3809,29 +3779,23 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>flex</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>text / image / video</t>
+          <t>text/image</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.0125</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>USD per 1M tokens</t>
@@ -3842,11 +3806,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
@@ -3854,7 +3814,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3826,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Flash-Lite</t>
+          <t>Gemini 3.1 Flash TTS Preview</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3876,29 +3836,23 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>priority</t>
+          <t>batch</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>audio</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H54" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.09</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>USD per 1M tokens</t>
@@ -3909,11 +3863,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
@@ -3921,7 +3871,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3883,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Flash-Lite</t>
+          <t>Gemini 3.1 Flash TTS Preview</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3943,29 +3893,23 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>priority</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>text / image / video</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H55" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.045</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>USD per 1M tokens</t>
@@ -3976,11 +3920,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
-        </is>
-      </c>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
@@ -3988,7 +3928,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4010,7 +3950,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>batch</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4020,18 +3960,18 @@
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H56" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>0.05</v>
+        <v>0.025</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -4045,7 +3985,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -4055,7 +3995,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4077,7 +4017,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>batch</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4087,18 +4027,18 @@
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="H57" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="I57" t="n">
-        <v>0.025</v>
+        <v>0.0125</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -4112,7 +4052,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -4122,7 +4062,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4074,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro Image 🍌</t>
+          <t>Gemini 3.1 Flash-Lite</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4144,23 +4084,29 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>batch</t>
+          <t>flex</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>audio</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.025</v>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
+      <c r="L58" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>USD per 1M tokens</t>
@@ -4171,7 +4117,11 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
@@ -4179,7 +4129,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4141,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro Image 🍌</t>
+          <t>Gemini 3.1 Flash-Lite</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4201,23 +4151,29 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>batch</t>
+          <t>flex</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>text / image / video</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+        <v>0.125</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.0125</v>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+      <c r="L59" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
           <t>USD per 1M tokens</t>
@@ -4228,7 +4184,11 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
@@ -4236,7 +4196,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4208,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro Image 🍌</t>
+          <t>Gemini 3.1 Flash-Lite</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4258,23 +4218,29 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>flex</t>
+          <t>priority</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>audio</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="H60" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.09</v>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
+      <c r="L60" t="n">
+        <v>1.8</v>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t>USD per 1M tokens</t>
@@ -4285,7 +4251,11 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
@@ -4293,7 +4263,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4275,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro Image 🍌</t>
+          <t>Gemini 3.1 Flash-Lite</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4315,23 +4285,29 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>flex</t>
+          <t>priority</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>text / image / video</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+        <v>0.45</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.045</v>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+      <c r="L61" t="n">
+        <v>1.8</v>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>USD per 1M tokens</t>
@@ -4342,7 +4318,11 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
@@ -4350,7 +4330,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4342,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro Image 🍌</t>
+          <t>Gemini 3.1 Flash-Lite</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4372,23 +4352,29 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>priority</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>text/image</t>
+          <t>audio</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.05</v>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>USD per 1M tokens</t>
@@ -4399,7 +4385,11 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
@@ -4407,7 +4397,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4409,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro Image 🍌</t>
+          <t>Gemini 3.1 Flash-Lite</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4434,18 +4424,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>text/image</t>
+          <t>text / image / video</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>2</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.025</v>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
+      <c r="L63" t="n">
+        <v>1</v>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>USD per 1M tokens</t>
@@ -4456,7 +4452,11 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q869"/>
+  <dimension ref="A1:Q983"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -64189,6 +64189,7300 @@
         </is>
       </c>
     </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Claude Haiku 4.5</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>haiku</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr"/>
+      <c r="G870" t="n">
+        <v>1</v>
+      </c>
+      <c r="H870" t="n">
+        <v>5</v>
+      </c>
+      <c r="I870" t="inlineStr"/>
+      <c r="J870" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K870" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L870" t="inlineStr"/>
+      <c r="M870" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N870" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O870" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P870" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q870" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Claude Opus 4</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr"/>
+      <c r="G871" t="n">
+        <v>15</v>
+      </c>
+      <c r="H871" t="n">
+        <v>75</v>
+      </c>
+      <c r="I871" t="inlineStr"/>
+      <c r="J871" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="K871" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L871" t="inlineStr"/>
+      <c r="M871" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N871" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O871" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P871" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q871" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.1</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr"/>
+      <c r="G872" t="n">
+        <v>15</v>
+      </c>
+      <c r="H872" t="n">
+        <v>75</v>
+      </c>
+      <c r="I872" t="inlineStr"/>
+      <c r="J872" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="K872" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L872" t="inlineStr"/>
+      <c r="M872" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N872" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O872" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P872" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q872" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.5</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr"/>
+      <c r="G873" t="n">
+        <v>5</v>
+      </c>
+      <c r="H873" t="n">
+        <v>25</v>
+      </c>
+      <c r="I873" t="inlineStr"/>
+      <c r="J873" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K873" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L873" t="inlineStr"/>
+      <c r="M873" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N873" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O873" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P873" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q873" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.6</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr"/>
+      <c r="G874" t="n">
+        <v>5</v>
+      </c>
+      <c r="H874" t="n">
+        <v>25</v>
+      </c>
+      <c r="I874" t="inlineStr"/>
+      <c r="J874" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K874" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L874" t="inlineStr"/>
+      <c r="M874" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N874" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O874" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P874" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q874" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.8</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr"/>
+      <c r="G875" t="n">
+        <v>5</v>
+      </c>
+      <c r="H875" t="n">
+        <v>25</v>
+      </c>
+      <c r="I875" t="inlineStr"/>
+      <c r="J875" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K875" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L875" t="inlineStr"/>
+      <c r="M875" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N875" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O875" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P875" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q875" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr"/>
+      <c r="G876" t="n">
+        <v>3</v>
+      </c>
+      <c r="H876" t="n">
+        <v>15</v>
+      </c>
+      <c r="I876" t="inlineStr"/>
+      <c r="J876" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K876" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L876" t="inlineStr"/>
+      <c r="M876" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N876" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O876" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P876" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q876" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.5</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr"/>
+      <c r="G877" t="n">
+        <v>3</v>
+      </c>
+      <c r="H877" t="n">
+        <v>15</v>
+      </c>
+      <c r="I877" t="inlineStr"/>
+      <c r="J877" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K877" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L877" t="inlineStr"/>
+      <c r="M877" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N877" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O877" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P877" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q877" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr"/>
+      <c r="G878" t="n">
+        <v>3</v>
+      </c>
+      <c r="H878" t="n">
+        <v>15</v>
+      </c>
+      <c r="I878" t="inlineStr"/>
+      <c r="J878" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K878" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L878" t="inlineStr"/>
+      <c r="M878" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N878" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O878" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P878" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q878" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr"/>
+      <c r="G879" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H879" t="inlineStr"/>
+      <c r="I879" t="inlineStr"/>
+      <c r="J879" t="inlineStr"/>
+      <c r="K879" t="inlineStr"/>
+      <c r="L879" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M879" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N879" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O879" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P879" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q879" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr"/>
+      <c r="G880" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H880" t="inlineStr"/>
+      <c r="I880" t="inlineStr"/>
+      <c r="J880" t="inlineStr"/>
+      <c r="K880" t="inlineStr"/>
+      <c r="L880" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M880" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N880" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O880" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P880" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q880" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr"/>
+      <c r="G881" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H881" t="inlineStr"/>
+      <c r="I881" t="inlineStr"/>
+      <c r="J881" t="inlineStr"/>
+      <c r="K881" t="inlineStr"/>
+      <c r="L881" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M881" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N881" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O881" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P881" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q881" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr"/>
+      <c r="G882" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H882" t="inlineStr"/>
+      <c r="I882" t="inlineStr"/>
+      <c r="J882" t="inlineStr"/>
+      <c r="K882" t="inlineStr"/>
+      <c r="L882" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M882" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N882" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O882" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P882" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q882" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr"/>
+      <c r="G883" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="H883" t="inlineStr"/>
+      <c r="I883" t="inlineStr"/>
+      <c r="J883" t="inlineStr"/>
+      <c r="K883" t="inlineStr"/>
+      <c r="L883" t="inlineStr"/>
+      <c r="M883" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N883" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O883" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P883" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q883" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr"/>
+      <c r="G884" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H884" t="inlineStr"/>
+      <c r="I884" t="inlineStr"/>
+      <c r="J884" t="inlineStr"/>
+      <c r="K884" t="inlineStr"/>
+      <c r="L884" t="inlineStr"/>
+      <c r="M884" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N884" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O884" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P884" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q884" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr"/>
+      <c r="G885" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H885" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I885" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J885" t="inlineStr"/>
+      <c r="K885" t="inlineStr"/>
+      <c r="L885" t="n">
+        <v>1</v>
+      </c>
+      <c r="M885" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N885" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O885" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P885" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q885" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr"/>
+      <c r="G886" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H886" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I886" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J886" t="inlineStr"/>
+      <c r="K886" t="inlineStr"/>
+      <c r="L886" t="n">
+        <v>1</v>
+      </c>
+      <c r="M886" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N886" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O886" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P886" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q886" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr"/>
+      <c r="G887" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H887" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I887" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J887" t="inlineStr"/>
+      <c r="K887" t="inlineStr"/>
+      <c r="L887" t="n">
+        <v>1</v>
+      </c>
+      <c r="M887" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N887" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O887" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P887" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q887" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr"/>
+      <c r="G888" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H888" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I888" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J888" t="inlineStr"/>
+      <c r="K888" t="inlineStr"/>
+      <c r="L888" t="n">
+        <v>1</v>
+      </c>
+      <c r="M888" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N888" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O888" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P888" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q888" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr"/>
+      <c r="G889" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H889" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I889" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J889" t="inlineStr"/>
+      <c r="K889" t="inlineStr"/>
+      <c r="L889" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M889" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N889" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O889" t="inlineStr">
+        <is>
+          <t>$0.054 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P889" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q889" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr"/>
+      <c r="G890" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H890" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I890" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J890" t="inlineStr"/>
+      <c r="K890" t="inlineStr"/>
+      <c r="L890" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M890" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N890" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O890" t="inlineStr">
+        <is>
+          <t>$0.054 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P890" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q890" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr"/>
+      <c r="G891" t="n">
+        <v>1</v>
+      </c>
+      <c r="H891" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I891" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J891" t="inlineStr"/>
+      <c r="K891" t="inlineStr"/>
+      <c r="L891" t="n">
+        <v>1</v>
+      </c>
+      <c r="M891" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N891" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O891" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P891" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q891" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr"/>
+      <c r="G892" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H892" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I892" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J892" t="inlineStr"/>
+      <c r="K892" t="inlineStr"/>
+      <c r="L892" t="n">
+        <v>1</v>
+      </c>
+      <c r="M892" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N892" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O892" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P892" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q892" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr"/>
+      <c r="G893" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H893" t="inlineStr"/>
+      <c r="I893" t="inlineStr"/>
+      <c r="J893" t="inlineStr"/>
+      <c r="K893" t="inlineStr"/>
+      <c r="L893" t="inlineStr"/>
+      <c r="M893" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N893" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O893" t="inlineStr"/>
+      <c r="P893" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q893" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr"/>
+      <c r="G894" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H894" t="inlineStr"/>
+      <c r="I894" t="inlineStr"/>
+      <c r="J894" t="inlineStr"/>
+      <c r="K894" t="inlineStr"/>
+      <c r="L894" t="inlineStr"/>
+      <c r="M894" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N894" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O894" t="inlineStr"/>
+      <c r="P894" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q894" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr"/>
+      <c r="G895" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H895" t="inlineStr"/>
+      <c r="I895" t="inlineStr"/>
+      <c r="J895" t="inlineStr"/>
+      <c r="K895" t="inlineStr"/>
+      <c r="L895" t="inlineStr"/>
+      <c r="M895" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N895" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O895" t="inlineStr"/>
+      <c r="P895" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q895" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr"/>
+      <c r="G896" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H896" t="inlineStr"/>
+      <c r="I896" t="inlineStr"/>
+      <c r="J896" t="inlineStr"/>
+      <c r="K896" t="inlineStr"/>
+      <c r="L896" t="inlineStr"/>
+      <c r="M896" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N896" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O896" t="inlineStr"/>
+      <c r="P896" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q896" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Preview TTS</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr"/>
+      <c r="G897" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H897" t="inlineStr"/>
+      <c r="I897" t="inlineStr"/>
+      <c r="J897" t="inlineStr"/>
+      <c r="K897" t="inlineStr"/>
+      <c r="L897" t="inlineStr"/>
+      <c r="M897" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N897" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O897" t="inlineStr"/>
+      <c r="P897" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q897" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Preview TTS</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr"/>
+      <c r="G898" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H898" t="inlineStr"/>
+      <c r="I898" t="inlineStr"/>
+      <c r="J898" t="inlineStr"/>
+      <c r="K898" t="inlineStr"/>
+      <c r="L898" t="inlineStr"/>
+      <c r="M898" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N898" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O898" t="inlineStr"/>
+      <c r="P898" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q898" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr"/>
+      <c r="G899" t="inlineStr"/>
+      <c r="H899" t="n">
+        <v>5</v>
+      </c>
+      <c r="I899" t="inlineStr"/>
+      <c r="J899" t="inlineStr"/>
+      <c r="K899" t="inlineStr"/>
+      <c r="L899" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M899" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N899" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O899" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P899" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q899" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr"/>
+      <c r="G900" t="inlineStr"/>
+      <c r="H900" t="n">
+        <v>5</v>
+      </c>
+      <c r="I900" t="inlineStr"/>
+      <c r="J900" t="inlineStr"/>
+      <c r="K900" t="inlineStr"/>
+      <c r="L900" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M900" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N900" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O900" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P900" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q900" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr"/>
+      <c r="G901" t="inlineStr"/>
+      <c r="H901" t="n">
+        <v>18</v>
+      </c>
+      <c r="I901" t="inlineStr"/>
+      <c r="J901" t="inlineStr"/>
+      <c r="K901" t="inlineStr"/>
+      <c r="L901" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M901" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N901" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O901" t="inlineStr">
+        <is>
+          <t>$0.225, prompts &lt;= 200k tokens $0.45, prompts &gt; 200k $8.10 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P901" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q901" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr"/>
+      <c r="G902" t="inlineStr"/>
+      <c r="H902" t="n">
+        <v>10</v>
+      </c>
+      <c r="I902" t="inlineStr"/>
+      <c r="J902" t="inlineStr"/>
+      <c r="K902" t="inlineStr"/>
+      <c r="L902" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M902" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N902" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O902" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P902" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q902" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro Preview TTS</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr"/>
+      <c r="G903" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H903" t="inlineStr"/>
+      <c r="I903" t="inlineStr"/>
+      <c r="J903" t="inlineStr"/>
+      <c r="K903" t="inlineStr"/>
+      <c r="L903" t="inlineStr"/>
+      <c r="M903" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N903" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O903" t="inlineStr"/>
+      <c r="P903" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q903" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro Preview TTS</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr"/>
+      <c r="G904" t="n">
+        <v>1</v>
+      </c>
+      <c r="H904" t="inlineStr"/>
+      <c r="I904" t="inlineStr"/>
+      <c r="J904" t="inlineStr"/>
+      <c r="K904" t="inlineStr"/>
+      <c r="L904" t="inlineStr"/>
+      <c r="M904" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N904" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O904" t="inlineStr"/>
+      <c r="P904" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q904" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr"/>
+      <c r="G905" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H905" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I905" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J905" t="inlineStr"/>
+      <c r="K905" t="inlineStr"/>
+      <c r="L905" t="n">
+        <v>1</v>
+      </c>
+      <c r="M905" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N905" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O905" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P905" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q905" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr"/>
+      <c r="G906" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H906" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I906" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J906" t="inlineStr"/>
+      <c r="K906" t="inlineStr"/>
+      <c r="L906" t="n">
+        <v>1</v>
+      </c>
+      <c r="M906" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N906" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O906" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P906" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q906" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr"/>
+      <c r="G907" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H907" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I907" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J907" t="inlineStr"/>
+      <c r="K907" t="inlineStr"/>
+      <c r="L907" t="n">
+        <v>1</v>
+      </c>
+      <c r="M907" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N907" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O907" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P907" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q907" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr"/>
+      <c r="G908" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H908" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I908" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J908" t="inlineStr"/>
+      <c r="K908" t="inlineStr"/>
+      <c r="L908" t="n">
+        <v>1</v>
+      </c>
+      <c r="M908" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N908" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O908" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P908" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q908" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr"/>
+      <c r="G909" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H909" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I909" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J909" t="inlineStr"/>
+      <c r="K909" t="inlineStr"/>
+      <c r="L909" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M909" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N909" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O909" t="inlineStr">
+        <is>
+          <t>$0.09 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P909" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q909" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr"/>
+      <c r="G910" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H910" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I910" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J910" t="inlineStr"/>
+      <c r="K910" t="inlineStr"/>
+      <c r="L910" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M910" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N910" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O910" t="inlineStr">
+        <is>
+          <t>$0.09 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P910" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q910" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr"/>
+      <c r="G911" t="n">
+        <v>1</v>
+      </c>
+      <c r="H911" t="n">
+        <v>3</v>
+      </c>
+      <c r="I911" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J911" t="inlineStr"/>
+      <c r="K911" t="inlineStr"/>
+      <c r="L911" t="n">
+        <v>1</v>
+      </c>
+      <c r="M911" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N911" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O911" t="inlineStr">
+        <is>
+          <t>$0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P911" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q911" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr"/>
+      <c r="G912" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H912" t="n">
+        <v>3</v>
+      </c>
+      <c r="I912" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J912" t="inlineStr"/>
+      <c r="K912" t="inlineStr"/>
+      <c r="L912" t="n">
+        <v>1</v>
+      </c>
+      <c r="M912" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N912" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O912" t="inlineStr">
+        <is>
+          <t>$0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P912" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q912" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr"/>
+      <c r="G913" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H913" t="inlineStr"/>
+      <c r="I913" t="inlineStr"/>
+      <c r="J913" t="inlineStr"/>
+      <c r="K913" t="inlineStr"/>
+      <c r="L913" t="inlineStr"/>
+      <c r="M913" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N913" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O913" t="inlineStr"/>
+      <c r="P913" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q913" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr"/>
+      <c r="G914" t="n">
+        <v>1</v>
+      </c>
+      <c r="H914" t="inlineStr"/>
+      <c r="I914" t="inlineStr"/>
+      <c r="J914" t="inlineStr"/>
+      <c r="K914" t="inlineStr"/>
+      <c r="L914" t="inlineStr"/>
+      <c r="M914" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N914" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O914" t="inlineStr"/>
+      <c r="P914" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q914" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr"/>
+      <c r="G915" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H915" t="inlineStr"/>
+      <c r="I915" t="inlineStr"/>
+      <c r="J915" t="inlineStr"/>
+      <c r="K915" t="inlineStr"/>
+      <c r="L915" t="inlineStr"/>
+      <c r="M915" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N915" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O915" t="inlineStr"/>
+      <c r="P915" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q915" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr"/>
+      <c r="G916" t="n">
+        <v>1</v>
+      </c>
+      <c r="H916" t="inlineStr"/>
+      <c r="I916" t="inlineStr"/>
+      <c r="J916" t="inlineStr"/>
+      <c r="K916" t="inlineStr"/>
+      <c r="L916" t="inlineStr"/>
+      <c r="M916" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N916" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O916" t="inlineStr"/>
+      <c r="P916" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q916" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr"/>
+      <c r="G917" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H917" t="inlineStr"/>
+      <c r="I917" t="inlineStr"/>
+      <c r="J917" t="inlineStr"/>
+      <c r="K917" t="inlineStr"/>
+      <c r="L917" t="inlineStr"/>
+      <c r="M917" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N917" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O917" t="inlineStr"/>
+      <c r="P917" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q917" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr"/>
+      <c r="G918" t="n">
+        <v>2</v>
+      </c>
+      <c r="H918" t="inlineStr"/>
+      <c r="I918" t="inlineStr"/>
+      <c r="J918" t="inlineStr"/>
+      <c r="K918" t="inlineStr"/>
+      <c r="L918" t="inlineStr"/>
+      <c r="M918" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N918" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O918" t="inlineStr"/>
+      <c r="P918" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q918" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>text, image</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr"/>
+      <c r="G919" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H919" t="inlineStr"/>
+      <c r="I919" t="inlineStr"/>
+      <c r="J919" t="inlineStr"/>
+      <c r="K919" t="inlineStr"/>
+      <c r="L919" t="inlineStr"/>
+      <c r="M919" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N919" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O919" t="inlineStr"/>
+      <c r="P919" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q919" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr"/>
+      <c r="G920" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H920" t="inlineStr"/>
+      <c r="I920" t="inlineStr"/>
+      <c r="J920" t="inlineStr"/>
+      <c r="K920" t="inlineStr"/>
+      <c r="L920" t="inlineStr"/>
+      <c r="M920" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N920" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O920" t="inlineStr"/>
+      <c r="P920" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q920" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash TTS Preview</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr"/>
+      <c r="G921" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H921" t="inlineStr"/>
+      <c r="I921" t="inlineStr"/>
+      <c r="J921" t="inlineStr"/>
+      <c r="K921" t="inlineStr"/>
+      <c r="L921" t="inlineStr"/>
+      <c r="M921" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N921" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O921" t="inlineStr"/>
+      <c r="P921" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q921" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash TTS Preview</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr"/>
+      <c r="G922" t="n">
+        <v>1</v>
+      </c>
+      <c r="H922" t="inlineStr"/>
+      <c r="I922" t="inlineStr"/>
+      <c r="J922" t="inlineStr"/>
+      <c r="K922" t="inlineStr"/>
+      <c r="L922" t="inlineStr"/>
+      <c r="M922" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N922" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O922" t="inlineStr"/>
+      <c r="P922" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q922" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr"/>
+      <c r="G923" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H923" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I923" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J923" t="inlineStr"/>
+      <c r="K923" t="inlineStr"/>
+      <c r="L923" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M923" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N923" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O923" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P923" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q923" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr"/>
+      <c r="G924" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H924" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I924" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J924" t="inlineStr"/>
+      <c r="K924" t="inlineStr"/>
+      <c r="L924" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M924" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N924" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O924" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P924" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q924" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr"/>
+      <c r="G925" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H925" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I925" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J925" t="inlineStr"/>
+      <c r="K925" t="inlineStr"/>
+      <c r="L925" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M925" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N925" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O925" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P925" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q925" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr"/>
+      <c r="G926" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H926" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I926" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J926" t="inlineStr"/>
+      <c r="K926" t="inlineStr"/>
+      <c r="L926" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M926" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N926" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O926" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P926" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q926" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr"/>
+      <c r="G927" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H927" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I927" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J927" t="inlineStr"/>
+      <c r="K927" t="inlineStr"/>
+      <c r="L927" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M927" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N927" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O927" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P927" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q927" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr"/>
+      <c r="G928" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H928" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I928" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J928" t="inlineStr"/>
+      <c r="K928" t="inlineStr"/>
+      <c r="L928" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M928" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N928" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O928" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P928" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q928" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr"/>
+      <c r="G929" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H929" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I929" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J929" t="inlineStr"/>
+      <c r="K929" t="inlineStr"/>
+      <c r="L929" t="n">
+        <v>1</v>
+      </c>
+      <c r="M929" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N929" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O929" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P929" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q929" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr"/>
+      <c r="G930" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H930" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I930" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J930" t="inlineStr"/>
+      <c r="K930" t="inlineStr"/>
+      <c r="L930" t="n">
+        <v>1</v>
+      </c>
+      <c r="M930" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N930" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O930" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P930" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q930" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr"/>
+      <c r="G931" t="inlineStr"/>
+      <c r="H931" t="n">
+        <v>6</v>
+      </c>
+      <c r="I931" t="inlineStr"/>
+      <c r="J931" t="inlineStr"/>
+      <c r="K931" t="inlineStr"/>
+      <c r="L931" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M931" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N931" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O931" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P931" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q931" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr"/>
+      <c r="G932" t="inlineStr"/>
+      <c r="H932" t="n">
+        <v>6</v>
+      </c>
+      <c r="I932" t="inlineStr"/>
+      <c r="J932" t="inlineStr"/>
+      <c r="K932" t="inlineStr"/>
+      <c r="L932" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M932" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N932" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O932" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P932" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q932" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr"/>
+      <c r="G933" t="inlineStr"/>
+      <c r="H933" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I933" t="inlineStr"/>
+      <c r="J933" t="inlineStr"/>
+      <c r="K933" t="inlineStr"/>
+      <c r="L933" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M933" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N933" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O933" t="inlineStr">
+        <is>
+          <t>$0.36, prompts &lt;= 200k tokens $0.72, prompts &gt; 200k $8.10 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P933" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q933" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr"/>
+      <c r="G934" t="inlineStr"/>
+      <c r="H934" t="n">
+        <v>12</v>
+      </c>
+      <c r="I934" t="inlineStr"/>
+      <c r="J934" t="inlineStr"/>
+      <c r="K934" t="inlineStr"/>
+      <c r="L934" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M934" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N934" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O934" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P934" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q934" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr"/>
+      <c r="G935" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H935" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I935" t="inlineStr"/>
+      <c r="J935" t="inlineStr"/>
+      <c r="K935" t="inlineStr"/>
+      <c r="L935" t="n">
+        <v>1</v>
+      </c>
+      <c r="M935" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N935" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O935" t="inlineStr">
+        <is>
+          <t>$0.075 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P935" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q935" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr"/>
+      <c r="G936" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H936" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I936" t="inlineStr"/>
+      <c r="J936" t="inlineStr"/>
+      <c r="K936" t="inlineStr"/>
+      <c r="L936" t="n">
+        <v>1</v>
+      </c>
+      <c r="M936" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N936" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O936" t="inlineStr">
+        <is>
+          <t>$0.08 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P936" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q936" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr"/>
+      <c r="G937" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H937" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I937" t="inlineStr"/>
+      <c r="J937" t="inlineStr"/>
+      <c r="K937" t="inlineStr"/>
+      <c r="L937" t="n">
+        <v>1</v>
+      </c>
+      <c r="M937" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N937" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O937" t="inlineStr">
+        <is>
+          <t>$0.27 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P937" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q937" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr"/>
+      <c r="G938" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H938" t="n">
+        <v>9</v>
+      </c>
+      <c r="I938" t="inlineStr"/>
+      <c r="J938" t="inlineStr"/>
+      <c r="K938" t="inlineStr"/>
+      <c r="L938" t="n">
+        <v>1</v>
+      </c>
+      <c r="M938" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N938" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O938" t="inlineStr">
+        <is>
+          <t>$0.15 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P938" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q938" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Gemini Embedding</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>embedding</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr"/>
+      <c r="G939" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H939" t="inlineStr"/>
+      <c r="I939" t="inlineStr"/>
+      <c r="J939" t="inlineStr"/>
+      <c r="K939" t="inlineStr"/>
+      <c r="L939" t="inlineStr"/>
+      <c r="M939" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N939" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O939" t="inlineStr"/>
+      <c r="P939" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q939" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Gemini Embedding</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>embedding</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr"/>
+      <c r="G940" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H940" t="inlineStr"/>
+      <c r="I940" t="inlineStr"/>
+      <c r="J940" t="inlineStr"/>
+      <c r="K940" t="inlineStr"/>
+      <c r="L940" t="inlineStr"/>
+      <c r="M940" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N940" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O940" t="inlineStr"/>
+      <c r="P940" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q940" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr"/>
+      <c r="G941" t="n">
+        <v>1</v>
+      </c>
+      <c r="H941" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I941" t="inlineStr"/>
+      <c r="J941" t="inlineStr"/>
+      <c r="K941" t="inlineStr"/>
+      <c r="L941" t="inlineStr"/>
+      <c r="M941" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N941" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O941" t="inlineStr"/>
+      <c r="P941" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q941" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr"/>
+      <c r="G942" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H942" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I942" t="inlineStr"/>
+      <c r="J942" t="inlineStr"/>
+      <c r="K942" t="inlineStr"/>
+      <c r="L942" t="inlineStr"/>
+      <c r="M942" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N942" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O942" t="inlineStr"/>
+      <c r="P942" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q942" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr"/>
+      <c r="G943" t="n">
+        <v>2</v>
+      </c>
+      <c r="H943" t="n">
+        <v>5</v>
+      </c>
+      <c r="I943" t="inlineStr"/>
+      <c r="J943" t="inlineStr"/>
+      <c r="K943" t="inlineStr"/>
+      <c r="L943" t="inlineStr"/>
+      <c r="M943" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N943" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O943" t="inlineStr"/>
+      <c r="P943" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q943" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr"/>
+      <c r="G944" t="n">
+        <v>1</v>
+      </c>
+      <c r="H944" t="n">
+        <v>5</v>
+      </c>
+      <c r="I944" t="inlineStr"/>
+      <c r="J944" t="inlineStr"/>
+      <c r="K944" t="inlineStr"/>
+      <c r="L944" t="inlineStr"/>
+      <c r="M944" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N944" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O944" t="inlineStr"/>
+      <c r="P944" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q944" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>chat-latest</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>chat</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>tools</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr"/>
+      <c r="G945" t="n">
+        <v>5</v>
+      </c>
+      <c r="H945" t="n">
+        <v>30</v>
+      </c>
+      <c r="I945" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J945" t="inlineStr"/>
+      <c r="K945" t="inlineStr"/>
+      <c r="L945" t="inlineStr"/>
+      <c r="M945" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N945" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O945" t="inlineStr">
+        <is>
+          <t>Video generation models | Transcription models | Prices per 1M tokens unless noted. | Tools</t>
+        </is>
+      </c>
+      <c r="P945" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q945" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>computer-use-preview</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>computer</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr"/>
+      <c r="G946" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H946" t="n">
+        <v>6</v>
+      </c>
+      <c r="I946" t="inlineStr"/>
+      <c r="J946" t="inlineStr"/>
+      <c r="K946" t="inlineStr"/>
+      <c r="L946" t="inlineStr"/>
+      <c r="M946" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N946" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O946" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P946" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q946" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini-transcribe</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>video-generation-models</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr"/>
+      <c r="G947" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H947" t="n">
+        <v>5</v>
+      </c>
+      <c r="I947" t="inlineStr"/>
+      <c r="J947" t="inlineStr"/>
+      <c r="K947" t="inlineStr"/>
+      <c r="L947" t="inlineStr"/>
+      <c r="M947" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N947" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O947" t="inlineStr">
+        <is>
+          <t>Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models | Video generation models</t>
+        </is>
+      </c>
+      <c r="P947" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q947" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>gpt-4o-transcribe</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>video-generation-models</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr"/>
+      <c r="G948" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H948" t="n">
+        <v>10</v>
+      </c>
+      <c r="I948" t="inlineStr"/>
+      <c r="J948" t="inlineStr"/>
+      <c r="K948" t="inlineStr"/>
+      <c r="L948" t="inlineStr"/>
+      <c r="M948" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N948" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O948" t="inlineStr">
+        <is>
+          <t>Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models | Video generation models</t>
+        </is>
+      </c>
+      <c r="P948" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q948" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>gpt-5.3-codex</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr"/>
+      <c r="G949" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H949" t="n">
+        <v>28</v>
+      </c>
+      <c r="I949" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J949" t="inlineStr"/>
+      <c r="K949" t="inlineStr"/>
+      <c r="L949" t="inlineStr"/>
+      <c r="M949" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N949" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O949" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P949" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q949" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>gpt-5.3-codex</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>tools</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr"/>
+      <c r="G950" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H950" t="n">
+        <v>14</v>
+      </c>
+      <c r="I950" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="J950" t="inlineStr"/>
+      <c r="K950" t="inlineStr"/>
+      <c r="L950" t="inlineStr"/>
+      <c r="M950" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N950" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O950" t="inlineStr">
+        <is>
+          <t>Video generation models | Transcription models | Prices per 1M tokens unless noted. | Tools</t>
+        </is>
+      </c>
+      <c r="P950" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q950" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G951" t="n">
+        <v>5</v>
+      </c>
+      <c r="H951" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I951" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J951" t="inlineStr"/>
+      <c r="K951" t="inlineStr"/>
+      <c r="L951" t="inlineStr"/>
+      <c r="M951" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N951" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O951" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P951" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q951" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G952" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H952" t="n">
+        <v>15</v>
+      </c>
+      <c r="I952" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J952" t="inlineStr"/>
+      <c r="K952" t="inlineStr"/>
+      <c r="L952" t="inlineStr"/>
+      <c r="M952" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N952" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O952" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P952" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q952" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>gpt-5.4-mini</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G953" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H953" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I953" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J953" t="inlineStr"/>
+      <c r="K953" t="inlineStr"/>
+      <c r="L953" t="inlineStr"/>
+      <c r="M953" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N953" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O953" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P953" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q953" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>gpt-5.4-nano</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G954" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H954" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I954" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J954" t="inlineStr"/>
+      <c r="K954" t="inlineStr"/>
+      <c r="L954" t="inlineStr"/>
+      <c r="M954" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N954" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O954" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P954" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q954" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>gpt-5.4-pro</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G955" t="n">
+        <v>60</v>
+      </c>
+      <c r="H955" t="n">
+        <v>270</v>
+      </c>
+      <c r="I955" t="inlineStr"/>
+      <c r="J955" t="inlineStr"/>
+      <c r="K955" t="inlineStr"/>
+      <c r="L955" t="inlineStr"/>
+      <c r="M955" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N955" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O955" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P955" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q955" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>gpt-5.4-pro</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G956" t="n">
+        <v>30</v>
+      </c>
+      <c r="H956" t="n">
+        <v>180</v>
+      </c>
+      <c r="I956" t="inlineStr"/>
+      <c r="J956" t="inlineStr"/>
+      <c r="K956" t="inlineStr"/>
+      <c r="L956" t="inlineStr"/>
+      <c r="M956" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N956" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O956" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P956" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q956" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G957" t="n">
+        <v>10</v>
+      </c>
+      <c r="H957" t="n">
+        <v>45</v>
+      </c>
+      <c r="I957" t="n">
+        <v>1</v>
+      </c>
+      <c r="J957" t="inlineStr"/>
+      <c r="K957" t="inlineStr"/>
+      <c r="L957" t="inlineStr"/>
+      <c r="M957" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N957" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O957" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P957" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q957" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G958" t="n">
+        <v>5</v>
+      </c>
+      <c r="H958" t="n">
+        <v>30</v>
+      </c>
+      <c r="I958" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J958" t="inlineStr"/>
+      <c r="K958" t="inlineStr"/>
+      <c r="L958" t="inlineStr"/>
+      <c r="M958" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N958" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O958" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P958" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q958" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>gpt-5.5-pro</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G959" t="n">
+        <v>60</v>
+      </c>
+      <c r="H959" t="n">
+        <v>270</v>
+      </c>
+      <c r="I959" t="inlineStr"/>
+      <c r="J959" t="inlineStr"/>
+      <c r="K959" t="inlineStr"/>
+      <c r="L959" t="inlineStr"/>
+      <c r="M959" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N959" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O959" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P959" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q959" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>gpt-5.5-pro</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G960" t="n">
+        <v>30</v>
+      </c>
+      <c r="H960" t="n">
+        <v>180</v>
+      </c>
+      <c r="I960" t="inlineStr"/>
+      <c r="J960" t="inlineStr"/>
+      <c r="K960" t="inlineStr"/>
+      <c r="L960" t="inlineStr"/>
+      <c r="M960" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N960" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O960" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P960" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q960" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr"/>
+      <c r="G961" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H961" t="n">
+        <v>4</v>
+      </c>
+      <c r="I961" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J961" t="inlineStr"/>
+      <c r="K961" t="inlineStr"/>
+      <c r="L961" t="inlineStr"/>
+      <c r="M961" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N961" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O961" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P961" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q961" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr"/>
+      <c r="G962" t="n">
+        <v>1</v>
+      </c>
+      <c r="H962" t="inlineStr"/>
+      <c r="I962" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J962" t="inlineStr"/>
+      <c r="K962" t="inlineStr"/>
+      <c r="L962" t="inlineStr"/>
+      <c r="M962" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N962" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O962" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P962" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q962" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr"/>
+      <c r="G963" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H963" t="n">
+        <v>8</v>
+      </c>
+      <c r="I963" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J963" t="inlineStr"/>
+      <c r="K963" t="inlineStr"/>
+      <c r="L963" t="inlineStr"/>
+      <c r="M963" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N963" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O963" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P963" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q963" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr"/>
+      <c r="G964" t="n">
+        <v>2</v>
+      </c>
+      <c r="H964" t="inlineStr"/>
+      <c r="I964" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J964" t="inlineStr"/>
+      <c r="K964" t="inlineStr"/>
+      <c r="L964" t="inlineStr"/>
+      <c r="M964" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N964" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O964" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P964" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q964" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr"/>
+      <c r="G965" t="n">
+        <v>4</v>
+      </c>
+      <c r="H965" t="n">
+        <v>16</v>
+      </c>
+      <c r="I965" t="n">
+        <v>1</v>
+      </c>
+      <c r="J965" t="inlineStr"/>
+      <c r="K965" t="inlineStr"/>
+      <c r="L965" t="inlineStr"/>
+      <c r="M965" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N965" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O965" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P965" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q965" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr"/>
+      <c r="G966" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H966" t="n">
+        <v>5</v>
+      </c>
+      <c r="I966" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J966" t="inlineStr"/>
+      <c r="K966" t="inlineStr"/>
+      <c r="L966" t="inlineStr"/>
+      <c r="M966" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N966" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O966" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P966" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q966" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr"/>
+      <c r="G967" t="n">
+        <v>8</v>
+      </c>
+      <c r="H967" t="n">
+        <v>32</v>
+      </c>
+      <c r="I967" t="n">
+        <v>2</v>
+      </c>
+      <c r="J967" t="inlineStr"/>
+      <c r="K967" t="inlineStr"/>
+      <c r="L967" t="inlineStr"/>
+      <c r="M967" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N967" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O967" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P967" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q967" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr"/>
+      <c r="G968" t="n">
+        <v>5</v>
+      </c>
+      <c r="H968" t="n">
+        <v>10</v>
+      </c>
+      <c r="I968" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J968" t="inlineStr"/>
+      <c r="K968" t="inlineStr"/>
+      <c r="L968" t="inlineStr"/>
+      <c r="M968" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N968" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O968" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P968" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q968" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr"/>
+      <c r="G969" t="n">
+        <v>4</v>
+      </c>
+      <c r="H969" t="n">
+        <v>15</v>
+      </c>
+      <c r="I969" t="n">
+        <v>1</v>
+      </c>
+      <c r="J969" t="inlineStr"/>
+      <c r="K969" t="inlineStr"/>
+      <c r="L969" t="inlineStr"/>
+      <c r="M969" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N969" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O969" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P969" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q969" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr"/>
+      <c r="G970" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H970" t="inlineStr"/>
+      <c r="I970" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="J970" t="inlineStr"/>
+      <c r="K970" t="inlineStr"/>
+      <c r="L970" t="inlineStr"/>
+      <c r="M970" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N970" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O970" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P970" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q970" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr"/>
+      <c r="G971" t="n">
+        <v>8</v>
+      </c>
+      <c r="H971" t="n">
+        <v>30</v>
+      </c>
+      <c r="I971" t="n">
+        <v>2</v>
+      </c>
+      <c r="J971" t="inlineStr"/>
+      <c r="K971" t="inlineStr"/>
+      <c r="L971" t="inlineStr"/>
+      <c r="M971" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N971" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O971" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P971" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q971" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr"/>
+      <c r="G972" t="n">
+        <v>5</v>
+      </c>
+      <c r="H972" t="inlineStr"/>
+      <c r="I972" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J972" t="inlineStr"/>
+      <c r="K972" t="inlineStr"/>
+      <c r="L972" t="inlineStr"/>
+      <c r="M972" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N972" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O972" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P972" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q972" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>o3-deep-research</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr"/>
+      <c r="G973" t="n">
+        <v>5</v>
+      </c>
+      <c r="H973" t="n">
+        <v>20</v>
+      </c>
+      <c r="I973" t="inlineStr"/>
+      <c r="J973" t="inlineStr"/>
+      <c r="K973" t="inlineStr"/>
+      <c r="L973" t="inlineStr"/>
+      <c r="M973" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N973" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O973" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P973" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q973" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>all-fine-tuned-models-will-remain-available-for-inference-until-their-base-models-are-deprecated-the-full-timeline-is-here</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr"/>
+      <c r="G974" t="n">
+        <v>2</v>
+      </c>
+      <c r="H974" t="n">
+        <v>8</v>
+      </c>
+      <c r="I974" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J974" t="inlineStr"/>
+      <c r="K974" t="inlineStr"/>
+      <c r="L974" t="inlineStr"/>
+      <c r="M974" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N974" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O974" t="inlineStr">
+        <is>
+          <t>Specialized models | Finetuning | OpenAI is winding down the fine-tuning platform. The platform is no longer accessible to new users, but existing users of the fine-tuning platform will be able to create training jobs for the coming months. | All fine-tuned models will remain available for inference until their base models are deprecated. The full timeline is here .</t>
+        </is>
+      </c>
+      <c r="P974" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q974" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr"/>
+      <c r="G975" t="n">
+        <v>4</v>
+      </c>
+      <c r="H975" t="n">
+        <v>16</v>
+      </c>
+      <c r="I975" t="n">
+        <v>1</v>
+      </c>
+      <c r="J975" t="inlineStr"/>
+      <c r="K975" t="inlineStr"/>
+      <c r="L975" t="inlineStr"/>
+      <c r="M975" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N975" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O975" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P975" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q975" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16 with data sharing</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>all-fine-tuned-models-will-remain-available-for-inference-until-their-base-models-are-deprecated-the-full-timeline-is-here</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr"/>
+      <c r="G976" t="n">
+        <v>1</v>
+      </c>
+      <c r="H976" t="n">
+        <v>4</v>
+      </c>
+      <c r="I976" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J976" t="inlineStr"/>
+      <c r="K976" t="inlineStr"/>
+      <c r="L976" t="inlineStr"/>
+      <c r="M976" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N976" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O976" t="inlineStr">
+        <is>
+          <t>Specialized models | Finetuning | OpenAI is winding down the fine-tuning platform. The platform is no longer accessible to new users, but existing users of the fine-tuning platform will be able to create training jobs for the coming months. | All fine-tuned models will remain available for inference until their base models are deprecated. The full timeline is here .</t>
+        </is>
+      </c>
+      <c r="P976" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q976" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16 with data sharing</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr"/>
+      <c r="G977" t="n">
+        <v>2</v>
+      </c>
+      <c r="H977" t="n">
+        <v>8</v>
+      </c>
+      <c r="I977" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J977" t="inlineStr"/>
+      <c r="K977" t="inlineStr"/>
+      <c r="L977" t="inlineStr"/>
+      <c r="M977" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N977" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O977" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P977" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q977" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>o4-mini-deep-research</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr"/>
+      <c r="G978" t="n">
+        <v>1</v>
+      </c>
+      <c r="H978" t="n">
+        <v>4</v>
+      </c>
+      <c r="I978" t="inlineStr"/>
+      <c r="J978" t="inlineStr"/>
+      <c r="K978" t="inlineStr"/>
+      <c r="L978" t="inlineStr"/>
+      <c r="M978" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N978" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O978" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P978" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q978" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>grok-4.20-0309-non-reasoning</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G979" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H979" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I979" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J979" t="inlineStr"/>
+      <c r="K979" t="inlineStr"/>
+      <c r="L979" t="inlineStr"/>
+      <c r="M979" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N979" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O979" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P979" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q979" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>grok-4.20-0309-reasoning</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G980" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H980" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I980" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J980" t="inlineStr"/>
+      <c r="K980" t="inlineStr"/>
+      <c r="L980" t="inlineStr"/>
+      <c r="M980" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N980" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O980" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P980" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q980" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>grok-4.20-multi-agent-0309</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G981" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H981" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I981" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J981" t="inlineStr"/>
+      <c r="K981" t="inlineStr"/>
+      <c r="L981" t="inlineStr"/>
+      <c r="M981" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N981" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O981" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P981" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q981" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>grok-4.3</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G982" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H982" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I982" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J982" t="inlineStr"/>
+      <c r="K982" t="inlineStr"/>
+      <c r="L982" t="inlineStr"/>
+      <c r="M982" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N982" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O982" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P982" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q982" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>grok-build-0.1</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>256k</t>
+        </is>
+      </c>
+      <c r="G983" t="n">
+        <v>1</v>
+      </c>
+      <c r="H983" t="n">
+        <v>2</v>
+      </c>
+      <c r="I983" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J983" t="inlineStr"/>
+      <c r="K983" t="inlineStr"/>
+      <c r="L983" t="inlineStr"/>
+      <c r="M983" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N983" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O983" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P983" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q983" t="inlineStr">
+        <is>
+          <t>2026-05-30T06:56:49+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -64234,7 +71528,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-29T07:14:36+00:00</t>
+          <t>2026-05-30T06:56:49+00:00</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/llm_costs.xlsx
+++ b/data/llm_costs.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q983"/>
+  <dimension ref="A1:Q1097"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -71483,6 +71483,7300 @@
         </is>
       </c>
     </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Claude Haiku 4.5</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>haiku</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr"/>
+      <c r="G984" t="n">
+        <v>1</v>
+      </c>
+      <c r="H984" t="n">
+        <v>5</v>
+      </c>
+      <c r="I984" t="inlineStr"/>
+      <c r="J984" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K984" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L984" t="inlineStr"/>
+      <c r="M984" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N984" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O984" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P984" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q984" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Claude Opus 4</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr"/>
+      <c r="G985" t="n">
+        <v>15</v>
+      </c>
+      <c r="H985" t="n">
+        <v>75</v>
+      </c>
+      <c r="I985" t="inlineStr"/>
+      <c r="J985" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="K985" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L985" t="inlineStr"/>
+      <c r="M985" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N985" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O985" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P985" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q985" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.1</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr"/>
+      <c r="G986" t="n">
+        <v>15</v>
+      </c>
+      <c r="H986" t="n">
+        <v>75</v>
+      </c>
+      <c r="I986" t="inlineStr"/>
+      <c r="J986" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="K986" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L986" t="inlineStr"/>
+      <c r="M986" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N986" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O986" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P986" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q986" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.5</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr"/>
+      <c r="G987" t="n">
+        <v>5</v>
+      </c>
+      <c r="H987" t="n">
+        <v>25</v>
+      </c>
+      <c r="I987" t="inlineStr"/>
+      <c r="J987" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K987" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L987" t="inlineStr"/>
+      <c r="M987" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N987" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O987" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P987" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q987" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.6</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr"/>
+      <c r="G988" t="n">
+        <v>5</v>
+      </c>
+      <c r="H988" t="n">
+        <v>25</v>
+      </c>
+      <c r="I988" t="inlineStr"/>
+      <c r="J988" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K988" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L988" t="inlineStr"/>
+      <c r="M988" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N988" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O988" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P988" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q988" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.8</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr"/>
+      <c r="G989" t="n">
+        <v>5</v>
+      </c>
+      <c r="H989" t="n">
+        <v>25</v>
+      </c>
+      <c r="I989" t="inlineStr"/>
+      <c r="J989" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K989" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L989" t="inlineStr"/>
+      <c r="M989" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N989" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O989" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P989" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q989" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr"/>
+      <c r="G990" t="n">
+        <v>3</v>
+      </c>
+      <c r="H990" t="n">
+        <v>15</v>
+      </c>
+      <c r="I990" t="inlineStr"/>
+      <c r="J990" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K990" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L990" t="inlineStr"/>
+      <c r="M990" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N990" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O990" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P990" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q990" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.5</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr"/>
+      <c r="G991" t="n">
+        <v>3</v>
+      </c>
+      <c r="H991" t="n">
+        <v>15</v>
+      </c>
+      <c r="I991" t="inlineStr"/>
+      <c r="J991" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K991" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L991" t="inlineStr"/>
+      <c r="M991" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N991" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O991" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P991" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q991" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr"/>
+      <c r="G992" t="n">
+        <v>3</v>
+      </c>
+      <c r="H992" t="n">
+        <v>15</v>
+      </c>
+      <c r="I992" t="inlineStr"/>
+      <c r="J992" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K992" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L992" t="inlineStr"/>
+      <c r="M992" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N992" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O992" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P992" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q992" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr"/>
+      <c r="G993" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H993" t="inlineStr"/>
+      <c r="I993" t="inlineStr"/>
+      <c r="J993" t="inlineStr"/>
+      <c r="K993" t="inlineStr"/>
+      <c r="L993" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M993" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N993" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O993" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P993" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q993" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr"/>
+      <c r="G994" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H994" t="inlineStr"/>
+      <c r="I994" t="inlineStr"/>
+      <c r="J994" t="inlineStr"/>
+      <c r="K994" t="inlineStr"/>
+      <c r="L994" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M994" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N994" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O994" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P994" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q994" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr"/>
+      <c r="G995" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H995" t="inlineStr"/>
+      <c r="I995" t="inlineStr"/>
+      <c r="J995" t="inlineStr"/>
+      <c r="K995" t="inlineStr"/>
+      <c r="L995" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M995" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N995" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O995" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P995" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q995" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr"/>
+      <c r="G996" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H996" t="inlineStr"/>
+      <c r="I996" t="inlineStr"/>
+      <c r="J996" t="inlineStr"/>
+      <c r="K996" t="inlineStr"/>
+      <c r="L996" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M996" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N996" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O996" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P996" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q996" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr"/>
+      <c r="G997" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="H997" t="inlineStr"/>
+      <c r="I997" t="inlineStr"/>
+      <c r="J997" t="inlineStr"/>
+      <c r="K997" t="inlineStr"/>
+      <c r="L997" t="inlineStr"/>
+      <c r="M997" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N997" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O997" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P997" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q997" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr"/>
+      <c r="G998" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H998" t="inlineStr"/>
+      <c r="I998" t="inlineStr"/>
+      <c r="J998" t="inlineStr"/>
+      <c r="K998" t="inlineStr"/>
+      <c r="L998" t="inlineStr"/>
+      <c r="M998" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N998" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O998" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P998" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q998" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr"/>
+      <c r="G999" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H999" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I999" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J999" t="inlineStr"/>
+      <c r="K999" t="inlineStr"/>
+      <c r="L999" t="n">
+        <v>1</v>
+      </c>
+      <c r="M999" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N999" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O999" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P999" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q999" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr"/>
+      <c r="G1000" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1000" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I1000" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J1000" t="inlineStr"/>
+      <c r="K1000" t="inlineStr"/>
+      <c r="L1000" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1000" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1000" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1000" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1000" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1000" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr"/>
+      <c r="G1001" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1001" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I1001" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J1001" t="inlineStr"/>
+      <c r="K1001" t="inlineStr"/>
+      <c r="L1001" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1001" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1001" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1001" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1001" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1001" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr"/>
+      <c r="G1002" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1002" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I1002" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J1002" t="inlineStr"/>
+      <c r="K1002" t="inlineStr"/>
+      <c r="L1002" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1002" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1002" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1002" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1002" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1002" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr"/>
+      <c r="G1003" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H1003" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I1003" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J1003" t="inlineStr"/>
+      <c r="K1003" t="inlineStr"/>
+      <c r="L1003" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M1003" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1003" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1003" t="inlineStr">
+        <is>
+          <t>$0.054 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1003" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1003" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr"/>
+      <c r="G1004" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H1004" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I1004" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J1004" t="inlineStr"/>
+      <c r="K1004" t="inlineStr"/>
+      <c r="L1004" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M1004" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1004" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1004" t="inlineStr">
+        <is>
+          <t>$0.054 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1004" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1004" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr"/>
+      <c r="G1005" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1005" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1005" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J1005" t="inlineStr"/>
+      <c r="K1005" t="inlineStr"/>
+      <c r="L1005" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1005" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1005" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1005" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1005" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1005" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr"/>
+      <c r="G1006" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H1006" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1006" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J1006" t="inlineStr"/>
+      <c r="K1006" t="inlineStr"/>
+      <c r="L1006" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1006" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1006" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1006" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1006" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1006" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr"/>
+      <c r="G1007" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1007" t="inlineStr"/>
+      <c r="I1007" t="inlineStr"/>
+      <c r="J1007" t="inlineStr"/>
+      <c r="K1007" t="inlineStr"/>
+      <c r="L1007" t="inlineStr"/>
+      <c r="M1007" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1007" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1007" t="inlineStr"/>
+      <c r="P1007" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1007" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr"/>
+      <c r="G1008" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1008" t="inlineStr"/>
+      <c r="I1008" t="inlineStr"/>
+      <c r="J1008" t="inlineStr"/>
+      <c r="K1008" t="inlineStr"/>
+      <c r="L1008" t="inlineStr"/>
+      <c r="M1008" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1008" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1008" t="inlineStr"/>
+      <c r="P1008" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1008" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr"/>
+      <c r="G1009" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H1009" t="inlineStr"/>
+      <c r="I1009" t="inlineStr"/>
+      <c r="J1009" t="inlineStr"/>
+      <c r="K1009" t="inlineStr"/>
+      <c r="L1009" t="inlineStr"/>
+      <c r="M1009" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1009" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1009" t="inlineStr"/>
+      <c r="P1009" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1009" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr"/>
+      <c r="G1010" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H1010" t="inlineStr"/>
+      <c r="I1010" t="inlineStr"/>
+      <c r="J1010" t="inlineStr"/>
+      <c r="K1010" t="inlineStr"/>
+      <c r="L1010" t="inlineStr"/>
+      <c r="M1010" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1010" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1010" t="inlineStr"/>
+      <c r="P1010" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1010" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Preview TTS</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr"/>
+      <c r="G1011" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1011" t="inlineStr"/>
+      <c r="I1011" t="inlineStr"/>
+      <c r="J1011" t="inlineStr"/>
+      <c r="K1011" t="inlineStr"/>
+      <c r="L1011" t="inlineStr"/>
+      <c r="M1011" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1011" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1011" t="inlineStr"/>
+      <c r="P1011" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1011" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Preview TTS</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr"/>
+      <c r="G1012" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1012" t="inlineStr"/>
+      <c r="I1012" t="inlineStr"/>
+      <c r="J1012" t="inlineStr"/>
+      <c r="K1012" t="inlineStr"/>
+      <c r="L1012" t="inlineStr"/>
+      <c r="M1012" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1012" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1012" t="inlineStr"/>
+      <c r="P1012" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1012" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr"/>
+      <c r="G1013" t="inlineStr"/>
+      <c r="H1013" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1013" t="inlineStr"/>
+      <c r="J1013" t="inlineStr"/>
+      <c r="K1013" t="inlineStr"/>
+      <c r="L1013" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M1013" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1013" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1013" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1013" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1013" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr"/>
+      <c r="G1014" t="inlineStr"/>
+      <c r="H1014" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1014" t="inlineStr"/>
+      <c r="J1014" t="inlineStr"/>
+      <c r="K1014" t="inlineStr"/>
+      <c r="L1014" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M1014" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1014" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1014" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1014" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1014" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr"/>
+      <c r="G1015" t="inlineStr"/>
+      <c r="H1015" t="n">
+        <v>18</v>
+      </c>
+      <c r="I1015" t="inlineStr"/>
+      <c r="J1015" t="inlineStr"/>
+      <c r="K1015" t="inlineStr"/>
+      <c r="L1015" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M1015" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1015" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1015" t="inlineStr">
+        <is>
+          <t>$0.225, prompts &lt;= 200k tokens $0.45, prompts &gt; 200k $8.10 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1015" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1015" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr"/>
+      <c r="G1016" t="inlineStr"/>
+      <c r="H1016" t="n">
+        <v>10</v>
+      </c>
+      <c r="I1016" t="inlineStr"/>
+      <c r="J1016" t="inlineStr"/>
+      <c r="K1016" t="inlineStr"/>
+      <c r="L1016" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M1016" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1016" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1016" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1016" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1016" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro Preview TTS</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr"/>
+      <c r="G1017" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1017" t="inlineStr"/>
+      <c r="I1017" t="inlineStr"/>
+      <c r="J1017" t="inlineStr"/>
+      <c r="K1017" t="inlineStr"/>
+      <c r="L1017" t="inlineStr"/>
+      <c r="M1017" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1017" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1017" t="inlineStr"/>
+      <c r="P1017" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1017" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro Preview TTS</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr"/>
+      <c r="G1018" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1018" t="inlineStr"/>
+      <c r="I1018" t="inlineStr"/>
+      <c r="J1018" t="inlineStr"/>
+      <c r="K1018" t="inlineStr"/>
+      <c r="L1018" t="inlineStr"/>
+      <c r="M1018" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1018" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1018" t="inlineStr"/>
+      <c r="P1018" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1018" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr"/>
+      <c r="G1019" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1019" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I1019" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J1019" t="inlineStr"/>
+      <c r="K1019" t="inlineStr"/>
+      <c r="L1019" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1019" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1019" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1019" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1019" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1019" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr"/>
+      <c r="G1020" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1020" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I1020" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J1020" t="inlineStr"/>
+      <c r="K1020" t="inlineStr"/>
+      <c r="L1020" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1020" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1020" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1020" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1020" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1020" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr"/>
+      <c r="G1021" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1021" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I1021" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J1021" t="inlineStr"/>
+      <c r="K1021" t="inlineStr"/>
+      <c r="L1021" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1021" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1021" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1021" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1021" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1021" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr"/>
+      <c r="G1022" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1022" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I1022" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J1022" t="inlineStr"/>
+      <c r="K1022" t="inlineStr"/>
+      <c r="L1022" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1022" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1022" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1022" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1022" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1022" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr"/>
+      <c r="G1023" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H1023" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I1023" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J1023" t="inlineStr"/>
+      <c r="K1023" t="inlineStr"/>
+      <c r="L1023" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M1023" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1023" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1023" t="inlineStr">
+        <is>
+          <t>$0.09 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1023" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1023" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr"/>
+      <c r="G1024" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H1024" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I1024" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J1024" t="inlineStr"/>
+      <c r="K1024" t="inlineStr"/>
+      <c r="L1024" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M1024" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1024" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1024" t="inlineStr">
+        <is>
+          <t>$0.09 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1024" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1024" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr"/>
+      <c r="G1025" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1025" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1025" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J1025" t="inlineStr"/>
+      <c r="K1025" t="inlineStr"/>
+      <c r="L1025" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1025" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1025" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1025" t="inlineStr">
+        <is>
+          <t>$0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1025" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1025" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr"/>
+      <c r="G1026" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1026" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1026" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J1026" t="inlineStr"/>
+      <c r="K1026" t="inlineStr"/>
+      <c r="L1026" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1026" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1026" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1026" t="inlineStr">
+        <is>
+          <t>$0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1026" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1026" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr"/>
+      <c r="G1027" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H1027" t="inlineStr"/>
+      <c r="I1027" t="inlineStr"/>
+      <c r="J1027" t="inlineStr"/>
+      <c r="K1027" t="inlineStr"/>
+      <c r="L1027" t="inlineStr"/>
+      <c r="M1027" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1027" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1027" t="inlineStr"/>
+      <c r="P1027" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1027" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr"/>
+      <c r="G1028" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1028" t="inlineStr"/>
+      <c r="I1028" t="inlineStr"/>
+      <c r="J1028" t="inlineStr"/>
+      <c r="K1028" t="inlineStr"/>
+      <c r="L1028" t="inlineStr"/>
+      <c r="M1028" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1028" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1028" t="inlineStr"/>
+      <c r="P1028" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1028" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr"/>
+      <c r="G1029" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H1029" t="inlineStr"/>
+      <c r="I1029" t="inlineStr"/>
+      <c r="J1029" t="inlineStr"/>
+      <c r="K1029" t="inlineStr"/>
+      <c r="L1029" t="inlineStr"/>
+      <c r="M1029" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1029" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1029" t="inlineStr"/>
+      <c r="P1029" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1029" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr"/>
+      <c r="G1030" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1030" t="inlineStr"/>
+      <c r="I1030" t="inlineStr"/>
+      <c r="J1030" t="inlineStr"/>
+      <c r="K1030" t="inlineStr"/>
+      <c r="L1030" t="inlineStr"/>
+      <c r="M1030" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1030" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1030" t="inlineStr"/>
+      <c r="P1030" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1030" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr"/>
+      <c r="G1031" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H1031" t="inlineStr"/>
+      <c r="I1031" t="inlineStr"/>
+      <c r="J1031" t="inlineStr"/>
+      <c r="K1031" t="inlineStr"/>
+      <c r="L1031" t="inlineStr"/>
+      <c r="M1031" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1031" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1031" t="inlineStr"/>
+      <c r="P1031" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1031" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr"/>
+      <c r="G1032" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1032" t="inlineStr"/>
+      <c r="I1032" t="inlineStr"/>
+      <c r="J1032" t="inlineStr"/>
+      <c r="K1032" t="inlineStr"/>
+      <c r="L1032" t="inlineStr"/>
+      <c r="M1032" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1032" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1032" t="inlineStr"/>
+      <c r="P1032" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1032" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>text, image</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr"/>
+      <c r="G1033" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1033" t="inlineStr"/>
+      <c r="I1033" t="inlineStr"/>
+      <c r="J1033" t="inlineStr"/>
+      <c r="K1033" t="inlineStr"/>
+      <c r="L1033" t="inlineStr"/>
+      <c r="M1033" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1033" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1033" t="inlineStr"/>
+      <c r="P1033" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1033" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr"/>
+      <c r="G1034" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1034" t="inlineStr"/>
+      <c r="I1034" t="inlineStr"/>
+      <c r="J1034" t="inlineStr"/>
+      <c r="K1034" t="inlineStr"/>
+      <c r="L1034" t="inlineStr"/>
+      <c r="M1034" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1034" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1034" t="inlineStr"/>
+      <c r="P1034" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1034" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash TTS Preview</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr"/>
+      <c r="G1035" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1035" t="inlineStr"/>
+      <c r="I1035" t="inlineStr"/>
+      <c r="J1035" t="inlineStr"/>
+      <c r="K1035" t="inlineStr"/>
+      <c r="L1035" t="inlineStr"/>
+      <c r="M1035" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1035" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1035" t="inlineStr"/>
+      <c r="P1035" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1035" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash TTS Preview</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr"/>
+      <c r="G1036" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1036" t="inlineStr"/>
+      <c r="I1036" t="inlineStr"/>
+      <c r="J1036" t="inlineStr"/>
+      <c r="K1036" t="inlineStr"/>
+      <c r="L1036" t="inlineStr"/>
+      <c r="M1036" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1036" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1036" t="inlineStr"/>
+      <c r="P1036" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1036" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr"/>
+      <c r="G1037" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1037" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I1037" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J1037" t="inlineStr"/>
+      <c r="K1037" t="inlineStr"/>
+      <c r="L1037" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M1037" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1037" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1037" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1037" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1037" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr"/>
+      <c r="G1038" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H1038" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I1038" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J1038" t="inlineStr"/>
+      <c r="K1038" t="inlineStr"/>
+      <c r="L1038" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M1038" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1038" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1038" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1038" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1038" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr"/>
+      <c r="G1039" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1039" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I1039" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J1039" t="inlineStr"/>
+      <c r="K1039" t="inlineStr"/>
+      <c r="L1039" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M1039" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1039" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1039" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1039" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1039" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr"/>
+      <c r="G1040" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H1040" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I1040" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J1040" t="inlineStr"/>
+      <c r="K1040" t="inlineStr"/>
+      <c r="L1040" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M1040" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1040" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1040" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1040" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1040" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr"/>
+      <c r="G1041" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H1041" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I1041" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J1041" t="inlineStr"/>
+      <c r="K1041" t="inlineStr"/>
+      <c r="L1041" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M1041" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1041" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1041" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1041" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1041" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr"/>
+      <c r="G1042" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H1042" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I1042" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J1042" t="inlineStr"/>
+      <c r="K1042" t="inlineStr"/>
+      <c r="L1042" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M1042" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1042" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1042" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1042" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1042" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr"/>
+      <c r="G1043" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1043" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I1043" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J1043" t="inlineStr"/>
+      <c r="K1043" t="inlineStr"/>
+      <c r="L1043" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1043" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1043" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1043" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1043" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1043" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr"/>
+      <c r="G1044" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1044" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I1044" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J1044" t="inlineStr"/>
+      <c r="K1044" t="inlineStr"/>
+      <c r="L1044" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1044" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1044" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1044" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1044" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1044" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr"/>
+      <c r="G1045" t="inlineStr"/>
+      <c r="H1045" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1045" t="inlineStr"/>
+      <c r="J1045" t="inlineStr"/>
+      <c r="K1045" t="inlineStr"/>
+      <c r="L1045" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M1045" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1045" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1045" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1045" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1045" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr"/>
+      <c r="G1046" t="inlineStr"/>
+      <c r="H1046" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1046" t="inlineStr"/>
+      <c r="J1046" t="inlineStr"/>
+      <c r="K1046" t="inlineStr"/>
+      <c r="L1046" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M1046" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1046" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1046" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1046" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1046" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr"/>
+      <c r="G1047" t="inlineStr"/>
+      <c r="H1047" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I1047" t="inlineStr"/>
+      <c r="J1047" t="inlineStr"/>
+      <c r="K1047" t="inlineStr"/>
+      <c r="L1047" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M1047" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1047" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1047" t="inlineStr">
+        <is>
+          <t>$0.36, prompts &lt;= 200k tokens $0.72, prompts &gt; 200k $8.10 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1047" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1047" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr"/>
+      <c r="G1048" t="inlineStr"/>
+      <c r="H1048" t="n">
+        <v>12</v>
+      </c>
+      <c r="I1048" t="inlineStr"/>
+      <c r="J1048" t="inlineStr"/>
+      <c r="K1048" t="inlineStr"/>
+      <c r="L1048" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M1048" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1048" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1048" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1048" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1048" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr"/>
+      <c r="G1049" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H1049" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I1049" t="inlineStr"/>
+      <c r="J1049" t="inlineStr"/>
+      <c r="K1049" t="inlineStr"/>
+      <c r="L1049" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1049" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1049" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1049" t="inlineStr">
+        <is>
+          <t>$0.075 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1049" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1049" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr"/>
+      <c r="G1050" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H1050" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I1050" t="inlineStr"/>
+      <c r="J1050" t="inlineStr"/>
+      <c r="K1050" t="inlineStr"/>
+      <c r="L1050" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1050" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1050" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1050" t="inlineStr">
+        <is>
+          <t>$0.08 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1050" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1050" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr"/>
+      <c r="G1051" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H1051" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I1051" t="inlineStr"/>
+      <c r="J1051" t="inlineStr"/>
+      <c r="K1051" t="inlineStr"/>
+      <c r="L1051" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1051" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1051" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1051" t="inlineStr">
+        <is>
+          <t>$0.27 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1051" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1051" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr"/>
+      <c r="G1052" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H1052" t="n">
+        <v>9</v>
+      </c>
+      <c r="I1052" t="inlineStr"/>
+      <c r="J1052" t="inlineStr"/>
+      <c r="K1052" t="inlineStr"/>
+      <c r="L1052" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1052" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1052" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1052" t="inlineStr">
+        <is>
+          <t>$0.15 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1052" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1052" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Gemini Embedding</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>embedding</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr"/>
+      <c r="G1053" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H1053" t="inlineStr"/>
+      <c r="I1053" t="inlineStr"/>
+      <c r="J1053" t="inlineStr"/>
+      <c r="K1053" t="inlineStr"/>
+      <c r="L1053" t="inlineStr"/>
+      <c r="M1053" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1053" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1053" t="inlineStr"/>
+      <c r="P1053" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1053" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>Gemini Embedding</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>embedding</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr"/>
+      <c r="G1054" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1054" t="inlineStr"/>
+      <c r="I1054" t="inlineStr"/>
+      <c r="J1054" t="inlineStr"/>
+      <c r="K1054" t="inlineStr"/>
+      <c r="L1054" t="inlineStr"/>
+      <c r="M1054" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1054" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1054" t="inlineStr"/>
+      <c r="P1054" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1054" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr"/>
+      <c r="G1055" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1055" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1055" t="inlineStr"/>
+      <c r="J1055" t="inlineStr"/>
+      <c r="K1055" t="inlineStr"/>
+      <c r="L1055" t="inlineStr"/>
+      <c r="M1055" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1055" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1055" t="inlineStr"/>
+      <c r="P1055" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1055" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr"/>
+      <c r="G1056" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1056" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1056" t="inlineStr"/>
+      <c r="J1056" t="inlineStr"/>
+      <c r="K1056" t="inlineStr"/>
+      <c r="L1056" t="inlineStr"/>
+      <c r="M1056" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1056" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1056" t="inlineStr"/>
+      <c r="P1056" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1056" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr"/>
+      <c r="G1057" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1057" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1057" t="inlineStr"/>
+      <c r="J1057" t="inlineStr"/>
+      <c r="K1057" t="inlineStr"/>
+      <c r="L1057" t="inlineStr"/>
+      <c r="M1057" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1057" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1057" t="inlineStr"/>
+      <c r="P1057" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1057" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr"/>
+      <c r="G1058" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1058" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1058" t="inlineStr"/>
+      <c r="J1058" t="inlineStr"/>
+      <c r="K1058" t="inlineStr"/>
+      <c r="L1058" t="inlineStr"/>
+      <c r="M1058" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1058" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1058" t="inlineStr"/>
+      <c r="P1058" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1058" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>chat-latest</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>chat</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>tools</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr"/>
+      <c r="G1059" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1059" t="n">
+        <v>30</v>
+      </c>
+      <c r="I1059" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J1059" t="inlineStr"/>
+      <c r="K1059" t="inlineStr"/>
+      <c r="L1059" t="inlineStr"/>
+      <c r="M1059" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1059" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1059" t="inlineStr">
+        <is>
+          <t>Video generation models | Transcription models | Prices per 1M tokens unless noted. | Tools</t>
+        </is>
+      </c>
+      <c r="P1059" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1059" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>computer-use-preview</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>computer</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr"/>
+      <c r="G1060" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H1060" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1060" t="inlineStr"/>
+      <c r="J1060" t="inlineStr"/>
+      <c r="K1060" t="inlineStr"/>
+      <c r="L1060" t="inlineStr"/>
+      <c r="M1060" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1060" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1060" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P1060" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1060" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini-transcribe</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>video-generation-models</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr"/>
+      <c r="G1061" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1061" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1061" t="inlineStr"/>
+      <c r="J1061" t="inlineStr"/>
+      <c r="K1061" t="inlineStr"/>
+      <c r="L1061" t="inlineStr"/>
+      <c r="M1061" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1061" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1061" t="inlineStr">
+        <is>
+          <t>Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models | Video generation models</t>
+        </is>
+      </c>
+      <c r="P1061" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1061" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>gpt-4o-transcribe</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>video-generation-models</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr"/>
+      <c r="G1062" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1062" t="n">
+        <v>10</v>
+      </c>
+      <c r="I1062" t="inlineStr"/>
+      <c r="J1062" t="inlineStr"/>
+      <c r="K1062" t="inlineStr"/>
+      <c r="L1062" t="inlineStr"/>
+      <c r="M1062" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1062" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1062" t="inlineStr">
+        <is>
+          <t>Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models | Video generation models</t>
+        </is>
+      </c>
+      <c r="P1062" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1062" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>gpt-5.3-codex</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr"/>
+      <c r="G1063" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H1063" t="n">
+        <v>28</v>
+      </c>
+      <c r="I1063" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J1063" t="inlineStr"/>
+      <c r="K1063" t="inlineStr"/>
+      <c r="L1063" t="inlineStr"/>
+      <c r="M1063" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1063" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1063" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P1063" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1063" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>gpt-5.3-codex</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>tools</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr"/>
+      <c r="G1064" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H1064" t="n">
+        <v>14</v>
+      </c>
+      <c r="I1064" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="J1064" t="inlineStr"/>
+      <c r="K1064" t="inlineStr"/>
+      <c r="L1064" t="inlineStr"/>
+      <c r="M1064" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1064" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1064" t="inlineStr">
+        <is>
+          <t>Video generation models | Transcription models | Prices per 1M tokens unless noted. | Tools</t>
+        </is>
+      </c>
+      <c r="P1064" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1064" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G1065" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1065" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I1065" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J1065" t="inlineStr"/>
+      <c r="K1065" t="inlineStr"/>
+      <c r="L1065" t="inlineStr"/>
+      <c r="M1065" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1065" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1065" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1065" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1065" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G1066" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1066" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1066" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J1066" t="inlineStr"/>
+      <c r="K1066" t="inlineStr"/>
+      <c r="L1066" t="inlineStr"/>
+      <c r="M1066" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1066" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1066" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1066" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1066" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>gpt-5.4-mini</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G1067" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H1067" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I1067" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J1067" t="inlineStr"/>
+      <c r="K1067" t="inlineStr"/>
+      <c r="L1067" t="inlineStr"/>
+      <c r="M1067" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1067" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1067" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1067" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1067" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>gpt-5.4-nano</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G1068" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H1068" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I1068" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J1068" t="inlineStr"/>
+      <c r="K1068" t="inlineStr"/>
+      <c r="L1068" t="inlineStr"/>
+      <c r="M1068" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1068" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1068" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1068" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1068" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>gpt-5.4-pro</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G1069" t="n">
+        <v>60</v>
+      </c>
+      <c r="H1069" t="n">
+        <v>270</v>
+      </c>
+      <c r="I1069" t="inlineStr"/>
+      <c r="J1069" t="inlineStr"/>
+      <c r="K1069" t="inlineStr"/>
+      <c r="L1069" t="inlineStr"/>
+      <c r="M1069" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1069" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1069" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1069" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1069" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>gpt-5.4-pro</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G1070" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1070" t="n">
+        <v>180</v>
+      </c>
+      <c r="I1070" t="inlineStr"/>
+      <c r="J1070" t="inlineStr"/>
+      <c r="K1070" t="inlineStr"/>
+      <c r="L1070" t="inlineStr"/>
+      <c r="M1070" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1070" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1070" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1070" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1070" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G1071" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1071" t="n">
+        <v>45</v>
+      </c>
+      <c r="I1071" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1071" t="inlineStr"/>
+      <c r="K1071" t="inlineStr"/>
+      <c r="L1071" t="inlineStr"/>
+      <c r="M1071" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1071" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1071" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1071" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1071" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G1072" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1072" t="n">
+        <v>30</v>
+      </c>
+      <c r="I1072" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J1072" t="inlineStr"/>
+      <c r="K1072" t="inlineStr"/>
+      <c r="L1072" t="inlineStr"/>
+      <c r="M1072" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1072" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1072" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1072" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1072" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>gpt-5.5-pro</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G1073" t="n">
+        <v>60</v>
+      </c>
+      <c r="H1073" t="n">
+        <v>270</v>
+      </c>
+      <c r="I1073" t="inlineStr"/>
+      <c r="J1073" t="inlineStr"/>
+      <c r="K1073" t="inlineStr"/>
+      <c r="L1073" t="inlineStr"/>
+      <c r="M1073" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1073" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1073" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1073" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1073" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>gpt-5.5-pro</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G1074" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1074" t="n">
+        <v>180</v>
+      </c>
+      <c r="I1074" t="inlineStr"/>
+      <c r="J1074" t="inlineStr"/>
+      <c r="K1074" t="inlineStr"/>
+      <c r="L1074" t="inlineStr"/>
+      <c r="M1074" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1074" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1074" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1074" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1074" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr"/>
+      <c r="G1075" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1075" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1075" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J1075" t="inlineStr"/>
+      <c r="K1075" t="inlineStr"/>
+      <c r="L1075" t="inlineStr"/>
+      <c r="M1075" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1075" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1075" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P1075" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1075" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr"/>
+      <c r="G1076" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1076" t="inlineStr"/>
+      <c r="I1076" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J1076" t="inlineStr"/>
+      <c r="K1076" t="inlineStr"/>
+      <c r="L1076" t="inlineStr"/>
+      <c r="M1076" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1076" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1076" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P1076" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1076" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr"/>
+      <c r="G1077" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1077" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1077" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J1077" t="inlineStr"/>
+      <c r="K1077" t="inlineStr"/>
+      <c r="L1077" t="inlineStr"/>
+      <c r="M1077" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1077" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1077" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P1077" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1077" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr"/>
+      <c r="G1078" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1078" t="inlineStr"/>
+      <c r="I1078" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J1078" t="inlineStr"/>
+      <c r="K1078" t="inlineStr"/>
+      <c r="L1078" t="inlineStr"/>
+      <c r="M1078" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1078" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1078" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P1078" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1078" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr"/>
+      <c r="G1079" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1079" t="n">
+        <v>16</v>
+      </c>
+      <c r="I1079" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1079" t="inlineStr"/>
+      <c r="K1079" t="inlineStr"/>
+      <c r="L1079" t="inlineStr"/>
+      <c r="M1079" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1079" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1079" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P1079" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1079" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr"/>
+      <c r="G1080" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1080" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1080" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J1080" t="inlineStr"/>
+      <c r="K1080" t="inlineStr"/>
+      <c r="L1080" t="inlineStr"/>
+      <c r="M1080" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1080" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1080" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P1080" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1080" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr"/>
+      <c r="G1081" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1081" t="n">
+        <v>32</v>
+      </c>
+      <c r="I1081" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1081" t="inlineStr"/>
+      <c r="K1081" t="inlineStr"/>
+      <c r="L1081" t="inlineStr"/>
+      <c r="M1081" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1081" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1081" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P1081" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1081" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr"/>
+      <c r="G1082" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1082" t="n">
+        <v>10</v>
+      </c>
+      <c r="I1082" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J1082" t="inlineStr"/>
+      <c r="K1082" t="inlineStr"/>
+      <c r="L1082" t="inlineStr"/>
+      <c r="M1082" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1082" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1082" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P1082" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1082" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr"/>
+      <c r="G1083" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1083" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1083" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1083" t="inlineStr"/>
+      <c r="K1083" t="inlineStr"/>
+      <c r="L1083" t="inlineStr"/>
+      <c r="M1083" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1083" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1083" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P1083" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1083" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr"/>
+      <c r="G1084" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1084" t="inlineStr"/>
+      <c r="I1084" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="J1084" t="inlineStr"/>
+      <c r="K1084" t="inlineStr"/>
+      <c r="L1084" t="inlineStr"/>
+      <c r="M1084" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1084" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1084" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P1084" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1084" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr"/>
+      <c r="G1085" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1085" t="n">
+        <v>30</v>
+      </c>
+      <c r="I1085" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1085" t="inlineStr"/>
+      <c r="K1085" t="inlineStr"/>
+      <c r="L1085" t="inlineStr"/>
+      <c r="M1085" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1085" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1085" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P1085" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1085" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr"/>
+      <c r="G1086" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1086" t="inlineStr"/>
+      <c r="I1086" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J1086" t="inlineStr"/>
+      <c r="K1086" t="inlineStr"/>
+      <c r="L1086" t="inlineStr"/>
+      <c r="M1086" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1086" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1086" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P1086" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1086" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>o3-deep-research</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr"/>
+      <c r="G1087" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1087" t="n">
+        <v>20</v>
+      </c>
+      <c r="I1087" t="inlineStr"/>
+      <c r="J1087" t="inlineStr"/>
+      <c r="K1087" t="inlineStr"/>
+      <c r="L1087" t="inlineStr"/>
+      <c r="M1087" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1087" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1087" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P1087" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1087" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>all-fine-tuned-models-will-remain-available-for-inference-until-their-base-models-are-deprecated-the-full-timeline-is-here</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr"/>
+      <c r="G1088" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1088" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1088" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J1088" t="inlineStr"/>
+      <c r="K1088" t="inlineStr"/>
+      <c r="L1088" t="inlineStr"/>
+      <c r="M1088" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1088" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1088" t="inlineStr">
+        <is>
+          <t>Specialized models | Finetuning | OpenAI is winding down the fine-tuning platform. The platform is no longer accessible to new users, but existing users of the fine-tuning platform will be able to create training jobs for the coming months. | All fine-tuned models will remain available for inference until their base models are deprecated. The full timeline is here .</t>
+        </is>
+      </c>
+      <c r="P1088" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1088" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr"/>
+      <c r="G1089" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1089" t="n">
+        <v>16</v>
+      </c>
+      <c r="I1089" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1089" t="inlineStr"/>
+      <c r="K1089" t="inlineStr"/>
+      <c r="L1089" t="inlineStr"/>
+      <c r="M1089" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1089" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1089" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P1089" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1089" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16 with data sharing</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>all-fine-tuned-models-will-remain-available-for-inference-until-their-base-models-are-deprecated-the-full-timeline-is-here</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr"/>
+      <c r="G1090" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1090" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1090" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J1090" t="inlineStr"/>
+      <c r="K1090" t="inlineStr"/>
+      <c r="L1090" t="inlineStr"/>
+      <c r="M1090" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1090" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1090" t="inlineStr">
+        <is>
+          <t>Specialized models | Finetuning | OpenAI is winding down the fine-tuning platform. The platform is no longer accessible to new users, but existing users of the fine-tuning platform will be able to create training jobs for the coming months. | All fine-tuned models will remain available for inference until their base models are deprecated. The full timeline is here .</t>
+        </is>
+      </c>
+      <c r="P1090" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1090" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16 with data sharing</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr"/>
+      <c r="G1091" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1091" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1091" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J1091" t="inlineStr"/>
+      <c r="K1091" t="inlineStr"/>
+      <c r="L1091" t="inlineStr"/>
+      <c r="M1091" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1091" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1091" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P1091" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1091" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>o4-mini-deep-research</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr"/>
+      <c r="G1092" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1092" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1092" t="inlineStr"/>
+      <c r="J1092" t="inlineStr"/>
+      <c r="K1092" t="inlineStr"/>
+      <c r="L1092" t="inlineStr"/>
+      <c r="M1092" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1092" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1092" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P1092" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1092" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>grok-4.20-0309-non-reasoning</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G1093" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1093" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1093" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J1093" t="inlineStr"/>
+      <c r="K1093" t="inlineStr"/>
+      <c r="L1093" t="inlineStr"/>
+      <c r="M1093" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1093" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1093" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P1093" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q1093" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>grok-4.20-0309-reasoning</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G1094" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1094" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1094" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J1094" t="inlineStr"/>
+      <c r="K1094" t="inlineStr"/>
+      <c r="L1094" t="inlineStr"/>
+      <c r="M1094" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1094" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1094" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P1094" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q1094" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>grok-4.20-multi-agent-0309</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G1095" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1095" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1095" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J1095" t="inlineStr"/>
+      <c r="K1095" t="inlineStr"/>
+      <c r="L1095" t="inlineStr"/>
+      <c r="M1095" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1095" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1095" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P1095" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q1095" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>grok-4.3</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G1096" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1096" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1096" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J1096" t="inlineStr"/>
+      <c r="K1096" t="inlineStr"/>
+      <c r="L1096" t="inlineStr"/>
+      <c r="M1096" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1096" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1096" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P1096" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q1096" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>grok-build-0.1</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>256k</t>
+        </is>
+      </c>
+      <c r="G1097" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1097" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1097" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J1097" t="inlineStr"/>
+      <c r="K1097" t="inlineStr"/>
+      <c r="L1097" t="inlineStr"/>
+      <c r="M1097" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1097" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1097" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P1097" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q1097" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:14:42+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -71528,7 +78822,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-30T06:56:49+00:00</t>
+          <t>2026-05-31T07:14:42+00:00</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/llm_costs.xlsx
+++ b/data/llm_costs.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1097"/>
+  <dimension ref="A1:Q1211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -78777,6 +78777,7300 @@
         </is>
       </c>
     </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Claude Haiku 4.5</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>haiku</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr"/>
+      <c r="G1098" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1098" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1098" t="inlineStr"/>
+      <c r="J1098" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K1098" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L1098" t="inlineStr"/>
+      <c r="M1098" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1098" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1098" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P1098" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q1098" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Claude Opus 4</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr"/>
+      <c r="G1099" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1099" t="n">
+        <v>75</v>
+      </c>
+      <c r="I1099" t="inlineStr"/>
+      <c r="J1099" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="K1099" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L1099" t="inlineStr"/>
+      <c r="M1099" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1099" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1099" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P1099" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q1099" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.1</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr"/>
+      <c r="G1100" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1100" t="n">
+        <v>75</v>
+      </c>
+      <c r="I1100" t="inlineStr"/>
+      <c r="J1100" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="K1100" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L1100" t="inlineStr"/>
+      <c r="M1100" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1100" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P1100" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q1100" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.5</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr"/>
+      <c r="G1101" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1101" t="n">
+        <v>25</v>
+      </c>
+      <c r="I1101" t="inlineStr"/>
+      <c r="J1101" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K1101" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L1101" t="inlineStr"/>
+      <c r="M1101" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1101" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P1101" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q1101" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.6</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr"/>
+      <c r="G1102" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1102" t="n">
+        <v>25</v>
+      </c>
+      <c r="I1102" t="inlineStr"/>
+      <c r="J1102" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K1102" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L1102" t="inlineStr"/>
+      <c r="M1102" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1102" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P1102" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q1102" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.8</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>opus</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr"/>
+      <c r="G1103" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1103" t="n">
+        <v>25</v>
+      </c>
+      <c r="I1103" t="inlineStr"/>
+      <c r="J1103" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K1103" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L1103" t="inlineStr"/>
+      <c r="M1103" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1103" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P1103" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q1103" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr"/>
+      <c r="G1104" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1104" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1104" t="inlineStr"/>
+      <c r="J1104" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K1104" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L1104" t="inlineStr"/>
+      <c r="M1104" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1104" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P1104" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q1104" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.5</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr"/>
+      <c r="G1105" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1105" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1105" t="inlineStr"/>
+      <c r="J1105" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K1105" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L1105" t="inlineStr"/>
+      <c r="M1105" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1105" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P1105" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q1105" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>sonnet</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr"/>
+      <c r="G1106" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1106" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1106" t="inlineStr"/>
+      <c r="J1106" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K1106" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L1106" t="inlineStr"/>
+      <c r="M1106" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1106" t="inlineStr">
+        <is>
+          <t>Official Anthropic API pricing page.</t>
+        </is>
+      </c>
+      <c r="P1106" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/pricing#api</t>
+        </is>
+      </c>
+      <c r="Q1106" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr"/>
+      <c r="G1107" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H1107" t="inlineStr"/>
+      <c r="I1107" t="inlineStr"/>
+      <c r="J1107" t="inlineStr"/>
+      <c r="K1107" t="inlineStr"/>
+      <c r="L1107" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M1107" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1107" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P1107" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1107" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr"/>
+      <c r="G1108" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H1108" t="inlineStr"/>
+      <c r="I1108" t="inlineStr"/>
+      <c r="J1108" t="inlineStr"/>
+      <c r="K1108" t="inlineStr"/>
+      <c r="L1108" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M1108" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1108" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P1108" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1108" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr"/>
+      <c r="G1109" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H1109" t="inlineStr"/>
+      <c r="I1109" t="inlineStr"/>
+      <c r="J1109" t="inlineStr"/>
+      <c r="K1109" t="inlineStr"/>
+      <c r="L1109" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M1109" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1109" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P1109" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1109" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr"/>
+      <c r="G1110" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H1110" t="inlineStr"/>
+      <c r="I1110" t="inlineStr"/>
+      <c r="J1110" t="inlineStr"/>
+      <c r="K1110" t="inlineStr"/>
+      <c r="L1110" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M1110" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1110" t="inlineStr">
+        <is>
+          <t>$0.025 / 1,000,000 tokens (text/image/video) $0.175 / 1,000,000 tokens (audio)</t>
+        </is>
+      </c>
+      <c r="P1110" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1110" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr"/>
+      <c r="G1111" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="H1111" t="inlineStr"/>
+      <c r="I1111" t="inlineStr"/>
+      <c r="J1111" t="inlineStr"/>
+      <c r="K1111" t="inlineStr"/>
+      <c r="L1111" t="inlineStr"/>
+      <c r="M1111" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1111" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P1111" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1111" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Gemini 2.0 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr"/>
+      <c r="G1112" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H1112" t="inlineStr"/>
+      <c r="I1112" t="inlineStr"/>
+      <c r="J1112" t="inlineStr"/>
+      <c r="K1112" t="inlineStr"/>
+      <c r="L1112" t="inlineStr"/>
+      <c r="M1112" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1112" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P1112" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1112" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr"/>
+      <c r="G1113" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1113" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I1113" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J1113" t="inlineStr"/>
+      <c r="K1113" t="inlineStr"/>
+      <c r="L1113" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1113" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1113" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1113" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1113" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr"/>
+      <c r="G1114" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1114" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I1114" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J1114" t="inlineStr"/>
+      <c r="K1114" t="inlineStr"/>
+      <c r="L1114" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1114" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1114" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1114" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1114" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr"/>
+      <c r="G1115" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1115" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I1115" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J1115" t="inlineStr"/>
+      <c r="K1115" t="inlineStr"/>
+      <c r="L1115" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1115" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1115" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1115" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1115" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr"/>
+      <c r="G1116" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1116" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I1116" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J1116" t="inlineStr"/>
+      <c r="K1116" t="inlineStr"/>
+      <c r="L1116" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1116" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1116" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1116" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1116" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr"/>
+      <c r="G1117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H1117" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I1117" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J1117" t="inlineStr"/>
+      <c r="K1117" t="inlineStr"/>
+      <c r="L1117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M1117" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1117" t="inlineStr">
+        <is>
+          <t>$0.054 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1117" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1117" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr"/>
+      <c r="G1118" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H1118" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I1118" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J1118" t="inlineStr"/>
+      <c r="K1118" t="inlineStr"/>
+      <c r="L1118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M1118" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1118" t="inlineStr">
+        <is>
+          <t>$0.054 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1118" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1118" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr"/>
+      <c r="G1119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1119" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1119" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J1119" t="inlineStr"/>
+      <c r="K1119" t="inlineStr"/>
+      <c r="L1119" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1119" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1119" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1119" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1119" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr"/>
+      <c r="G1120" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H1120" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1120" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J1120" t="inlineStr"/>
+      <c r="K1120" t="inlineStr"/>
+      <c r="L1120" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1120" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1120" t="inlineStr">
+        <is>
+          <t>$0.03 (text / image / video) $0.1 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1120" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1120" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr"/>
+      <c r="G1121" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1121" t="inlineStr"/>
+      <c r="I1121" t="inlineStr"/>
+      <c r="J1121" t="inlineStr"/>
+      <c r="K1121" t="inlineStr"/>
+      <c r="L1121" t="inlineStr"/>
+      <c r="M1121" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1121" t="inlineStr"/>
+      <c r="P1121" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1121" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr"/>
+      <c r="G1122" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1122" t="inlineStr"/>
+      <c r="I1122" t="inlineStr"/>
+      <c r="J1122" t="inlineStr"/>
+      <c r="K1122" t="inlineStr"/>
+      <c r="L1122" t="inlineStr"/>
+      <c r="M1122" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1122" t="inlineStr"/>
+      <c r="P1122" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1122" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr"/>
+      <c r="G1123" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H1123" t="inlineStr"/>
+      <c r="I1123" t="inlineStr"/>
+      <c r="J1123" t="inlineStr"/>
+      <c r="K1123" t="inlineStr"/>
+      <c r="L1123" t="inlineStr"/>
+      <c r="M1123" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1123" t="inlineStr"/>
+      <c r="P1123" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1123" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>text / image</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr"/>
+      <c r="G1124" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H1124" t="inlineStr"/>
+      <c r="I1124" t="inlineStr"/>
+      <c r="J1124" t="inlineStr"/>
+      <c r="K1124" t="inlineStr"/>
+      <c r="L1124" t="inlineStr"/>
+      <c r="M1124" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1124" t="inlineStr"/>
+      <c r="P1124" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1124" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Preview TTS</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr"/>
+      <c r="G1125" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1125" t="inlineStr"/>
+      <c r="I1125" t="inlineStr"/>
+      <c r="J1125" t="inlineStr"/>
+      <c r="K1125" t="inlineStr"/>
+      <c r="L1125" t="inlineStr"/>
+      <c r="M1125" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1125" t="inlineStr"/>
+      <c r="P1125" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1125" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Preview TTS</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr"/>
+      <c r="G1126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1126" t="inlineStr"/>
+      <c r="I1126" t="inlineStr"/>
+      <c r="J1126" t="inlineStr"/>
+      <c r="K1126" t="inlineStr"/>
+      <c r="L1126" t="inlineStr"/>
+      <c r="M1126" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1126" t="inlineStr"/>
+      <c r="P1126" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1126" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr"/>
+      <c r="G1127" t="inlineStr"/>
+      <c r="H1127" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1127" t="inlineStr"/>
+      <c r="J1127" t="inlineStr"/>
+      <c r="K1127" t="inlineStr"/>
+      <c r="L1127" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M1127" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1127" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1127" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1127" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr"/>
+      <c r="G1128" t="inlineStr"/>
+      <c r="H1128" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1128" t="inlineStr"/>
+      <c r="J1128" t="inlineStr"/>
+      <c r="K1128" t="inlineStr"/>
+      <c r="L1128" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M1128" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1128" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1128" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1128" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr"/>
+      <c r="G1129" t="inlineStr"/>
+      <c r="H1129" t="n">
+        <v>18</v>
+      </c>
+      <c r="I1129" t="inlineStr"/>
+      <c r="J1129" t="inlineStr"/>
+      <c r="K1129" t="inlineStr"/>
+      <c r="L1129" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M1129" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1129" t="inlineStr">
+        <is>
+          <t>$0.225, prompts &lt;= 200k tokens $0.45, prompts &gt; 200k $8.10 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1129" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1129" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr"/>
+      <c r="G1130" t="inlineStr"/>
+      <c r="H1130" t="n">
+        <v>10</v>
+      </c>
+      <c r="I1130" t="inlineStr"/>
+      <c r="J1130" t="inlineStr"/>
+      <c r="K1130" t="inlineStr"/>
+      <c r="L1130" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M1130" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1130" t="inlineStr">
+        <is>
+          <t>$0.125, prompts &lt;= 200k tokens $0.25, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1130" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1130" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro Preview TTS</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr"/>
+      <c r="G1131" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1131" t="inlineStr"/>
+      <c r="I1131" t="inlineStr"/>
+      <c r="J1131" t="inlineStr"/>
+      <c r="K1131" t="inlineStr"/>
+      <c r="L1131" t="inlineStr"/>
+      <c r="M1131" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1131" t="inlineStr"/>
+      <c r="P1131" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1131" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro Preview TTS</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr"/>
+      <c r="G1132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1132" t="inlineStr"/>
+      <c r="I1132" t="inlineStr"/>
+      <c r="J1132" t="inlineStr"/>
+      <c r="K1132" t="inlineStr"/>
+      <c r="L1132" t="inlineStr"/>
+      <c r="M1132" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1132" t="inlineStr"/>
+      <c r="P1132" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1132" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr"/>
+      <c r="G1133" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1133" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I1133" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J1133" t="inlineStr"/>
+      <c r="K1133" t="inlineStr"/>
+      <c r="L1133" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1133" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1133" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1133" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1133" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr"/>
+      <c r="G1134" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1134" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I1134" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J1134" t="inlineStr"/>
+      <c r="K1134" t="inlineStr"/>
+      <c r="L1134" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1134" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1134" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1134" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1134" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr"/>
+      <c r="G1135" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1135" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I1135" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J1135" t="inlineStr"/>
+      <c r="K1135" t="inlineStr"/>
+      <c r="L1135" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1135" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1135" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1135" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1135" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr"/>
+      <c r="G1136" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1136" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I1136" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J1136" t="inlineStr"/>
+      <c r="K1136" t="inlineStr"/>
+      <c r="L1136" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1136" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1136" t="inlineStr">
+        <is>
+          <t>Same as Standard, Batch pricing not yet implemented $0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1136" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1136" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr"/>
+      <c r="G1137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H1137" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I1137" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J1137" t="inlineStr"/>
+      <c r="K1137" t="inlineStr"/>
+      <c r="L1137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M1137" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1137" t="inlineStr">
+        <is>
+          <t>$0.09 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1137" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1137" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr"/>
+      <c r="G1138" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H1138" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I1138" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J1138" t="inlineStr"/>
+      <c r="K1138" t="inlineStr"/>
+      <c r="L1138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M1138" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1138" t="inlineStr">
+        <is>
+          <t>$0.09 (text / image / video) $0.18 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1138" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1138" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr"/>
+      <c r="G1139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1139" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1139" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J1139" t="inlineStr"/>
+      <c r="K1139" t="inlineStr"/>
+      <c r="L1139" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1139" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1139" t="inlineStr">
+        <is>
+          <t>$0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1139" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1139" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash Preview</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr"/>
+      <c r="G1140" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1140" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1140" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J1140" t="inlineStr"/>
+      <c r="K1140" t="inlineStr"/>
+      <c r="L1140" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1140" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1140" t="inlineStr">
+        <is>
+          <t>$0.05 (text / image / video) $0.10 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1140" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1140" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr"/>
+      <c r="G1141" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H1141" t="inlineStr"/>
+      <c r="I1141" t="inlineStr"/>
+      <c r="J1141" t="inlineStr"/>
+      <c r="K1141" t="inlineStr"/>
+      <c r="L1141" t="inlineStr"/>
+      <c r="M1141" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1141" t="inlineStr"/>
+      <c r="P1141" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1141" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr"/>
+      <c r="G1142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1142" t="inlineStr"/>
+      <c r="I1142" t="inlineStr"/>
+      <c r="J1142" t="inlineStr"/>
+      <c r="K1142" t="inlineStr"/>
+      <c r="L1142" t="inlineStr"/>
+      <c r="M1142" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1142" t="inlineStr"/>
+      <c r="P1142" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1142" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr"/>
+      <c r="G1143" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H1143" t="inlineStr"/>
+      <c r="I1143" t="inlineStr"/>
+      <c r="J1143" t="inlineStr"/>
+      <c r="K1143" t="inlineStr"/>
+      <c r="L1143" t="inlineStr"/>
+      <c r="M1143" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1143" t="inlineStr"/>
+      <c r="P1143" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1143" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr"/>
+      <c r="G1144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1144" t="inlineStr"/>
+      <c r="I1144" t="inlineStr"/>
+      <c r="J1144" t="inlineStr"/>
+      <c r="K1144" t="inlineStr"/>
+      <c r="L1144" t="inlineStr"/>
+      <c r="M1144" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1144" t="inlineStr"/>
+      <c r="P1144" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1144" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr"/>
+      <c r="G1145" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H1145" t="inlineStr"/>
+      <c r="I1145" t="inlineStr"/>
+      <c r="J1145" t="inlineStr"/>
+      <c r="K1145" t="inlineStr"/>
+      <c r="L1145" t="inlineStr"/>
+      <c r="M1145" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1145" t="inlineStr"/>
+      <c r="P1145" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1145" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>Gemini 3 Pro Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr"/>
+      <c r="G1146" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1146" t="inlineStr"/>
+      <c r="I1146" t="inlineStr"/>
+      <c r="J1146" t="inlineStr"/>
+      <c r="K1146" t="inlineStr"/>
+      <c r="L1146" t="inlineStr"/>
+      <c r="M1146" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1146" t="inlineStr"/>
+      <c r="P1146" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1146" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>text, image</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr"/>
+      <c r="G1147" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1147" t="inlineStr"/>
+      <c r="I1147" t="inlineStr"/>
+      <c r="J1147" t="inlineStr"/>
+      <c r="K1147" t="inlineStr"/>
+      <c r="L1147" t="inlineStr"/>
+      <c r="M1147" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1147" t="inlineStr"/>
+      <c r="P1147" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1147" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash Image 🍌</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>text/image</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr"/>
+      <c r="G1148" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1148" t="inlineStr"/>
+      <c r="I1148" t="inlineStr"/>
+      <c r="J1148" t="inlineStr"/>
+      <c r="K1148" t="inlineStr"/>
+      <c r="L1148" t="inlineStr"/>
+      <c r="M1148" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1148" t="inlineStr"/>
+      <c r="P1148" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1148" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash TTS Preview</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr"/>
+      <c r="G1149" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1149" t="inlineStr"/>
+      <c r="I1149" t="inlineStr"/>
+      <c r="J1149" t="inlineStr"/>
+      <c r="K1149" t="inlineStr"/>
+      <c r="L1149" t="inlineStr"/>
+      <c r="M1149" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1149" t="inlineStr"/>
+      <c r="P1149" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1149" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash TTS Preview</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr"/>
+      <c r="G1150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1150" t="inlineStr"/>
+      <c r="I1150" t="inlineStr"/>
+      <c r="J1150" t="inlineStr"/>
+      <c r="K1150" t="inlineStr"/>
+      <c r="L1150" t="inlineStr"/>
+      <c r="M1150" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1150" t="inlineStr"/>
+      <c r="P1150" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1150" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr"/>
+      <c r="G1151" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1151" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I1151" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J1151" t="inlineStr"/>
+      <c r="K1151" t="inlineStr"/>
+      <c r="L1151" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M1151" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1151" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1151" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1151" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr"/>
+      <c r="G1152" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H1152" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I1152" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J1152" t="inlineStr"/>
+      <c r="K1152" t="inlineStr"/>
+      <c r="L1152" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M1152" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1152" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1152" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1152" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr"/>
+      <c r="G1153" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1153" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I1153" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J1153" t="inlineStr"/>
+      <c r="K1153" t="inlineStr"/>
+      <c r="L1153" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M1153" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1153" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1153" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1153" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr"/>
+      <c r="G1154" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H1154" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I1154" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J1154" t="inlineStr"/>
+      <c r="K1154" t="inlineStr"/>
+      <c r="L1154" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M1154" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1154" t="inlineStr">
+        <is>
+          <t>$0.0125 (text / image / video) $0.025 (audio) $0.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1154" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1154" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr"/>
+      <c r="G1155" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H1155" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I1155" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J1155" t="inlineStr"/>
+      <c r="K1155" t="inlineStr"/>
+      <c r="L1155" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M1155" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1155" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1155" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1155" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr"/>
+      <c r="G1156" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H1156" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I1156" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J1156" t="inlineStr"/>
+      <c r="K1156" t="inlineStr"/>
+      <c r="L1156" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M1156" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1156" t="inlineStr">
+        <is>
+          <t>$0.045 (text / image / video) $0.09 (audio) $1.80 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1156" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1156" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr"/>
+      <c r="G1157" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1157" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I1157" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J1157" t="inlineStr"/>
+      <c r="K1157" t="inlineStr"/>
+      <c r="L1157" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1157" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1157" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1157" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1157" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr"/>
+      <c r="G1158" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1158" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I1158" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J1158" t="inlineStr"/>
+      <c r="K1158" t="inlineStr"/>
+      <c r="L1158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1158" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1158" t="inlineStr">
+        <is>
+          <t>$0.025 (text / image / video) $0.05 (audio) $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1158" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1158" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr"/>
+      <c r="G1159" t="inlineStr"/>
+      <c r="H1159" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1159" t="inlineStr"/>
+      <c r="J1159" t="inlineStr"/>
+      <c r="K1159" t="inlineStr"/>
+      <c r="L1159" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M1159" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1159" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1159" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1159" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr"/>
+      <c r="G1160" t="inlineStr"/>
+      <c r="H1160" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1160" t="inlineStr"/>
+      <c r="J1160" t="inlineStr"/>
+      <c r="K1160" t="inlineStr"/>
+      <c r="L1160" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M1160" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1160" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1160" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1160" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr"/>
+      <c r="G1161" t="inlineStr"/>
+      <c r="H1161" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I1161" t="inlineStr"/>
+      <c r="J1161" t="inlineStr"/>
+      <c r="K1161" t="inlineStr"/>
+      <c r="L1161" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M1161" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1161" t="inlineStr">
+        <is>
+          <t>$0.36, prompts &lt;= 200k tokens $0.72, prompts &gt; 200k $8.10 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1161" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1161" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro Preview</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr"/>
+      <c r="G1162" t="inlineStr"/>
+      <c r="H1162" t="n">
+        <v>12</v>
+      </c>
+      <c r="I1162" t="inlineStr"/>
+      <c r="J1162" t="inlineStr"/>
+      <c r="K1162" t="inlineStr"/>
+      <c r="L1162" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M1162" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1162" t="inlineStr">
+        <is>
+          <t>$0.20, prompts &lt;= 200k tokens $0.40, prompts &gt; 200k $4.50 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1162" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1162" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr"/>
+      <c r="G1163" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H1163" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I1163" t="inlineStr"/>
+      <c r="J1163" t="inlineStr"/>
+      <c r="K1163" t="inlineStr"/>
+      <c r="L1163" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1163" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1163" t="inlineStr">
+        <is>
+          <t>$0.075 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1163" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1163" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr"/>
+      <c r="G1164" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H1164" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I1164" t="inlineStr"/>
+      <c r="J1164" t="inlineStr"/>
+      <c r="K1164" t="inlineStr"/>
+      <c r="L1164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1164" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1164" t="inlineStr">
+        <is>
+          <t>$0.08 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1164" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1164" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr"/>
+      <c r="G1165" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H1165" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I1165" t="inlineStr"/>
+      <c r="J1165" t="inlineStr"/>
+      <c r="K1165" t="inlineStr"/>
+      <c r="L1165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1165" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1165" t="inlineStr">
+        <is>
+          <t>$0.27 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1165" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1165" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr"/>
+      <c r="G1166" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H1166" t="n">
+        <v>9</v>
+      </c>
+      <c r="I1166" t="inlineStr"/>
+      <c r="J1166" t="inlineStr"/>
+      <c r="K1166" t="inlineStr"/>
+      <c r="L1166" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1166" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1166" t="inlineStr">
+        <is>
+          <t>$0.15 $1.00 / 1,000,000 tokens per hour (storage price)</t>
+        </is>
+      </c>
+      <c r="P1166" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1166" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>Gemini Embedding</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>embedding</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr"/>
+      <c r="G1167" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H1167" t="inlineStr"/>
+      <c r="I1167" t="inlineStr"/>
+      <c r="J1167" t="inlineStr"/>
+      <c r="K1167" t="inlineStr"/>
+      <c r="L1167" t="inlineStr"/>
+      <c r="M1167" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1167" t="inlineStr"/>
+      <c r="P1167" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1167" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>Gemini Embedding</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>embedding</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr"/>
+      <c r="G1168" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1168" t="inlineStr"/>
+      <c r="I1168" t="inlineStr"/>
+      <c r="J1168" t="inlineStr"/>
+      <c r="K1168" t="inlineStr"/>
+      <c r="L1168" t="inlineStr"/>
+      <c r="M1168" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1168" t="inlineStr"/>
+      <c r="P1168" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1168" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr"/>
+      <c r="G1169" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1169" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1169" t="inlineStr"/>
+      <c r="J1169" t="inlineStr"/>
+      <c r="K1169" t="inlineStr"/>
+      <c r="L1169" t="inlineStr"/>
+      <c r="M1169" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1169" t="inlineStr"/>
+      <c r="P1169" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1169" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr"/>
+      <c r="G1170" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1170" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1170" t="inlineStr"/>
+      <c r="J1170" t="inlineStr"/>
+      <c r="K1170" t="inlineStr"/>
+      <c r="L1170" t="inlineStr"/>
+      <c r="M1170" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1170" t="inlineStr"/>
+      <c r="P1170" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1170" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr"/>
+      <c r="G1171" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1171" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1171" t="inlineStr"/>
+      <c r="J1171" t="inlineStr"/>
+      <c r="K1171" t="inlineStr"/>
+      <c r="L1171" t="inlineStr"/>
+      <c r="M1171" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1171" t="inlineStr"/>
+      <c r="P1171" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1171" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>Gemini Robotics-ER 1.6 Preview</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>robotics-er</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>text / image / video</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr"/>
+      <c r="G1172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1172" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1172" t="inlineStr"/>
+      <c r="J1172" t="inlineStr"/>
+      <c r="K1172" t="inlineStr"/>
+      <c r="L1172" t="inlineStr"/>
+      <c r="M1172" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1172" t="inlineStr"/>
+      <c r="P1172" t="inlineStr">
+        <is>
+          <t>https://ai.google.dev/gemini-api/docs/pricing?hl=en</t>
+        </is>
+      </c>
+      <c r="Q1172" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>chat-latest</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>chat</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>tools</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr"/>
+      <c r="G1173" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1173" t="n">
+        <v>30</v>
+      </c>
+      <c r="I1173" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J1173" t="inlineStr"/>
+      <c r="K1173" t="inlineStr"/>
+      <c r="L1173" t="inlineStr"/>
+      <c r="M1173" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1173" t="inlineStr">
+        <is>
+          <t>Video generation models | Transcription models | Prices per 1M tokens unless noted. | Tools</t>
+        </is>
+      </c>
+      <c r="P1173" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1173" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>computer-use-preview</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>computer</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr"/>
+      <c r="G1174" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H1174" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1174" t="inlineStr"/>
+      <c r="J1174" t="inlineStr"/>
+      <c r="K1174" t="inlineStr"/>
+      <c r="L1174" t="inlineStr"/>
+      <c r="M1174" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1174" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1174" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P1174" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1174" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini-transcribe</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>video-generation-models</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr"/>
+      <c r="G1175" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1175" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1175" t="inlineStr"/>
+      <c r="J1175" t="inlineStr"/>
+      <c r="K1175" t="inlineStr"/>
+      <c r="L1175" t="inlineStr"/>
+      <c r="M1175" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1175" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1175" t="inlineStr">
+        <is>
+          <t>Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models | Video generation models</t>
+        </is>
+      </c>
+      <c r="P1175" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1175" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>gpt-4o-transcribe</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>video-generation-models</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr"/>
+      <c r="G1176" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1176" t="n">
+        <v>10</v>
+      </c>
+      <c r="I1176" t="inlineStr"/>
+      <c r="J1176" t="inlineStr"/>
+      <c r="K1176" t="inlineStr"/>
+      <c r="L1176" t="inlineStr"/>
+      <c r="M1176" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1176" t="inlineStr">
+        <is>
+          <t>Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models | Video generation models</t>
+        </is>
+      </c>
+      <c r="P1176" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1176" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>gpt-5.3-codex</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr"/>
+      <c r="G1177" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H1177" t="n">
+        <v>28</v>
+      </c>
+      <c r="I1177" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J1177" t="inlineStr"/>
+      <c r="K1177" t="inlineStr"/>
+      <c r="L1177" t="inlineStr"/>
+      <c r="M1177" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1177" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P1177" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1177" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>gpt-5.3-codex</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>tools</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr"/>
+      <c r="G1178" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H1178" t="n">
+        <v>14</v>
+      </c>
+      <c r="I1178" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="J1178" t="inlineStr"/>
+      <c r="K1178" t="inlineStr"/>
+      <c r="L1178" t="inlineStr"/>
+      <c r="M1178" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1178" t="inlineStr">
+        <is>
+          <t>Video generation models | Transcription models | Prices per 1M tokens unless noted. | Tools</t>
+        </is>
+      </c>
+      <c r="P1178" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1178" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G1179" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1179" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I1179" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J1179" t="inlineStr"/>
+      <c r="K1179" t="inlineStr"/>
+      <c r="L1179" t="inlineStr"/>
+      <c r="M1179" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1179" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1179" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1179" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1179" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G1180" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1180" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1180" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J1180" t="inlineStr"/>
+      <c r="K1180" t="inlineStr"/>
+      <c r="L1180" t="inlineStr"/>
+      <c r="M1180" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1180" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1180" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1180" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>gpt-5.4-mini</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G1181" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H1181" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I1181" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J1181" t="inlineStr"/>
+      <c r="K1181" t="inlineStr"/>
+      <c r="L1181" t="inlineStr"/>
+      <c r="M1181" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1181" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1181" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1181" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1181" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>gpt-5.4-nano</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G1182" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H1182" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I1182" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J1182" t="inlineStr"/>
+      <c r="K1182" t="inlineStr"/>
+      <c r="L1182" t="inlineStr"/>
+      <c r="M1182" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1182" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1182" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1182" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1182" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>gpt-5.4-pro</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G1183" t="n">
+        <v>60</v>
+      </c>
+      <c r="H1183" t="n">
+        <v>270</v>
+      </c>
+      <c r="I1183" t="inlineStr"/>
+      <c r="J1183" t="inlineStr"/>
+      <c r="K1183" t="inlineStr"/>
+      <c r="L1183" t="inlineStr"/>
+      <c r="M1183" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1183" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1183" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1183" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1183" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>gpt-5.4-pro</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G1184" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1184" t="n">
+        <v>180</v>
+      </c>
+      <c r="I1184" t="inlineStr"/>
+      <c r="J1184" t="inlineStr"/>
+      <c r="K1184" t="inlineStr"/>
+      <c r="L1184" t="inlineStr"/>
+      <c r="M1184" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1184" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1184" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1184" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G1185" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1185" t="n">
+        <v>45</v>
+      </c>
+      <c r="I1185" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1185" t="inlineStr"/>
+      <c r="K1185" t="inlineStr"/>
+      <c r="L1185" t="inlineStr"/>
+      <c r="M1185" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1185" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1185" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1185" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1185" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G1186" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1186" t="n">
+        <v>30</v>
+      </c>
+      <c r="I1186" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J1186" t="inlineStr"/>
+      <c r="K1186" t="inlineStr"/>
+      <c r="L1186" t="inlineStr"/>
+      <c r="M1186" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1186" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1186" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1186" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1186" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>gpt-5.5-pro</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>flagship-models-long-context</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G1187" t="n">
+        <v>60</v>
+      </c>
+      <c r="H1187" t="n">
+        <v>270</v>
+      </c>
+      <c r="I1187" t="inlineStr"/>
+      <c r="J1187" t="inlineStr"/>
+      <c r="K1187" t="inlineStr"/>
+      <c r="L1187" t="inlineStr"/>
+      <c r="M1187" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1187" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1187" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1187" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>gpt-5.5-pro</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>flagship-models-short-context</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G1188" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1188" t="n">
+        <v>180</v>
+      </c>
+      <c r="I1188" t="inlineStr"/>
+      <c r="J1188" t="inlineStr"/>
+      <c r="K1188" t="inlineStr"/>
+      <c r="L1188" t="inlineStr"/>
+      <c r="M1188" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1188" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1188" t="inlineStr">
+        <is>
+          <t>Going live | Legacy APIs | Resources | Flagship models</t>
+        </is>
+      </c>
+      <c r="P1188" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1188" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr"/>
+      <c r="G1189" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1189" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1189" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J1189" t="inlineStr"/>
+      <c r="K1189" t="inlineStr"/>
+      <c r="L1189" t="inlineStr"/>
+      <c r="M1189" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1189" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1189" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P1189" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1189" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr"/>
+      <c r="G1190" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1190" t="inlineStr"/>
+      <c r="I1190" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J1190" t="inlineStr"/>
+      <c r="K1190" t="inlineStr"/>
+      <c r="L1190" t="inlineStr"/>
+      <c r="M1190" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1190" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1190" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P1190" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1190" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr"/>
+      <c r="G1191" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1191" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1191" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J1191" t="inlineStr"/>
+      <c r="K1191" t="inlineStr"/>
+      <c r="L1191" t="inlineStr"/>
+      <c r="M1191" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1191" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1191" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P1191" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1191" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>gpt-image-1-mini</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr"/>
+      <c r="G1192" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1192" t="inlineStr"/>
+      <c r="I1192" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J1192" t="inlineStr"/>
+      <c r="K1192" t="inlineStr"/>
+      <c r="L1192" t="inlineStr"/>
+      <c r="M1192" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1192" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1192" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P1192" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1192" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr"/>
+      <c r="G1193" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1193" t="n">
+        <v>16</v>
+      </c>
+      <c r="I1193" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1193" t="inlineStr"/>
+      <c r="K1193" t="inlineStr"/>
+      <c r="L1193" t="inlineStr"/>
+      <c r="M1193" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1193" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P1193" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1193" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr"/>
+      <c r="G1194" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1194" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1194" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J1194" t="inlineStr"/>
+      <c r="K1194" t="inlineStr"/>
+      <c r="L1194" t="inlineStr"/>
+      <c r="M1194" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1194" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P1194" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1194" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr"/>
+      <c r="G1195" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1195" t="n">
+        <v>32</v>
+      </c>
+      <c r="I1195" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1195" t="inlineStr"/>
+      <c r="K1195" t="inlineStr"/>
+      <c r="L1195" t="inlineStr"/>
+      <c r="M1195" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1195" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P1195" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1195" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>gpt-image-1.5</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr"/>
+      <c r="G1196" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1196" t="n">
+        <v>10</v>
+      </c>
+      <c r="I1196" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J1196" t="inlineStr"/>
+      <c r="K1196" t="inlineStr"/>
+      <c r="L1196" t="inlineStr"/>
+      <c r="M1196" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1196" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P1196" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1196" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr"/>
+      <c r="G1197" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1197" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1197" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1197" t="inlineStr"/>
+      <c r="K1197" t="inlineStr"/>
+      <c r="L1197" t="inlineStr"/>
+      <c r="M1197" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1197" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P1197" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1197" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>image-generation-models</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr"/>
+      <c r="G1198" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1198" t="inlineStr"/>
+      <c r="I1198" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="J1198" t="inlineStr"/>
+      <c r="K1198" t="inlineStr"/>
+      <c r="L1198" t="inlineStr"/>
+      <c r="M1198" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1198" t="inlineStr">
+        <is>
+          <t>Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted. | Image generation models</t>
+        </is>
+      </c>
+      <c r="P1198" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1198" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr"/>
+      <c r="G1199" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1199" t="n">
+        <v>30</v>
+      </c>
+      <c r="I1199" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1199" t="inlineStr"/>
+      <c r="K1199" t="inlineStr"/>
+      <c r="L1199" t="inlineStr"/>
+      <c r="M1199" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1199" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P1199" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1199" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>gpt</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>prices-per-1m-tokens-unless-noted</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr"/>
+      <c r="G1200" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1200" t="inlineStr"/>
+      <c r="I1200" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J1200" t="inlineStr"/>
+      <c r="K1200" t="inlineStr"/>
+      <c r="L1200" t="inlineStr"/>
+      <c r="M1200" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1200" t="inlineStr">
+        <is>
+          <t>Flagship models | Multimodal models | Realtime and audio generation models | Prices per 1M tokens unless noted.</t>
+        </is>
+      </c>
+      <c r="P1200" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1200" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>o3-deep-research</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr"/>
+      <c r="G1201" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1201" t="n">
+        <v>20</v>
+      </c>
+      <c r="I1201" t="inlineStr"/>
+      <c r="J1201" t="inlineStr"/>
+      <c r="K1201" t="inlineStr"/>
+      <c r="L1201" t="inlineStr"/>
+      <c r="M1201" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1201" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P1201" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1201" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>all-fine-tuned-models-will-remain-available-for-inference-until-their-base-models-are-deprecated-the-full-timeline-is-here</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr"/>
+      <c r="G1202" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1202" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1202" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J1202" t="inlineStr"/>
+      <c r="K1202" t="inlineStr"/>
+      <c r="L1202" t="inlineStr"/>
+      <c r="M1202" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1202" t="inlineStr">
+        <is>
+          <t>Specialized models | Finetuning | OpenAI is winding down the fine-tuning platform. The platform is no longer accessible to new users, but existing users of the fine-tuning platform will be able to create training jobs for the coming months. | All fine-tuned models will remain available for inference until their base models are deprecated. The full timeline is here .</t>
+        </is>
+      </c>
+      <c r="P1202" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1202" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr"/>
+      <c r="G1203" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1203" t="n">
+        <v>16</v>
+      </c>
+      <c r="I1203" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1203" t="inlineStr"/>
+      <c r="K1203" t="inlineStr"/>
+      <c r="L1203" t="inlineStr"/>
+      <c r="M1203" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1203" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P1203" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1203" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16 with data sharing</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>all-fine-tuned-models-will-remain-available-for-inference-until-their-base-models-are-deprecated-the-full-timeline-is-here</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr"/>
+      <c r="G1204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1204" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1204" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J1204" t="inlineStr"/>
+      <c r="K1204" t="inlineStr"/>
+      <c r="L1204" t="inlineStr"/>
+      <c r="M1204" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1204" t="inlineStr">
+        <is>
+          <t>Specialized models | Finetuning | OpenAI is winding down the fine-tuning platform. The platform is no longer accessible to new users, but existing users of the fine-tuning platform will be able to create training jobs for the coming months. | All fine-tuned models will remain available for inference until their base models are deprecated. The full timeline is here .</t>
+        </is>
+      </c>
+      <c r="P1204" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1204" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>o4-mini-2025-04-16 with data sharing</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr"/>
+      <c r="G1205" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1205" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1205" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J1205" t="inlineStr"/>
+      <c r="K1205" t="inlineStr"/>
+      <c r="L1205" t="inlineStr"/>
+      <c r="M1205" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1205" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P1205" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1205" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>o4-mini-deep-research</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>o4</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>specialized-models</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr"/>
+      <c r="G1206" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1206" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1206" t="inlineStr"/>
+      <c r="J1206" t="inlineStr"/>
+      <c r="K1206" t="inlineStr"/>
+      <c r="L1206" t="inlineStr"/>
+      <c r="M1206" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1206" t="inlineStr">
+        <is>
+          <t>Transcription models | Prices per 1M tokens unless noted. | Tools | Specialized models</t>
+        </is>
+      </c>
+      <c r="P1206" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/pricing?latest-pricing=flex</t>
+        </is>
+      </c>
+      <c r="Q1206" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>grok-4.20-0309-non-reasoning</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G1207" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1207" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1207" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J1207" t="inlineStr"/>
+      <c r="K1207" t="inlineStr"/>
+      <c r="L1207" t="inlineStr"/>
+      <c r="M1207" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1207" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P1207" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q1207" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>grok-4.20-0309-reasoning</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G1208" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1208" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1208" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J1208" t="inlineStr"/>
+      <c r="K1208" t="inlineStr"/>
+      <c r="L1208" t="inlineStr"/>
+      <c r="M1208" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1208" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P1208" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q1208" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>grok-4.20-multi-agent-0309</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G1209" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1209" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1209" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J1209" t="inlineStr"/>
+      <c r="K1209" t="inlineStr"/>
+      <c r="L1209" t="inlineStr"/>
+      <c r="M1209" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1209" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P1209" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q1209" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>grok-4.3</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G1210" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1210" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1210" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J1210" t="inlineStr"/>
+      <c r="K1210" t="inlineStr"/>
+      <c r="L1210" t="inlineStr"/>
+      <c r="M1210" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1210" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P1210" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q1210" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>grok-build-0.1</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>256k</t>
+        </is>
+      </c>
+      <c r="G1211" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1211" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1211" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J1211" t="inlineStr"/>
+      <c r="K1211" t="inlineStr"/>
+      <c r="L1211" t="inlineStr"/>
+      <c r="M1211" t="inlineStr">
+        <is>
+          <t>USD per 1M tokens</t>
+        </is>
+      </c>
+      <c r="N1211" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O1211" t="inlineStr">
+        <is>
+          <t>Official xAI Chat API pricing.</t>
+        </is>
+      </c>
+      <c r="P1211" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/docs/pricing</t>
+        </is>
+      </c>
+      <c r="Q1211" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:38:43+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -78822,7 +86116,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-31T07:14:42+00:00</t>
+          <t>2026-06-01T07:38:43+00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
